--- a/04_Network/03_Classify/c_data/03_classify.xlsx
+++ b/04_Network/03_Classify/c_data/03_classify.xlsx
@@ -10,15 +10,16 @@
     <sheet name="read_me" sheetId="1" r:id="rId1"/>
     <sheet name="counts" sheetId="2" r:id="rId2"/>
     <sheet name="auc" sheetId="3" r:id="rId3"/>
-    <sheet name="input_manifest" sheetId="4" r:id="rId4"/>
-    <sheet name="package_versions" sheetId="5" r:id="rId5"/>
+    <sheet name="plot_index" sheetId="4" r:id="rId4"/>
+    <sheet name="input_manifest" sheetId="5" r:id="rId5"/>
+    <sheet name="package_versions" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="124">
   <si>
     <t>sheet</t>
   </si>
@@ -38,6 +39,12 @@
     <t>Per module and task: AUC, median paired change (paired tasks), Wilcoxon p and BH FDR.</t>
   </si>
   <si>
+    <t>plot_index</t>
+  </si>
+  <si>
+    <t>PDF page and panel position (1 to 12) of every p &lt; 0.05 row of auc.</t>
+  </si>
+  <si>
     <t>input_manifest</t>
   </si>
   <si>
@@ -104,7 +111,7 @@
     <t>Baseline_HRvLR</t>
   </si>
   <si>
-    <t>HR vs LR at T1 (floor)</t>
+    <t>HR vs LR at T1</t>
   </si>
   <si>
     <t>Trained_HRvLR</t>
@@ -174,6 +181,12 @@
   </si>
   <si>
     <t>pink</t>
+  </si>
+  <si>
+    <t>pdf_page</t>
+  </si>
+  <si>
+    <t>position</t>
   </si>
   <si>
     <t>input</t>
@@ -720,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -761,6 +774,14 @@
       </c>
       <c r="B5" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -775,39 +796,39 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -833,10 +854,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -862,10 +883,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -891,10 +912,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -920,10 +941,10 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" t="b">
         <v>0</v>
@@ -949,10 +970,10 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" t="b">
         <v>0</v>
@@ -978,10 +999,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
@@ -1007,10 +1028,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
@@ -1046,54 +1067,54 @@
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>0.1836734693877551</v>
@@ -1116,19 +1137,19 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F3">
         <v>0.9183673469387755</v>
@@ -1151,19 +1172,19 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F4">
         <v>0.2448979591836735</v>
@@ -1186,19 +1207,19 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5">
         <v>0.2244897959183673</v>
@@ -1221,19 +1242,19 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F6">
         <v>0.7346938775510204</v>
@@ -1256,19 +1277,19 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F7">
         <v>0.6938775510204082</v>
@@ -1291,19 +1312,19 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F8">
         <v>0.5714285714285714</v>
@@ -1326,19 +1347,19 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F9">
         <v>0.6938775510204082</v>
@@ -1361,19 +1382,19 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F10">
         <v>0.3469387755102041</v>
@@ -1396,19 +1417,19 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F11">
         <v>0.4897959183673469</v>
@@ -1431,19 +1452,19 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" t="b">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F12">
         <v>0.6530612244897959</v>
@@ -1466,19 +1487,19 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F13">
         <v>0.5918367346938775</v>
@@ -1501,19 +1522,19 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" t="b">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F14">
         <v>0.859375</v>
@@ -1536,19 +1557,19 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C15" t="b">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F15">
         <v>0.171875</v>
@@ -1571,19 +1592,19 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" t="b">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F16">
         <v>0.78125</v>
@@ -1606,19 +1627,19 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C17" t="b">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F17">
         <v>0.265625</v>
@@ -1641,19 +1662,19 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18" t="b">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F18">
         <v>0.765625</v>
@@ -1676,19 +1697,19 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" t="b">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F19">
         <v>0.671875</v>
@@ -1711,19 +1732,19 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C20" t="b">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F20">
         <v>0.390625</v>
@@ -1746,19 +1767,19 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" t="b">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F21">
         <v>0.34375</v>
@@ -1781,19 +1802,19 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C22" t="b">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F22">
         <v>0.609375</v>
@@ -1816,19 +1837,19 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C23" t="b">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F23">
         <v>0.5625</v>
@@ -1851,19 +1872,19 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C24" t="b">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F24">
         <v>0.609375</v>
@@ -1886,19 +1907,19 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C25" t="b">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F25">
         <v>0.390625</v>
@@ -1921,19 +1942,19 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C26" t="b">
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F26">
         <v>0.1964285714285714</v>
@@ -1953,19 +1974,19 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C27" t="b">
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F27">
         <v>0.7857142857142857</v>
@@ -1985,19 +2006,19 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C28" t="b">
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F28">
         <v>0.2321428571428572</v>
@@ -2017,19 +2038,19 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C29" t="b">
         <v>0</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F29">
         <v>0.7321428571428571</v>
@@ -2049,19 +2070,19 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C30" t="b">
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F30">
         <v>0.3035714285714285</v>
@@ -2081,19 +2102,19 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C31" t="b">
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F31">
         <v>0.3392857142857143</v>
@@ -2113,19 +2134,19 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F32">
         <v>0.6607142857142857</v>
@@ -2145,19 +2166,19 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E33" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F33">
         <v>0.4107142857142857</v>
@@ -2177,19 +2198,19 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F34">
         <v>0.5357142857142857</v>
@@ -2209,19 +2230,19 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F35">
         <v>0.5178571428571429</v>
@@ -2241,19 +2262,19 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C36" t="b">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E36" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F36">
         <v>0.4821428571428572</v>
@@ -2273,19 +2294,19 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C37" t="b">
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E37" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F37">
         <v>0.4821428571428572</v>
@@ -2305,19 +2326,19 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C38" t="b">
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F38">
         <v>0.2857142857142857</v>
@@ -2337,19 +2358,19 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C39" t="b">
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E39" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F39">
         <v>0.7142857142857143</v>
@@ -2369,19 +2390,19 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C40" t="b">
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F40">
         <v>0.3214285714285715</v>
@@ -2401,19 +2422,19 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C41" t="b">
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E41" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F41">
         <v>0.6607142857142857</v>
@@ -2433,19 +2454,19 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C42" t="b">
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E42" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F42">
         <v>0.625</v>
@@ -2465,19 +2486,19 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C43" t="b">
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F43">
         <v>0.4464285714285715</v>
@@ -2497,19 +2518,19 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C44" t="b">
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F44">
         <v>0.5535714285714286</v>
@@ -2529,19 +2550,19 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C45" t="b">
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F45">
         <v>0.5357142857142857</v>
@@ -2561,19 +2582,19 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C46" t="b">
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F46">
         <v>0.5357142857142857</v>
@@ -2593,19 +2614,19 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C47" t="b">
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F47">
         <v>0.5357142857142857</v>
@@ -2625,19 +2646,19 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C48" t="b">
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E48" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F48">
         <v>0.5178571428571429</v>
@@ -2657,19 +2678,19 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C49" t="b">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E49" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F49">
         <v>0.5</v>
@@ -2689,19 +2710,19 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C50" t="b">
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E50" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F50">
         <v>0.7678571428571429</v>
@@ -2721,19 +2742,19 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C51" t="b">
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E51" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F51">
         <v>0.7321428571428571</v>
@@ -2753,19 +2774,19 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C52" t="b">
         <v>0</v>
       </c>
       <c r="D52" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E52" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F52">
         <v>0.7142857142857143</v>
@@ -2785,19 +2806,19 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C53" t="b">
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E53" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F53">
         <v>0.6964285714285714</v>
@@ -2817,19 +2838,19 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C54" t="b">
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E54" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F54">
         <v>0.3035714285714285</v>
@@ -2849,19 +2870,19 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C55" t="b">
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E55" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F55">
         <v>0.3571428571428572</v>
@@ -2881,19 +2902,19 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B56" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C56" t="b">
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E56" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F56">
         <v>0.375</v>
@@ -2913,19 +2934,19 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C57" t="b">
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E57" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F57">
         <v>0.6071428571428571</v>
@@ -2945,19 +2966,19 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C58" t="b">
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E58" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F58">
         <v>0.4107142857142857</v>
@@ -2977,19 +2998,19 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C59" t="b">
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E59" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F59">
         <v>0.4285714285714285</v>
@@ -3009,19 +3030,19 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C60" t="b">
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E60" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F60">
         <v>0.4285714285714285</v>
@@ -3041,19 +3062,19 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C61" t="b">
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E61" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F61">
         <v>0.4464285714285715</v>
@@ -3073,19 +3094,19 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C62" t="b">
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E62" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F62">
         <v>0.8888888888888888</v>
@@ -3108,19 +3129,19 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C63" t="b">
         <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E63" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F63">
         <v>0.3055555555555556</v>
@@ -3143,19 +3164,19 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C64" t="b">
         <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E64" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F64">
         <v>0.6944444444444444</v>
@@ -3178,19 +3199,19 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C65" t="b">
         <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E65" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F65">
         <v>0.6388888888888888</v>
@@ -3213,19 +3234,19 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C66" t="b">
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E66" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F66">
         <v>0.1388888888888889</v>
@@ -3248,19 +3269,19 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B67" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C67" t="b">
         <v>1</v>
       </c>
       <c r="D67" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E67" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F67">
         <v>0.6666666666666666</v>
@@ -3283,19 +3304,19 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B68" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C68" t="b">
         <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E68" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F68">
         <v>0.5277777777777778</v>
@@ -3318,19 +3339,19 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B69" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C69" t="b">
         <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E69" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F69">
         <v>0.5</v>
@@ -3353,19 +3374,19 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B70" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C70" t="b">
         <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E70" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F70">
         <v>0.4166666666666667</v>
@@ -3388,19 +3409,19 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B71" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C71" t="b">
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E71" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F71">
         <v>0.5277777777777778</v>
@@ -3423,19 +3444,19 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B72" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C72" t="b">
         <v>1</v>
       </c>
       <c r="D72" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E72" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F72">
         <v>0.6111111111111112</v>
@@ -3458,19 +3479,19 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C73" t="b">
         <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E73" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F73">
         <v>0.4722222222222222</v>
@@ -3493,19 +3514,19 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B74" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C74" t="b">
         <v>1</v>
       </c>
       <c r="D74" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E74" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F74">
         <v>0.6875</v>
@@ -3528,19 +3549,19 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B75" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C75" t="b">
         <v>1</v>
       </c>
       <c r="D75" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E75" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F75">
         <v>0.515625</v>
@@ -3563,19 +3584,19 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B76" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C76" t="b">
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E76" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F76">
         <v>0.421875</v>
@@ -3598,19 +3619,19 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B77" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C77" t="b">
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E77" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F77">
         <v>0.578125</v>
@@ -3633,19 +3654,19 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B78" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C78" t="b">
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E78" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F78">
         <v>0.40625</v>
@@ -3668,19 +3689,19 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B79" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C79" t="b">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E79" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F79">
         <v>0.46875</v>
@@ -3703,19 +3724,19 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B80" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C80" t="b">
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E80" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F80">
         <v>0.515625</v>
@@ -3738,19 +3759,19 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B81" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C81" t="b">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E81" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F81">
         <v>0.5</v>
@@ -3773,19 +3794,19 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B82" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C82" t="b">
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E82" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F82">
         <v>0.4375</v>
@@ -3808,19 +3829,19 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C83" t="b">
         <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E83" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F83">
         <v>0.390625</v>
@@ -3843,19 +3864,19 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B84" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C84" t="b">
         <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E84" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F84">
         <v>0.46875</v>
@@ -3878,19 +3899,19 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B85" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C85" t="b">
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E85" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F85">
         <v>0.625</v>
@@ -3913,19 +3934,19 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C86" t="b">
         <v>0</v>
       </c>
       <c r="D86" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E86" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F86">
         <v>0.7291666666666666</v>
@@ -3945,19 +3966,19 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B87" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C87" t="b">
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E87" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F87">
         <v>0.6666666666666666</v>
@@ -3977,19 +3998,19 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B88" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C88" t="b">
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E88" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F88">
         <v>0.3333333333333333</v>
@@ -4009,19 +4030,19 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C89" t="b">
         <v>0</v>
       </c>
       <c r="D89" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E89" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F89">
         <v>0.3541666666666667</v>
@@ -4041,19 +4062,19 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C90" t="b">
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E90" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F90">
         <v>0.625</v>
@@ -4073,19 +4094,19 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B91" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C91" t="b">
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E91" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F91">
         <v>0.6041666666666666</v>
@@ -4105,19 +4126,19 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B92" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C92" t="b">
         <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E92" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F92">
         <v>0.4375</v>
@@ -4137,19 +4158,19 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C93" t="b">
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E93" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F93">
         <v>0.4583333333333333</v>
@@ -4169,19 +4190,19 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B94" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C94" t="b">
         <v>0</v>
       </c>
       <c r="D94" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E94" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F94">
         <v>0.5416666666666666</v>
@@ -4201,19 +4222,19 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C95" t="b">
         <v>0</v>
       </c>
       <c r="D95" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E95" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F95">
         <v>0.4791666666666667</v>
@@ -4233,19 +4254,19 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C96" t="b">
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E96" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F96">
         <v>0.5</v>
@@ -4265,19 +4286,19 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C97" t="b">
         <v>0</v>
       </c>
       <c r="D97" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E97" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F97">
         <v>0.5</v>
@@ -4302,29 +4323,126 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1">
+    <row r="1" spans="1:5" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="E1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>44</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4334,337 +4452,369 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
         <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
         <v>67</v>
-      </c>
-      <c r="C27" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/04_Network/03_Classify/c_data/03_classify.xlsx
+++ b/04_Network/03_Classify/c_data/03_classify.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="169">
   <si>
     <t>sheet</t>
   </si>
@@ -42,7 +42,7 @@
     <t>plot_index</t>
   </si>
   <si>
-    <t>PDF page and panel position (1 to 12) of every p &lt; 0.05 row of auc.</t>
+    <t>PDF page of each overview, and page and panel position (1 to 12) of every p &lt; 0.05 row.</t>
   </si>
   <si>
     <t>input_manifest</t>
@@ -189,6 +189,12 @@
     <t>position</t>
   </si>
   <si>
+    <t>overview</t>
+  </si>
+  <si>
+    <t>modules</t>
+  </si>
+  <si>
     <t>input</t>
   </si>
   <si>
@@ -198,9 +204,6 @@
     <t>md5</t>
   </si>
   <si>
-    <t>modules</t>
-  </si>
-  <si>
     <t>04_Network/01_Build_Modules/c_data/modules.rds</t>
   </si>
   <si>
@@ -216,6 +219,15 @@
     <t>source</t>
   </si>
   <si>
+    <t>BiocGenerics</t>
+  </si>
+  <si>
+    <t>0.58.0</t>
+  </si>
+  <si>
+    <t>Bioconductor 3.23 (R 4.6.0)</t>
+  </si>
+  <si>
     <t>BiocManager</t>
   </si>
   <si>
@@ -225,12 +237,66 @@
     <t>CRAN (R 4.6.0)</t>
   </si>
   <si>
+    <t>circlize</t>
+  </si>
+  <si>
+    <t>0.4.18</t>
+  </si>
+  <si>
     <t>cli</t>
   </si>
   <si>
     <t>3.6.6</t>
   </si>
   <si>
+    <t>clue</t>
+  </si>
+  <si>
+    <t>0.3-68</t>
+  </si>
+  <si>
+    <t>cluster</t>
+  </si>
+  <si>
+    <t>2.1.8.2</t>
+  </si>
+  <si>
+    <t>codetools</t>
+  </si>
+  <si>
+    <t>0.2-20</t>
+  </si>
+  <si>
+    <t>colorspace</t>
+  </si>
+  <si>
+    <t>2.1-2</t>
+  </si>
+  <si>
+    <t>ComplexHeatmap</t>
+  </si>
+  <si>
+    <t>2.28.0</t>
+  </si>
+  <si>
+    <t>crayon</t>
+  </si>
+  <si>
+    <t>1.5.3</t>
+  </si>
+  <si>
+    <t>digest</t>
+  </si>
+  <si>
+    <t>0.6.39</t>
+  </si>
+  <si>
+    <t>doParallel</t>
+  </si>
+  <si>
+    <t>1.0.17</t>
+  </si>
+  <si>
     <t>dplyr</t>
   </si>
   <si>
@@ -243,18 +309,33 @@
     <t>2.1.2</t>
   </si>
   <si>
+    <t>foreach</t>
+  </si>
+  <si>
+    <t>1.5.2</t>
+  </si>
+  <si>
     <t>generics</t>
   </si>
   <si>
     <t>0.1.4</t>
   </si>
   <si>
+    <t>GetoptLong</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
     <t>ggplot2</t>
   </si>
   <si>
     <t>4.0.3</t>
   </si>
   <si>
+    <t>GlobalOptions</t>
+  </si>
+  <si>
     <t>glue</t>
   </si>
   <si>
@@ -273,6 +354,18 @@
     <t>1.0.2</t>
   </si>
   <si>
+    <t>IRanges</t>
+  </si>
+  <si>
+    <t>2.46.0</t>
+  </si>
+  <si>
+    <t>iterators</t>
+  </si>
+  <si>
+    <t>1.0.14</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -291,6 +384,12 @@
     <t>2.0.5</t>
   </si>
   <si>
+    <t>matrixStats</t>
+  </si>
+  <si>
+    <t>1.5.0</t>
+  </si>
+  <si>
     <t>pillar</t>
   </si>
   <si>
@@ -303,6 +402,12 @@
     <t>2.0.3</t>
   </si>
   <si>
+    <t>png</t>
+  </si>
+  <si>
+    <t>0.1-9</t>
+  </si>
+  <si>
     <t>purrr</t>
   </si>
   <si>
@@ -327,6 +432,12 @@
     <t>1.2.3</t>
   </si>
   <si>
+    <t>rjson</t>
+  </si>
+  <si>
+    <t>0.2.23</t>
+  </si>
+  <si>
     <t>rlang</t>
   </si>
   <si>
@@ -342,6 +453,12 @@
     <t>2.1.1</t>
   </si>
   <si>
+    <t>S4Vectors</t>
+  </si>
+  <si>
+    <t>0.50.0</t>
+  </si>
+  <si>
     <t>S7</t>
   </si>
   <si>
@@ -358,6 +475,24 @@
   </si>
   <si>
     <t>1.2.4</t>
+  </si>
+  <si>
+    <t>shape</t>
+  </si>
+  <si>
+    <t>1.4.6.1</t>
+  </si>
+  <si>
+    <t>stringi</t>
+  </si>
+  <si>
+    <t>1.8.7</t>
+  </si>
+  <si>
+    <t>stringr</t>
+  </si>
+  <si>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>tibble</t>
@@ -4323,7 +4458,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
@@ -4331,13 +4466,13 @@
         <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>55</v>
@@ -4345,33 +4480,27 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
+        <v>57</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3">
+        <v>44</v>
+      </c>
+      <c r="C3">
         <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -4382,33 +4511,33 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
+        <v>42</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5">
+        <v>43</v>
+      </c>
+      <c r="C5">
         <v>3</v>
       </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4416,16 +4545,16 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
+        <v>47</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4433,15 +4562,32 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
         <v>51</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
         <v>51</v>
       </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
+      <c r="E8">
         <v>3</v>
       </c>
     </row>
@@ -4457,24 +4603,24 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -4484,227 +4630,227 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
         <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4715,7 +4861,7 @@
         <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4726,7 +4872,7 @@
         <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4737,7 +4883,7 @@
         <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4748,7 +4894,7 @@
         <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4759,7 +4905,7 @@
         <v>114</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4770,7 +4916,7 @@
         <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4778,43 +4924,285 @@
         <v>117</v>
       </c>
       <c r="B27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" t="s">
         <v>71</v>
-      </c>
-      <c r="C27" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>133</v>
+      </c>
+      <c r="B35" t="s">
+        <v>134</v>
+      </c>
+      <c r="C35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>135</v>
+      </c>
+      <c r="B36" t="s">
+        <v>136</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" t="s">
+        <v>138</v>
+      </c>
+      <c r="C37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>148</v>
+      </c>
+      <c r="B42" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>150</v>
+      </c>
+      <c r="B43" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>154</v>
+      </c>
+      <c r="B45" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>156</v>
+      </c>
+      <c r="B46" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>160</v>
+      </c>
+      <c r="B48" t="s">
+        <v>161</v>
+      </c>
+      <c r="C48" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>163</v>
+      </c>
+      <c r="B50" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B52" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/04_Network/03_Classify/c_data/03_classify.xlsx
+++ b/04_Network/03_Classify/c_data/03_classify.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="170">
   <si>
     <t>sheet</t>
   </si>
@@ -192,16 +192,19 @@
     <t>overview</t>
   </si>
   <si>
+    <t>Classification overview: modules</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>md5</t>
+  </si>
+  <si>
     <t>modules</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>md5</t>
   </si>
   <si>
     <t>04_Network/01_Build_Modules/c_data/modules.rds</t>
@@ -4614,13 +4617,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4635,574 +4638,574 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
         <v>72</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C38" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C40" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B44" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B48" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C52" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/04_Network/03_Classify/c_data/03_classify.xlsx
+++ b/04_Network/03_Classify/c_data/03_classify.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="177">
   <si>
     <t>sheet</t>
   </si>
@@ -147,42 +147,51 @@
     <t>fdr</t>
   </si>
   <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>purple</t>
+  </si>
+  <si>
+    <t>turquoise</t>
+  </si>
+  <si>
+    <t>pink</t>
+  </si>
+  <si>
+    <t>brown</t>
+  </si>
+  <si>
     <t>green</t>
   </si>
   <si>
+    <t>magenta</t>
+  </si>
+  <si>
+    <t>salmon</t>
+  </si>
+  <si>
+    <t>black</t>
+  </si>
+  <si>
     <t>greenyellow</t>
   </si>
   <si>
-    <t>blue</t>
-  </si>
-  <si>
-    <t>brown</t>
-  </si>
-  <si>
-    <t>purple</t>
-  </si>
-  <si>
     <t>red</t>
   </si>
   <si>
-    <t>turquoise</t>
+    <t>cyan</t>
+  </si>
+  <si>
+    <t>midnightblue</t>
+  </si>
+  <si>
+    <t>tan</t>
   </si>
   <si>
     <t>yellow</t>
   </si>
   <si>
-    <t>tan</t>
-  </si>
-  <si>
-    <t>black</t>
-  </si>
-  <si>
-    <t>magenta</t>
-  </si>
-  <si>
-    <t>pink</t>
-  </si>
-  <si>
     <t>pdf_page</t>
   </si>
   <si>
@@ -210,7 +219,7 @@
     <t>04_Network/01_Build_Modules/c_data/modules.rds</t>
   </si>
   <si>
-    <t>d85662db0c6db8e9491364d9db854f76</t>
+    <t>78dd0603e90231fb458e53f5f2d172b9</t>
   </si>
   <si>
     <t>package</t>
@@ -411,6 +420,15 @@
     <t>0.1-9</t>
   </si>
   <si>
+    <t>pROC</t>
+  </si>
+  <si>
+    <t>1.19.1</t>
+  </si>
+  <si>
+    <t>CRAN (R 4.6.1)</t>
+  </si>
+  <si>
     <t>purrr</t>
   </si>
   <si>
@@ -429,6 +447,12 @@
     <t>1.1-3</t>
   </si>
   <si>
+    <t>Rcpp</t>
+  </si>
+  <si>
+    <t>1.1.1-1.1</t>
+  </si>
+  <si>
     <t>renv</t>
   </si>
   <si>
@@ -445,9 +469,6 @@
   </si>
   <si>
     <t>1.3.0</t>
-  </si>
-  <si>
-    <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
     <t>rprojroot</t>
@@ -981,10 +1002,10 @@
         <v>0.03125</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1010,7 +1031,7 @@
         <v>0.0078125</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1039,10 +1060,10 @@
         <v>0.015625</v>
       </c>
       <c r="G4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1068,13 +1089,13 @@
         <v>0.0078125</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
         <v>3</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1097,10 +1118,10 @@
         <v>0.0003108003108003108</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1126,7 +1147,7 @@
         <v>0.0003108003108003108</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1155,10 +1176,10 @@
         <v>0.000666000666000666</v>
       </c>
       <c r="G8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1184,13 +1205,13 @@
         <v>0.0003108003108003108</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1200,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1">
@@ -1255,10 +1276,10 @@
         <v>42</v>
       </c>
       <c r="F2">
-        <v>0.1836734693877551</v>
+        <v>0.163265306122449</v>
       </c>
       <c r="G2">
-        <v>-0.1080620137695293</v>
+        <v>-0.1895446333247326</v>
       </c>
       <c r="H2">
         <v>0.015625</v>
@@ -1270,7 +1291,7 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.1875000000000001</v>
+        <v>0.2343750000000001</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1293,7 +1314,7 @@
         <v>0.9183673469387755</v>
       </c>
       <c r="G3">
-        <v>0.2018992321765917</v>
+        <v>0.2017200455808207</v>
       </c>
       <c r="H3">
         <v>0.04687500000000001</v>
@@ -1305,7 +1326,7 @@
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.2812500000000001</v>
+        <v>0.2343750000000001</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1325,13 +1346,13 @@
         <v>44</v>
       </c>
       <c r="F4">
-        <v>0.2448979591836735</v>
+        <v>0.6122448979591837</v>
       </c>
       <c r="G4">
-        <v>-0.1338876973211036</v>
+        <v>0.04052501671806824</v>
       </c>
       <c r="H4">
-        <v>0.15625</v>
+        <v>0.04687500000000001</v>
       </c>
       <c r="I4">
         <v>7</v>
@@ -1340,7 +1361,7 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>0.3750000000000001</v>
+        <v>0.2343750000000001</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1360,13 +1381,13 @@
         <v>45</v>
       </c>
       <c r="F5">
-        <v>0.2244897959183673</v>
+        <v>0.7755102040816326</v>
       </c>
       <c r="G5">
-        <v>-0.2148513004164167</v>
+        <v>0.12256369925543</v>
       </c>
       <c r="H5">
-        <v>0.15625</v>
+        <v>0.109375</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -1375,7 +1396,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>0.3750000000000001</v>
+        <v>0.4101562500000001</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1395,13 +1416,13 @@
         <v>46</v>
       </c>
       <c r="F6">
-        <v>0.7346938775510204</v>
+        <v>0.2448979591836735</v>
       </c>
       <c r="G6">
-        <v>0.1140059438199842</v>
+        <v>-0.1596588599641741</v>
       </c>
       <c r="H6">
-        <v>0.15625</v>
+        <v>0.2187500000000001</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -1410,7 +1431,7 @@
         <v>7</v>
       </c>
       <c r="K6">
-        <v>0.3750000000000001</v>
+        <v>0.4687500000000001</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1430,10 +1451,10 @@
         <v>47</v>
       </c>
       <c r="F7">
-        <v>0.6938775510204082</v>
+        <v>0.6530612244897959</v>
       </c>
       <c r="G7">
-        <v>0.2463248734082179</v>
+        <v>0.1692604200258208</v>
       </c>
       <c r="H7">
         <v>0.2187500000000001</v>
@@ -1445,7 +1466,7 @@
         <v>7</v>
       </c>
       <c r="K7">
-        <v>0.3750000000000001</v>
+        <v>0.4687500000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1465,10 +1486,10 @@
         <v>48</v>
       </c>
       <c r="F8">
-        <v>0.5714285714285714</v>
+        <v>0.2040816326530612</v>
       </c>
       <c r="G8">
-        <v>0.03088528831463401</v>
+        <v>-0.07909445693915869</v>
       </c>
       <c r="H8">
         <v>0.2187500000000001</v>
@@ -1480,7 +1501,7 @@
         <v>7</v>
       </c>
       <c r="K8">
-        <v>0.3750000000000001</v>
+        <v>0.4687500000000001</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1500,10 +1521,10 @@
         <v>49</v>
       </c>
       <c r="F9">
-        <v>0.6938775510204082</v>
+        <v>0.2448979591836735</v>
       </c>
       <c r="G9">
-        <v>0.03097961597712295</v>
+        <v>-0.04210645234594217</v>
       </c>
       <c r="H9">
         <v>0.2968750000000001</v>
@@ -1515,7 +1536,7 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>0.4453125000000001</v>
+        <v>0.5566406250000001</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1535,10 +1556,10 @@
         <v>50</v>
       </c>
       <c r="F10">
-        <v>0.3469387755102041</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="G10">
-        <v>-0.06375413997686893</v>
+        <v>0.05695789805693754</v>
       </c>
       <c r="H10">
         <v>0.5781250000000001</v>
@@ -1550,7 +1571,7 @@
         <v>7</v>
       </c>
       <c r="K10">
-        <v>0.7500000000000001</v>
+        <v>0.7883522727272728</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1570,13 +1591,13 @@
         <v>51</v>
       </c>
       <c r="F11">
-        <v>0.4897959183673469</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="G11">
-        <v>-0.03523208062790908</v>
+        <v>-0.07482199314333263</v>
       </c>
       <c r="H11">
-        <v>0.6875000000000001</v>
+        <v>0.5781250000000001</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -1585,7 +1606,7 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>0.7500000000000001</v>
+        <v>0.7883522727272728</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1605,13 +1626,13 @@
         <v>52</v>
       </c>
       <c r="F12">
-        <v>0.6530612244897959</v>
+        <v>0.4489795918367347</v>
       </c>
       <c r="G12">
-        <v>0.01981267979496353</v>
+        <v>-0.08432245695934777</v>
       </c>
       <c r="H12">
-        <v>0.6875000000000001</v>
+        <v>0.5781250000000001</v>
       </c>
       <c r="I12">
         <v>7</v>
@@ -1620,7 +1641,7 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>0.7500000000000001</v>
+        <v>0.7883522727272728</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1640,10 +1661,10 @@
         <v>53</v>
       </c>
       <c r="F13">
-        <v>0.5918367346938775</v>
+        <v>0.4489795918367347</v>
       </c>
       <c r="G13">
-        <v>-0.02878060128583034</v>
+        <v>-0.01489577072963743</v>
       </c>
       <c r="H13">
         <v>0.8125000000000001</v>
@@ -1660,107 +1681,107 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" t="b">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F14">
-        <v>0.859375</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="G14">
-        <v>0.1340280487074366</v>
+        <v>0.01932100864239882</v>
       </c>
       <c r="H14">
-        <v>0.007812500000000002</v>
+        <v>0.8125000000000001</v>
       </c>
       <c r="I14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>0.09375000000000003</v>
+        <v>0.8125000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" t="b">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F15">
-        <v>0.171875</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G15">
-        <v>-0.09944772128704421</v>
+        <v>-0.05241491163505533</v>
       </c>
       <c r="H15">
-        <v>0.02343750000000001</v>
+        <v>0.8125000000000001</v>
       </c>
       <c r="I15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>0.1406250000000001</v>
+        <v>0.8125000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16" t="b">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F16">
-        <v>0.78125</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="G16">
-        <v>0.06199391912238138</v>
+        <v>-0.007881495365692354</v>
       </c>
       <c r="H16">
-        <v>0.03906250000000001</v>
+        <v>0.8125000000000001</v>
       </c>
       <c r="I16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>0.1562500000000001</v>
+        <v>0.8125000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1774,19 +1795,19 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F17">
-        <v>0.265625</v>
+        <v>0.171875</v>
       </c>
       <c r="G17">
-        <v>-0.07370302504252577</v>
+        <v>-0.09400482455360595</v>
       </c>
       <c r="H17">
-        <v>0.109375</v>
+        <v>0.007812500000000002</v>
       </c>
       <c r="I17">
         <v>8</v>
@@ -1795,7 +1816,7 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>0.3281250000000001</v>
+        <v>0.03906250000000001</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1809,19 +1830,19 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F18">
-        <v>0.765625</v>
+        <v>0.734375</v>
       </c>
       <c r="G18">
-        <v>0.08304145425613496</v>
+        <v>0.1162682800547686</v>
       </c>
       <c r="H18">
-        <v>0.1484375</v>
+        <v>0.007812500000000002</v>
       </c>
       <c r="I18">
         <v>8</v>
@@ -1830,7 +1851,7 @@
         <v>8</v>
       </c>
       <c r="K18">
-        <v>0.3562500000000001</v>
+        <v>0.03906250000000001</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1844,19 +1865,19 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F19">
-        <v>0.671875</v>
+        <v>0.09375</v>
       </c>
       <c r="G19">
-        <v>0.07743313898107258</v>
+        <v>-0.1637012459851492</v>
       </c>
       <c r="H19">
-        <v>0.5468750000000001</v>
+        <v>0.007812500000000002</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -1865,7 +1886,7 @@
         <v>8</v>
       </c>
       <c r="K19">
-        <v>0.8096590909090909</v>
+        <v>0.03906250000000001</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1879,19 +1900,19 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F20">
-        <v>0.390625</v>
+        <v>0.84375</v>
       </c>
       <c r="G20">
-        <v>-0.0236229074000185</v>
+        <v>0.1074234467393508</v>
       </c>
       <c r="H20">
-        <v>0.5468750000000001</v>
+        <v>0.015625</v>
       </c>
       <c r="I20">
         <v>8</v>
@@ -1900,7 +1921,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>0.8096590909090909</v>
+        <v>0.05859375000000001</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1914,19 +1935,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F21">
-        <v>0.34375</v>
+        <v>0.171875</v>
       </c>
       <c r="G21">
-        <v>-0.1011480518054794</v>
+        <v>-0.1267924341333494</v>
       </c>
       <c r="H21">
-        <v>0.5468750000000001</v>
+        <v>0.02343750000000001</v>
       </c>
       <c r="I21">
         <v>8</v>
@@ -1935,7 +1956,7 @@
         <v>8</v>
       </c>
       <c r="K21">
-        <v>0.8096590909090909</v>
+        <v>0.05859375000000001</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1949,19 +1970,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F22">
-        <v>0.609375</v>
+        <v>0.671875</v>
       </c>
       <c r="G22">
-        <v>0.02690979067477132</v>
+        <v>0.07580347806601506</v>
       </c>
       <c r="H22">
-        <v>0.7421875000000001</v>
+        <v>0.02343750000000001</v>
       </c>
       <c r="I22">
         <v>8</v>
@@ -1970,7 +1991,7 @@
         <v>8</v>
       </c>
       <c r="K22">
-        <v>0.8096590909090909</v>
+        <v>0.05859375000000001</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1984,19 +2005,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F23">
-        <v>0.5625</v>
+        <v>0.78125</v>
       </c>
       <c r="G23">
-        <v>0.05209008110099463</v>
+        <v>0.09568584612090247</v>
       </c>
       <c r="H23">
-        <v>0.7421875000000001</v>
+        <v>0.109375</v>
       </c>
       <c r="I23">
         <v>8</v>
@@ -2005,7 +2026,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>0.8096590909090909</v>
+        <v>0.1822916666666667</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2019,19 +2040,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F24">
-        <v>0.609375</v>
+        <v>0.734375</v>
       </c>
       <c r="G24">
-        <v>0.02175419534236315</v>
+        <v>0.1183212516935555</v>
       </c>
       <c r="H24">
-        <v>0.7421875000000001</v>
+        <v>0.109375</v>
       </c>
       <c r="I24">
         <v>8</v>
@@ -2040,7 +2061,7 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>0.8096590909090909</v>
+        <v>0.1822916666666667</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2054,19 +2075,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F25">
-        <v>0.390625</v>
+        <v>0.125</v>
       </c>
       <c r="G25">
-        <v>0.003193503640848416</v>
+        <v>-0.2204579449312783</v>
       </c>
       <c r="H25">
-        <v>0.8437500000000001</v>
+        <v>0.109375</v>
       </c>
       <c r="I25">
         <v>8</v>
@@ -2075,146 +2096,158 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <v>0.8437500000000001</v>
+        <v>0.1822916666666667</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F26">
-        <v>0.1964285714285714</v>
+        <v>0.328125</v>
+      </c>
+      <c r="G26">
+        <v>-0.05309823078175435</v>
       </c>
       <c r="H26">
-        <v>0.05407925407925408</v>
+        <v>0.3828125000000001</v>
       </c>
       <c r="I26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>8</v>
       </c>
       <c r="K26">
-        <v>0.3754467754467755</v>
+        <v>0.5742187500000001</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F27">
-        <v>0.7857142857142857</v>
+        <v>0.625</v>
+      </c>
+      <c r="G27">
+        <v>0.06792911749308136</v>
       </c>
       <c r="H27">
-        <v>0.07210567210567211</v>
+        <v>0.5468750000000001</v>
       </c>
       <c r="I27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>8</v>
       </c>
       <c r="K27">
-        <v>0.3754467754467755</v>
+        <v>0.7457386363636365</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E28" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F28">
-        <v>0.2321428571428572</v>
+        <v>0.625</v>
+      </c>
+      <c r="G28">
+        <v>0.01427255853272026</v>
       </c>
       <c r="H28">
-        <v>0.09386169386169387</v>
+        <v>0.7421875000000001</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>8</v>
       </c>
       <c r="K28">
-        <v>0.3754467754467755</v>
+        <v>0.9040178571428572</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F29">
-        <v>0.7321428571428571</v>
+        <v>0.515625</v>
+      </c>
+      <c r="G29">
+        <v>-0.0052395554723993</v>
       </c>
       <c r="H29">
-        <v>0.151981351981352</v>
+        <v>0.8437500000000001</v>
       </c>
       <c r="I29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>8</v>
       </c>
       <c r="K29">
-        <v>0.455944055944056</v>
+        <v>0.9040178571428572</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="s">
         <v>44</v>
@@ -2223,51 +2256,57 @@
         <v>44</v>
       </c>
       <c r="F30">
-        <v>0.3035714285714285</v>
+        <v>0.484375</v>
+      </c>
+      <c r="G30">
+        <v>-0.09822736654899855</v>
       </c>
       <c r="H30">
-        <v>0.2318570318570319</v>
+        <v>0.8437500000000001</v>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>8</v>
       </c>
       <c r="K30">
-        <v>0.5564568764568765</v>
+        <v>0.9040178571428572</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F31">
-        <v>0.3392857142857143</v>
+        <v>0.46875</v>
+      </c>
+      <c r="G31">
+        <v>0.02726510512914805</v>
       </c>
       <c r="H31">
-        <v>0.3356643356643357</v>
+        <v>0.9453124999999998</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J31">
         <v>8</v>
       </c>
       <c r="K31">
-        <v>0.5754245754245755</v>
+        <v>0.9453124999999998</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2281,16 +2320,16 @@
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F32">
-        <v>0.6607142857142857</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="H32">
-        <v>0.3356643356643357</v>
+        <v>0.002175602175602176</v>
       </c>
       <c r="I32">
         <v>7</v>
@@ -2299,7 +2338,7 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>0.5754245754245755</v>
+        <v>0.03263403263403263</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2313,16 +2352,16 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F33">
-        <v>0.4107142857142857</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="H33">
-        <v>0.6125874125874127</v>
+        <v>0.05407925407925408</v>
       </c>
       <c r="I33">
         <v>7</v>
@@ -2331,7 +2370,7 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>0.918881118881119</v>
+        <v>0.2703962703962704</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2345,16 +2384,16 @@
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F34">
-        <v>0.5357142857142857</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="H34">
-        <v>0.8665112665112666</v>
+        <v>0.05407925407925408</v>
       </c>
       <c r="I34">
         <v>7</v>
@@ -2363,7 +2402,7 @@
         <v>8</v>
       </c>
       <c r="K34">
-        <v>0.9550893550893552</v>
+        <v>0.2703962703962704</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2377,16 +2416,16 @@
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E35" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F35">
-        <v>0.5178571428571429</v>
+        <v>0.2321428571428572</v>
       </c>
       <c r="H35">
-        <v>0.9550893550893549</v>
+        <v>0.09386169386169387</v>
       </c>
       <c r="I35">
         <v>7</v>
@@ -2395,7 +2434,7 @@
         <v>8</v>
       </c>
       <c r="K35">
-        <v>0.9550893550893552</v>
+        <v>0.351981351981352</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2409,16 +2448,16 @@
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F36">
-        <v>0.4821428571428572</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="H36">
-        <v>0.9550893550893552</v>
+        <v>0.1892773892773893</v>
       </c>
       <c r="I36">
         <v>7</v>
@@ -2427,7 +2466,7 @@
         <v>8</v>
       </c>
       <c r="K36">
-        <v>0.9550893550893552</v>
+        <v>0.5678321678321678</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2441,16 +2480,16 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E37" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F37">
-        <v>0.4821428571428572</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="H37">
-        <v>0.9550893550893552</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="I37">
         <v>7</v>
@@ -2459,30 +2498,30 @@
         <v>8</v>
       </c>
       <c r="K37">
-        <v>0.9550893550893552</v>
+        <v>0.6614866614866616</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C38" t="b">
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F38">
-        <v>0.2857142857142857</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="H38">
-        <v>0.1892773892773893</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="I38">
         <v>7</v>
@@ -2491,30 +2530,30 @@
         <v>8</v>
       </c>
       <c r="K38">
-        <v>1</v>
+        <v>0.6614866614866616</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C39" t="b">
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E39" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F39">
-        <v>0.7142857142857143</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="H39">
-        <v>0.1892773892773893</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="I39">
         <v>7</v>
@@ -2523,30 +2562,30 @@
         <v>8</v>
       </c>
       <c r="K39">
-        <v>1</v>
+        <v>0.6614866614866616</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C40" t="b">
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E40" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F40">
-        <v>0.3214285714285715</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="H40">
-        <v>0.280963480963481</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="I40">
         <v>7</v>
@@ -2555,30 +2594,30 @@
         <v>8</v>
       </c>
       <c r="K40">
-        <v>1</v>
+        <v>0.6614866614866616</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C41" t="b">
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F41">
-        <v>0.6607142857142857</v>
+        <v>0.4107142857142857</v>
       </c>
       <c r="H41">
-        <v>0.3356643356643357</v>
+        <v>0.6125874125874127</v>
       </c>
       <c r="I41">
         <v>7</v>
@@ -2587,30 +2626,30 @@
         <v>8</v>
       </c>
       <c r="K41">
-        <v>1</v>
+        <v>0.8665112665112666</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C42" t="b">
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F42">
-        <v>0.625</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="H42">
-        <v>0.4634032634032634</v>
+        <v>0.7788655788655789</v>
       </c>
       <c r="I42">
         <v>7</v>
@@ -2619,15 +2658,15 @@
         <v>8</v>
       </c>
       <c r="K42">
-        <v>1</v>
+        <v>0.8665112665112666</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C43" t="b">
         <v>0</v>
@@ -2651,30 +2690,30 @@
         <v>8</v>
       </c>
       <c r="K43">
-        <v>1</v>
+        <v>0.8665112665112666</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C44" t="b">
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E44" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F44">
-        <v>0.5535714285714286</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="H44">
-        <v>0.7788655788655789</v>
+        <v>0.8665112665112666</v>
       </c>
       <c r="I44">
         <v>7</v>
@@ -2683,24 +2722,24 @@
         <v>8</v>
       </c>
       <c r="K44">
-        <v>1</v>
+        <v>0.8665112665112666</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C45" t="b">
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E45" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F45">
         <v>0.5357142857142857</v>
@@ -2715,27 +2754,27 @@
         <v>8</v>
       </c>
       <c r="K45">
-        <v>1</v>
+        <v>0.8665112665112666</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C46" t="b">
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E46" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F46">
-        <v>0.5357142857142857</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="H46">
         <v>0.8665112665112666</v>
@@ -2747,7 +2786,7 @@
         <v>8</v>
       </c>
       <c r="K46">
-        <v>1</v>
+        <v>0.8665112665112666</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2761,16 +2800,16 @@
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E47" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F47">
-        <v>0.5357142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="H47">
-        <v>0.8665112665112666</v>
+        <v>0.02051282051282051</v>
       </c>
       <c r="I47">
         <v>7</v>
@@ -2779,7 +2818,7 @@
         <v>8</v>
       </c>
       <c r="K47">
-        <v>1</v>
+        <v>0.3076923076923077</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2793,16 +2832,16 @@
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E48" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F48">
-        <v>0.5178571428571429</v>
+        <v>0.7321428571428571</v>
       </c>
       <c r="H48">
-        <v>0.9550893550893549</v>
+        <v>0.151981351981352</v>
       </c>
       <c r="I48">
         <v>7</v>
@@ -2811,7 +2850,7 @@
         <v>8</v>
       </c>
       <c r="K48">
-        <v>1</v>
+        <v>0.6951048951048951</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2825,16 +2864,16 @@
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E49" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F49">
-        <v>0.5</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0.1892773892773893</v>
       </c>
       <c r="I49">
         <v>7</v>
@@ -2843,30 +2882,30 @@
         <v>8</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>0.6951048951048951</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C50" t="b">
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E50" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F50">
-        <v>0.7678571428571429</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="H50">
-        <v>0.09386169386169387</v>
+        <v>0.1892773892773893</v>
       </c>
       <c r="I50">
         <v>7</v>
@@ -2875,30 +2914,30 @@
         <v>8</v>
       </c>
       <c r="K50">
-        <v>0.5564568764568765</v>
+        <v>0.6951048951048951</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C51" t="b">
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E51" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F51">
-        <v>0.7321428571428571</v>
+        <v>0.6964285714285714</v>
       </c>
       <c r="H51">
-        <v>0.151981351981352</v>
+        <v>0.2318570318570319</v>
       </c>
       <c r="I51">
         <v>7</v>
@@ -2907,30 +2946,30 @@
         <v>8</v>
       </c>
       <c r="K51">
-        <v>0.5564568764568765</v>
+        <v>0.6951048951048951</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C52" t="b">
         <v>0</v>
       </c>
       <c r="D52" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E52" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F52">
-        <v>0.7142857142857143</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="H52">
-        <v>0.1892773892773893</v>
+        <v>0.280963480963481</v>
       </c>
       <c r="I52">
         <v>7</v>
@@ -2939,30 +2978,30 @@
         <v>8</v>
       </c>
       <c r="K52">
-        <v>0.5564568764568765</v>
+        <v>0.6951048951048951</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C53" t="b">
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E53" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F53">
-        <v>0.6964285714285714</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="H53">
-        <v>0.2318570318570319</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="I53">
         <v>7</v>
@@ -2971,30 +3010,30 @@
         <v>8</v>
       </c>
       <c r="K53">
-        <v>0.5564568764568765</v>
+        <v>0.6951048951048951</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C54" t="b">
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E54" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F54">
-        <v>0.3035714285714285</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="H54">
-        <v>0.2318570318570319</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="I54">
         <v>7</v>
@@ -3003,30 +3042,30 @@
         <v>8</v>
       </c>
       <c r="K54">
-        <v>0.5564568764568765</v>
+        <v>0.6951048951048951</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C55" t="b">
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E55" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F55">
-        <v>0.3571428571428572</v>
+        <v>0.375</v>
       </c>
       <c r="H55">
-        <v>0.3968919968919969</v>
+        <v>0.4634032634032634</v>
       </c>
       <c r="I55">
         <v>7</v>
@@ -3035,27 +3074,27 @@
         <v>8</v>
       </c>
       <c r="K55">
-        <v>0.7574486119940665</v>
+        <v>0.6951048951048951</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C56" t="b">
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E56" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F56">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="H56">
         <v>0.4634032634032634</v>
@@ -3067,30 +3106,30 @@
         <v>8</v>
       </c>
       <c r="K56">
-        <v>0.7574486119940665</v>
+        <v>0.6951048951048951</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C57" t="b">
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E57" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F57">
-        <v>0.6071428571428571</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="H57">
-        <v>0.5358197358197359</v>
+        <v>0.7788655788655789</v>
       </c>
       <c r="I57">
         <v>7</v>
@@ -3099,30 +3138,30 @@
         <v>8</v>
       </c>
       <c r="K57">
-        <v>0.7574486119940665</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C58" t="b">
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E58" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F58">
-        <v>0.4107142857142857</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="H58">
-        <v>0.6125874125874127</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="I58">
         <v>7</v>
@@ -3131,15 +3170,15 @@
         <v>8</v>
       </c>
       <c r="K58">
-        <v>0.7574486119940665</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C59" t="b">
         <v>0</v>
@@ -3151,10 +3190,10 @@
         <v>44</v>
       </c>
       <c r="F59">
-        <v>0.4285714285714285</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="H59">
-        <v>0.6943278943278944</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="I59">
         <v>7</v>
@@ -3163,30 +3202,30 @@
         <v>8</v>
       </c>
       <c r="K59">
-        <v>0.7574486119940665</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C60" t="b">
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E60" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F60">
-        <v>0.4285714285714285</v>
+        <v>0.4821428571428572</v>
       </c>
       <c r="H60">
-        <v>0.6943278943278944</v>
+        <v>0.9550893550893552</v>
       </c>
       <c r="I60">
         <v>7</v>
@@ -3195,30 +3234,30 @@
         <v>8</v>
       </c>
       <c r="K60">
-        <v>0.7574486119940665</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C61" t="b">
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E61" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F61">
-        <v>0.4464285714285715</v>
+        <v>0.5</v>
       </c>
       <c r="H61">
-        <v>0.7788655788655789</v>
+        <v>1</v>
       </c>
       <c r="I61">
         <v>7</v>
@@ -3227,645 +3266,600 @@
         <v>8</v>
       </c>
       <c r="K61">
-        <v>0.7788655788655789</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E62" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F62">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="G62">
-        <v>0.1384275194285308</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="H62">
-        <v>0.03125000000000001</v>
+        <v>0.07210567210567211</v>
       </c>
       <c r="I62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K62">
-        <v>0.3750000000000002</v>
+        <v>0.7097902097902099</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E63" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F63">
-        <v>0.3055555555555556</v>
-      </c>
-      <c r="G63">
-        <v>-0.1662400707044667</v>
+        <v>0.75</v>
       </c>
       <c r="H63">
-        <v>0.2187500000000001</v>
+        <v>0.1205905205905206</v>
       </c>
       <c r="I63">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J63">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K63">
-        <v>0.7500000000000002</v>
+        <v>0.7097902097902099</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B64" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E64" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F64">
-        <v>0.6944444444444444</v>
-      </c>
-      <c r="G64">
-        <v>0.1628646741748922</v>
+        <v>0.2678571428571428</v>
       </c>
       <c r="H64">
-        <v>0.3125000000000001</v>
+        <v>0.151981351981352</v>
       </c>
       <c r="I64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J64">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K64">
-        <v>0.7500000000000002</v>
+        <v>0.7097902097902099</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B65" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E65" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F65">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="G65">
-        <v>0.07297757615446195</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H65">
-        <v>0.3125000000000001</v>
+        <v>0.1892773892773893</v>
       </c>
       <c r="I65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J65">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K65">
-        <v>0.7500000000000002</v>
+        <v>0.7097902097902099</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E66" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F66">
-        <v>0.1388888888888889</v>
-      </c>
-      <c r="G66">
-        <v>-0.09370705661765776</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="H66">
-        <v>0.3125000000000001</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="I66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J66">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K66">
-        <v>0.7500000000000002</v>
+        <v>0.7441724941724943</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B67" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E67" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F67">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="G67">
-        <v>0.1067694139055617</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="H67">
-        <v>0.4375000000000002</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="I67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J67">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K67">
-        <v>0.8250000000000003</v>
+        <v>0.7441724941724943</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B68" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E68" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F68">
-        <v>0.5277777777777778</v>
-      </c>
-      <c r="G68">
-        <v>0.0002056416777262635</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="H68">
-        <v>0.6875000000000002</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="I68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K68">
-        <v>0.8250000000000003</v>
+        <v>0.7441724941724943</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B69" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E69" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F69">
-        <v>0.5</v>
-      </c>
-      <c r="G69">
-        <v>0.009589036559340982</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="H69">
-        <v>0.6875000000000002</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J69">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K69">
-        <v>0.8250000000000003</v>
+        <v>0.7441724941724943</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E70" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F70">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="G70">
-        <v>-0.02782291446224044</v>
+        <v>0.375</v>
       </c>
       <c r="H70">
-        <v>0.6875000000000002</v>
+        <v>0.4634032634032634</v>
       </c>
       <c r="I70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J70">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K70">
-        <v>0.8250000000000003</v>
+        <v>0.7723387723387725</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E71" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F71">
-        <v>0.5277777777777778</v>
-      </c>
-      <c r="G71">
-        <v>-0.04993243790865892</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="H71">
-        <v>0.6875000000000002</v>
+        <v>0.6943278943278944</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J71">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K71">
-        <v>0.8250000000000003</v>
+        <v>0.867909867909868</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B72" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E72" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F72">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="G72">
-        <v>-0.008934337881931154</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="H72">
-        <v>0.8437500000000003</v>
+        <v>0.6943278943278944</v>
       </c>
       <c r="I72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J72">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K72">
-        <v>0.9204545454545457</v>
+        <v>0.867909867909868</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B73" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E73" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F73">
-        <v>0.4722222222222222</v>
-      </c>
-      <c r="G73">
-        <v>0.01631727109033811</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>0.6943278943278944</v>
       </c>
       <c r="I73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J73">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K73">
-        <v>1</v>
+        <v>0.867909867909868</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E74" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F74">
-        <v>0.6875</v>
-      </c>
-      <c r="G74">
-        <v>0.07878230773470925</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="H74">
-        <v>0.1484375</v>
+        <v>0.8665112665112666</v>
       </c>
       <c r="I74">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J74">
         <v>8</v>
       </c>
       <c r="K74">
-        <v>0.9204545454545455</v>
+        <v>0.9284049284049285</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E75" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F75">
-        <v>0.515625</v>
-      </c>
-      <c r="G75">
-        <v>0.05447923023902303</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="H75">
-        <v>0.3125000000000001</v>
+        <v>0.8665112665112666</v>
       </c>
       <c r="I75">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J75">
         <v>8</v>
       </c>
       <c r="K75">
-        <v>0.9204545454545455</v>
+        <v>0.9284049284049285</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E76" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F76">
-        <v>0.421875</v>
-      </c>
-      <c r="G76">
-        <v>-0.02789600499136297</v>
+        <v>0.4821428571428572</v>
       </c>
       <c r="H76">
-        <v>0.5468750000000001</v>
+        <v>0.9550893550893552</v>
       </c>
       <c r="I76">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J76">
         <v>8</v>
       </c>
       <c r="K76">
-        <v>0.9204545454545455</v>
+        <v>0.9550893550893552</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C77" t="b">
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E77" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F77">
-        <v>0.578125</v>
+        <v>0.8611111111111112</v>
       </c>
       <c r="G77">
-        <v>0.04422644198548616</v>
+        <v>0.1726841728124711</v>
       </c>
       <c r="H77">
-        <v>0.6406250000000001</v>
+        <v>0.06250000000000003</v>
       </c>
       <c r="I77">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J77">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K77">
-        <v>0.9204545454545455</v>
+        <v>0.7812500000000002</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C78" t="b">
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E78" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F78">
-        <v>0.40625</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G78">
-        <v>-0.03543688739499322</v>
+        <v>0.1066412365018345</v>
       </c>
       <c r="H78">
-        <v>0.6406250000000001</v>
+        <v>0.1562500000000001</v>
       </c>
       <c r="I78">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J78">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K78">
-        <v>0.9204545454545455</v>
+        <v>0.7812500000000002</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C79" t="b">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E79" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F79">
-        <v>0.46875</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G79">
-        <v>-0.003195862030299691</v>
+        <v>-0.1451396763010954</v>
       </c>
       <c r="H79">
-        <v>0.7421875000000001</v>
+        <v>0.1562500000000001</v>
       </c>
       <c r="I79">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J79">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K79">
-        <v>0.9204545454545455</v>
+        <v>0.7812500000000002</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C80" t="b">
         <v>1</v>
@@ -3877,170 +3871,170 @@
         <v>50</v>
       </c>
       <c r="F80">
-        <v>0.515625</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="G80">
-        <v>0.0360042241549882</v>
+        <v>0.1813157859027815</v>
       </c>
       <c r="H80">
-        <v>0.7421875000000001</v>
+        <v>0.3125000000000001</v>
       </c>
       <c r="I80">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J80">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K80">
-        <v>0.9204545454545455</v>
+        <v>0.7812500000000002</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C81" t="b">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E81" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F81">
-        <v>0.5</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="G81">
-        <v>0.03186942965319577</v>
+        <v>-0.06229167852528958</v>
       </c>
       <c r="H81">
-        <v>0.8437500000000001</v>
+        <v>0.3125000000000001</v>
       </c>
       <c r="I81">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J81">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K81">
-        <v>0.9204545454545455</v>
+        <v>0.7812500000000002</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C82" t="b">
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E82" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F82">
-        <v>0.4375</v>
+        <v>0.1944444444444444</v>
       </c>
       <c r="G82">
-        <v>0.001004733917143293</v>
+        <v>-0.1076335027443761</v>
       </c>
       <c r="H82">
-        <v>0.8437500000000001</v>
+        <v>0.3125000000000001</v>
       </c>
       <c r="I82">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J82">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K82">
-        <v>0.9204545454545455</v>
+        <v>0.7812500000000002</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C83" t="b">
         <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E83" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F83">
-        <v>0.390625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G83">
-        <v>-0.09841498059891063</v>
+        <v>0.1326734954674455</v>
       </c>
       <c r="H83">
-        <v>0.8437500000000001</v>
+        <v>0.4375000000000002</v>
       </c>
       <c r="I83">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J83">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K83">
-        <v>0.9204545454545455</v>
+        <v>0.8437500000000003</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C84" t="b">
         <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E84" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F84">
-        <v>0.46875</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="G84">
-        <v>0.008241925585471828</v>
+        <v>0.01776047608298494</v>
       </c>
       <c r="H84">
-        <v>0.8437500000000001</v>
+        <v>0.5625000000000002</v>
       </c>
       <c r="I84">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J84">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K84">
-        <v>0.9204545454545455</v>
+        <v>0.8437500000000003</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C85" t="b">
         <v>1</v>
@@ -4052,129 +4046,138 @@
         <v>49</v>
       </c>
       <c r="F85">
-        <v>0.625</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="G85">
-        <v>0.03953026798133572</v>
+        <v>0.1221424491899613</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>0.5625000000000002</v>
       </c>
       <c r="I85">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J85">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K85">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E86" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F86">
-        <v>0.7291666666666666</v>
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="G86">
+        <v>0.08681461636921775</v>
       </c>
       <c r="H86">
-        <v>0.1811521811521812</v>
+        <v>0.6875000000000002</v>
       </c>
       <c r="I86">
         <v>6</v>
       </c>
       <c r="J86">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K86">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E87" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F87">
-        <v>0.6666666666666666</v>
+        <v>0.4722222222222222</v>
+      </c>
+      <c r="G87">
+        <v>-0.05147354144125908</v>
       </c>
       <c r="H87">
-        <v>0.344988344988345</v>
+        <v>0.6875000000000002</v>
       </c>
       <c r="I87">
         <v>6</v>
       </c>
       <c r="J87">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K87">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E88" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F88">
-        <v>0.3333333333333333</v>
+        <v>0.5277777777777778</v>
+      </c>
+      <c r="G88">
+        <v>-0.04559408890641857</v>
       </c>
       <c r="H88">
-        <v>0.344988344988345</v>
+        <v>0.8437500000000003</v>
       </c>
       <c r="I88">
         <v>6</v>
       </c>
       <c r="J88">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K88">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B89" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" t="s">
         <v>48</v>
@@ -4183,274 +4186,1096 @@
         <v>48</v>
       </c>
       <c r="F89">
-        <v>0.3541666666666667</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G89">
+        <v>0.04772559282893921</v>
       </c>
       <c r="H89">
-        <v>0.4135864135864136</v>
+        <v>0.8437500000000003</v>
       </c>
       <c r="I89">
         <v>6</v>
       </c>
       <c r="J89">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K89">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E90" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F90">
-        <v>0.625</v>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G90">
+        <v>-0.04915417246721927</v>
       </c>
       <c r="H90">
-        <v>0.4908424908424909</v>
+        <v>0.8437500000000003</v>
       </c>
       <c r="I90">
         <v>6</v>
       </c>
       <c r="J90">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K90">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F91">
-        <v>0.6041666666666666</v>
+        <v>0.5</v>
+      </c>
+      <c r="G91">
+        <v>-0.002860536960869783</v>
       </c>
       <c r="H91">
-        <v>0.5727605727605728</v>
+        <v>0.8437500000000003</v>
       </c>
       <c r="I91">
         <v>6</v>
       </c>
       <c r="J91">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K91">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B92" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E92" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F92">
-        <v>0.4375</v>
+        <v>0.734375</v>
+      </c>
+      <c r="G92">
+        <v>0.06099995628669049</v>
       </c>
       <c r="H92">
-        <v>0.7545787545787546</v>
+        <v>0.07812500000000001</v>
       </c>
       <c r="I92">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J92">
         <v>8</v>
       </c>
       <c r="K92">
-        <v>1</v>
+        <v>0.8735795454545455</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E93" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F93">
-        <v>0.4583333333333333</v>
+        <v>0.609375</v>
+      </c>
+      <c r="G93">
+        <v>0.08853865778819013</v>
       </c>
       <c r="H93">
-        <v>0.8518148518148518</v>
+        <v>0.1953125</v>
       </c>
       <c r="I93">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J93">
         <v>8</v>
       </c>
       <c r="K93">
-        <v>1</v>
+        <v>0.8735795454545455</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E94" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F94">
-        <v>0.5416666666666666</v>
+        <v>0.65625</v>
+      </c>
+      <c r="G94">
+        <v>0.03478632577803124</v>
       </c>
       <c r="H94">
-        <v>0.8518148518148518</v>
+        <v>0.2500000000000001</v>
       </c>
       <c r="I94">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J94">
         <v>8</v>
       </c>
       <c r="K94">
-        <v>1</v>
+        <v>0.8735795454545455</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E95" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F95">
-        <v>0.4791666666666667</v>
+        <v>0.59375</v>
+      </c>
+      <c r="G95">
+        <v>0.04024573245569871</v>
       </c>
       <c r="H95">
-        <v>0.9497169497169498</v>
+        <v>0.3125000000000001</v>
       </c>
       <c r="I95">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J95">
         <v>8</v>
       </c>
       <c r="K95">
-        <v>1</v>
+        <v>0.8735795454545455</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E96" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F96">
-        <v>0.5</v>
+        <v>0.390625</v>
+      </c>
+      <c r="G96">
+        <v>-0.03318643260852032</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>0.4609375000000001</v>
       </c>
       <c r="I96">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J96">
         <v>8</v>
       </c>
       <c r="K96">
-        <v>1</v>
+        <v>0.8735795454545455</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
+        <v>23</v>
+      </c>
+      <c r="B97" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" t="b">
+        <v>1</v>
+      </c>
+      <c r="D97" t="s">
+        <v>47</v>
+      </c>
+      <c r="E97" t="s">
+        <v>47</v>
+      </c>
+      <c r="F97">
+        <v>0.390625</v>
+      </c>
+      <c r="G97">
+        <v>-0.03802187304407005</v>
+      </c>
+      <c r="H97">
+        <v>0.5468750000000001</v>
+      </c>
+      <c r="I97">
+        <v>8</v>
+      </c>
+      <c r="J97">
+        <v>8</v>
+      </c>
+      <c r="K97">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" t="s">
+        <v>23</v>
+      </c>
+      <c r="B98" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" t="b">
+        <v>1</v>
+      </c>
+      <c r="D98" t="s">
+        <v>53</v>
+      </c>
+      <c r="E98" t="s">
+        <v>53</v>
+      </c>
+      <c r="F98">
+        <v>0.4375</v>
+      </c>
+      <c r="G98">
+        <v>-0.01661325647678491</v>
+      </c>
+      <c r="H98">
+        <v>0.6406250000000001</v>
+      </c>
+      <c r="I98">
+        <v>8</v>
+      </c>
+      <c r="J98">
+        <v>8</v>
+      </c>
+      <c r="K98">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" t="s">
+        <v>23</v>
+      </c>
+      <c r="B99" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" t="b">
+        <v>1</v>
+      </c>
+      <c r="D99" t="s">
+        <v>54</v>
+      </c>
+      <c r="E99" t="s">
+        <v>54</v>
+      </c>
+      <c r="F99">
+        <v>0.421875</v>
+      </c>
+      <c r="G99">
+        <v>-0.02619076159136435</v>
+      </c>
+      <c r="H99">
+        <v>0.6406250000000001</v>
+      </c>
+      <c r="I99">
+        <v>8</v>
+      </c>
+      <c r="J99">
+        <v>8</v>
+      </c>
+      <c r="K99">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" t="s">
+        <v>23</v>
+      </c>
+      <c r="B100" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" t="b">
+        <v>1</v>
+      </c>
+      <c r="D100" t="s">
+        <v>45</v>
+      </c>
+      <c r="E100" t="s">
+        <v>45</v>
+      </c>
+      <c r="F100">
+        <v>0.34375</v>
+      </c>
+      <c r="G100">
+        <v>-0.1124340209448966</v>
+      </c>
+      <c r="H100">
+        <v>0.6406250000000001</v>
+      </c>
+      <c r="I100">
+        <v>8</v>
+      </c>
+      <c r="J100">
+        <v>8</v>
+      </c>
+      <c r="K100">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" t="b">
+        <v>1</v>
+      </c>
+      <c r="D101" t="s">
+        <v>49</v>
+      </c>
+      <c r="E101" t="s">
+        <v>49</v>
+      </c>
+      <c r="F101">
+        <v>0.65625</v>
+      </c>
+      <c r="G101">
+        <v>0.09049223067312329</v>
+      </c>
+      <c r="H101">
+        <v>0.6406250000000001</v>
+      </c>
+      <c r="I101">
+        <v>8</v>
+      </c>
+      <c r="J101">
+        <v>8</v>
+      </c>
+      <c r="K101">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" t="s">
+        <v>23</v>
+      </c>
+      <c r="B102" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102" t="b">
+        <v>1</v>
+      </c>
+      <c r="D102" t="s">
+        <v>56</v>
+      </c>
+      <c r="E102" t="s">
+        <v>56</v>
+      </c>
+      <c r="F102">
+        <v>0.625</v>
+      </c>
+      <c r="G102">
+        <v>0.007953079027062937</v>
+      </c>
+      <c r="H102">
+        <v>0.6406250000000001</v>
+      </c>
+      <c r="I102">
+        <v>8</v>
+      </c>
+      <c r="J102">
+        <v>8</v>
+      </c>
+      <c r="K102">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" t="s">
+        <v>23</v>
+      </c>
+      <c r="B103" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" t="b">
+        <v>1</v>
+      </c>
+      <c r="D103" t="s">
+        <v>46</v>
+      </c>
+      <c r="E103" t="s">
+        <v>46</v>
+      </c>
+      <c r="F103">
+        <v>0.578125</v>
+      </c>
+      <c r="G103">
+        <v>0.04476056869555671</v>
+      </c>
+      <c r="H103">
+        <v>0.7421875000000001</v>
+      </c>
+      <c r="I103">
+        <v>8</v>
+      </c>
+      <c r="J103">
+        <v>8</v>
+      </c>
+      <c r="K103">
+        <v>0.9040178571428572</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" t="s">
+        <v>23</v>
+      </c>
+      <c r="B104" t="s">
+        <v>24</v>
+      </c>
+      <c r="C104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D104" t="s">
+        <v>48</v>
+      </c>
+      <c r="E104" t="s">
+        <v>48</v>
+      </c>
+      <c r="F104">
+        <v>0.515625</v>
+      </c>
+      <c r="G104">
+        <v>-0.01729494621730936</v>
+      </c>
+      <c r="H104">
+        <v>0.8437500000000001</v>
+      </c>
+      <c r="I104">
+        <v>8</v>
+      </c>
+      <c r="J104">
+        <v>8</v>
+      </c>
+      <c r="K104">
+        <v>0.9040178571428572</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" t="s">
+        <v>23</v>
+      </c>
+      <c r="B105" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105" t="b">
+        <v>1</v>
+      </c>
+      <c r="D105" t="s">
+        <v>43</v>
+      </c>
+      <c r="E105" t="s">
+        <v>43</v>
+      </c>
+      <c r="F105">
+        <v>0.453125</v>
+      </c>
+      <c r="G105">
+        <v>-0.01027380439512042</v>
+      </c>
+      <c r="H105">
+        <v>0.8437500000000001</v>
+      </c>
+      <c r="I105">
+        <v>8</v>
+      </c>
+      <c r="J105">
+        <v>8</v>
+      </c>
+      <c r="K105">
+        <v>0.9040178571428572</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" t="s">
+        <v>23</v>
+      </c>
+      <c r="B106" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" t="b">
+        <v>1</v>
+      </c>
+      <c r="D106" t="s">
+        <v>55</v>
+      </c>
+      <c r="E106" t="s">
+        <v>55</v>
+      </c>
+      <c r="F106">
+        <v>0.453125</v>
+      </c>
+      <c r="G106">
+        <v>5.638777027187902E-05</v>
+      </c>
+      <c r="H106">
+        <v>0.9453124999999998</v>
+      </c>
+      <c r="I106">
+        <v>8</v>
+      </c>
+      <c r="J106">
+        <v>8</v>
+      </c>
+      <c r="K106">
+        <v>0.9453124999999998</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" t="s">
         <v>33</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B107" t="s">
         <v>34</v>
       </c>
-      <c r="C97" t="b">
-        <v>0</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="C107" t="b">
+        <v>0</v>
+      </c>
+      <c r="D107" t="s">
+        <v>55</v>
+      </c>
+      <c r="E107" t="s">
+        <v>55</v>
+      </c>
+      <c r="F107">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H107">
+        <v>0.04262404262404262</v>
+      </c>
+      <c r="I107">
+        <v>6</v>
+      </c>
+      <c r="J107">
+        <v>8</v>
+      </c>
+      <c r="K107">
+        <v>0.6393606393606394</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" t="s">
+        <v>33</v>
+      </c>
+      <c r="B108" t="s">
+        <v>34</v>
+      </c>
+      <c r="C108" t="b">
+        <v>0</v>
+      </c>
+      <c r="D108" t="s">
+        <v>42</v>
+      </c>
+      <c r="E108" t="s">
+        <v>42</v>
+      </c>
+      <c r="F108">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="H108">
+        <v>0.2284382284382285</v>
+      </c>
+      <c r="I108">
+        <v>6</v>
+      </c>
+      <c r="J108">
+        <v>8</v>
+      </c>
+      <c r="K108">
+        <v>0.8471528471528473</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" t="s">
+        <v>33</v>
+      </c>
+      <c r="B109" t="s">
+        <v>34</v>
+      </c>
+      <c r="C109" t="b">
+        <v>0</v>
+      </c>
+      <c r="D109" t="s">
+        <v>53</v>
+      </c>
+      <c r="E109" t="s">
+        <v>53</v>
+      </c>
+      <c r="F109">
+        <v>0.6875</v>
+      </c>
+      <c r="H109">
+        <v>0.2823842823842824</v>
+      </c>
+      <c r="I109">
+        <v>6</v>
+      </c>
+      <c r="J109">
+        <v>8</v>
+      </c>
+      <c r="K109">
+        <v>0.8471528471528473</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" t="s">
+        <v>33</v>
+      </c>
+      <c r="B110" t="s">
+        <v>34</v>
+      </c>
+      <c r="C110" t="b">
+        <v>0</v>
+      </c>
+      <c r="D110" t="s">
+        <v>51</v>
+      </c>
+      <c r="E110" t="s">
+        <v>51</v>
+      </c>
+      <c r="F110">
+        <v>0.3125</v>
+      </c>
+      <c r="H110">
+        <v>0.2823842823842824</v>
+      </c>
+      <c r="I110">
+        <v>6</v>
+      </c>
+      <c r="J110">
+        <v>8</v>
+      </c>
+      <c r="K110">
+        <v>0.8471528471528473</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" t="s">
+        <v>33</v>
+      </c>
+      <c r="B111" t="s">
+        <v>34</v>
+      </c>
+      <c r="C111" t="b">
+        <v>0</v>
+      </c>
+      <c r="D111" t="s">
+        <v>56</v>
+      </c>
+      <c r="E111" t="s">
+        <v>56</v>
+      </c>
+      <c r="F111">
+        <v>0.3125</v>
+      </c>
+      <c r="H111">
+        <v>0.2823842823842824</v>
+      </c>
+      <c r="I111">
+        <v>6</v>
+      </c>
+      <c r="J111">
+        <v>8</v>
+      </c>
+      <c r="K111">
+        <v>0.8471528471528473</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" t="s">
+        <v>33</v>
+      </c>
+      <c r="B112" t="s">
+        <v>34</v>
+      </c>
+      <c r="C112" t="b">
+        <v>0</v>
+      </c>
+      <c r="D112" t="s">
+        <v>50</v>
+      </c>
+      <c r="E112" t="s">
+        <v>50</v>
+      </c>
+      <c r="F112">
+        <v>0.625</v>
+      </c>
+      <c r="H112">
+        <v>0.4908424908424909</v>
+      </c>
+      <c r="I112">
+        <v>6</v>
+      </c>
+      <c r="J112">
+        <v>8</v>
+      </c>
+      <c r="K112">
+        <v>0.9546009546009547</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" t="s">
+        <v>33</v>
+      </c>
+      <c r="B113" t="s">
+        <v>34</v>
+      </c>
+      <c r="C113" t="b">
+        <v>0</v>
+      </c>
+      <c r="D113" t="s">
+        <v>47</v>
+      </c>
+      <c r="E113" t="s">
+        <v>47</v>
+      </c>
+      <c r="F113">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="H113">
+        <v>0.5727605727605728</v>
+      </c>
+      <c r="I113">
+        <v>6</v>
+      </c>
+      <c r="J113">
+        <v>8</v>
+      </c>
+      <c r="K113">
+        <v>0.9546009546009547</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114" t="s">
+        <v>33</v>
+      </c>
+      <c r="B114" t="s">
+        <v>34</v>
+      </c>
+      <c r="C114" t="b">
+        <v>0</v>
+      </c>
+      <c r="D114" t="s">
+        <v>49</v>
+      </c>
+      <c r="E114" t="s">
+        <v>49</v>
+      </c>
+      <c r="F114">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="H114">
+        <v>0.5727605727605728</v>
+      </c>
+      <c r="I114">
+        <v>6</v>
+      </c>
+      <c r="J114">
+        <v>8</v>
+      </c>
+      <c r="K114">
+        <v>0.9546009546009547</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115" t="s">
+        <v>33</v>
+      </c>
+      <c r="B115" t="s">
+        <v>34</v>
+      </c>
+      <c r="C115" t="b">
+        <v>0</v>
+      </c>
+      <c r="D115" t="s">
+        <v>44</v>
+      </c>
+      <c r="E115" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="H115">
+        <v>0.5727605727605728</v>
+      </c>
+      <c r="I115">
+        <v>6</v>
+      </c>
+      <c r="J115">
+        <v>8</v>
+      </c>
+      <c r="K115">
+        <v>0.9546009546009547</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116" t="s">
+        <v>33</v>
+      </c>
+      <c r="B116" t="s">
+        <v>34</v>
+      </c>
+      <c r="C116" t="b">
+        <v>0</v>
+      </c>
+      <c r="D116" t="s">
+        <v>52</v>
+      </c>
+      <c r="E116" t="s">
+        <v>52</v>
+      </c>
+      <c r="F116">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H116">
+        <v>0.662004662004662</v>
+      </c>
+      <c r="I116">
+        <v>6</v>
+      </c>
+      <c r="J116">
+        <v>8</v>
+      </c>
+      <c r="K116">
+        <v>0.993006993006993</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117" t="s">
+        <v>33</v>
+      </c>
+      <c r="B117" t="s">
+        <v>34</v>
+      </c>
+      <c r="C117" t="b">
+        <v>0</v>
+      </c>
+      <c r="D117" t="s">
+        <v>48</v>
+      </c>
+      <c r="E117" t="s">
+        <v>48</v>
+      </c>
+      <c r="F117">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H117">
+        <v>0.8518148518148518</v>
+      </c>
+      <c r="I117">
+        <v>6</v>
+      </c>
+      <c r="J117">
+        <v>8</v>
+      </c>
+      <c r="K117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" t="s">
+        <v>33</v>
+      </c>
+      <c r="B118" t="s">
+        <v>34</v>
+      </c>
+      <c r="C118" t="b">
+        <v>0</v>
+      </c>
+      <c r="D118" t="s">
+        <v>43</v>
+      </c>
+      <c r="E118" t="s">
+        <v>43</v>
+      </c>
+      <c r="F118">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H118">
+        <v>0.8518148518148518</v>
+      </c>
+      <c r="I118">
+        <v>6</v>
+      </c>
+      <c r="J118">
+        <v>8</v>
+      </c>
+      <c r="K118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" t="s">
+        <v>33</v>
+      </c>
+      <c r="B119" t="s">
+        <v>34</v>
+      </c>
+      <c r="C119" t="b">
+        <v>0</v>
+      </c>
+      <c r="D119" t="s">
+        <v>46</v>
+      </c>
+      <c r="E119" t="s">
+        <v>46</v>
+      </c>
+      <c r="F119">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="H119">
+        <v>0.9497169497169498</v>
+      </c>
+      <c r="I119">
+        <v>6</v>
+      </c>
+      <c r="J119">
+        <v>8</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" t="s">
+        <v>33</v>
+      </c>
+      <c r="B120" t="s">
+        <v>34</v>
+      </c>
+      <c r="C120" t="b">
+        <v>0</v>
+      </c>
+      <c r="D120" t="s">
+        <v>54</v>
+      </c>
+      <c r="E120" t="s">
+        <v>54</v>
+      </c>
+      <c r="F120">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="H120">
+        <v>0.9497169497169498</v>
+      </c>
+      <c r="I120">
+        <v>6</v>
+      </c>
+      <c r="J120">
+        <v>8</v>
+      </c>
+      <c r="K120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" t="s">
+        <v>33</v>
+      </c>
+      <c r="B121" t="s">
+        <v>34</v>
+      </c>
+      <c r="C121" t="b">
+        <v>0</v>
+      </c>
+      <c r="D121" t="s">
         <v>45</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E121" t="s">
         <v>45</v>
       </c>
-      <c r="F97">
+      <c r="F121">
         <v>0.5</v>
       </c>
-      <c r="H97">
-        <v>1</v>
-      </c>
-      <c r="I97">
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="I121">
         <v>6</v>
       </c>
-      <c r="J97">
-        <v>8</v>
-      </c>
-      <c r="K97">
+      <c r="J121">
+        <v>8</v>
+      </c>
+      <c r="K121">
         <v>1</v>
       </c>
     </row>
@@ -4461,7 +5286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
@@ -4472,21 +5297,21 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -4494,16 +5319,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -4514,16 +5339,16 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4531,16 +5356,16 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5">
         <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4548,13 +5373,13 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -4565,13 +5390,13 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -4585,13 +5410,115 @@
         <v>51</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
         <v>51</v>
       </c>
       <c r="E8">
         <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4606,24 +5533,24 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4633,466 +5560,466 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" t="s">
         <v>75</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B29" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B36" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B37" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B38" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C38" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B39" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C40" t="s">
-        <v>69</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B41" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C42" t="s">
         <v>72</v>
@@ -5100,112 +6027,134 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B43" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B44" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B45" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C45" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B46" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B47" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C47" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B48" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B50" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C50" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B51" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B52" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C52" t="s">
-        <v>142</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>173</v>
+      </c>
+      <c r="B53" t="s">
+        <v>174</v>
+      </c>
+      <c r="C53" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>175</v>
+      </c>
+      <c r="B54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C54" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/04_Network/03_Classify/c_data/03_classify.xlsx
+++ b/04_Network/03_Classify/c_data/03_classify.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="179">
   <si>
     <t>sheet</t>
   </si>
@@ -136,6 +136,12 @@
   </si>
   <si>
     <t>label</t>
+  </si>
+  <si>
+    <t>auc_lower</t>
+  </si>
+  <si>
+    <t>auc_upper</t>
   </si>
   <si>
     <t>median_change</t>
@@ -1221,10 +1227,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:13" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -1250,16 +1256,22 @@
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="M1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1270,31 +1282,31 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F2">
         <v>0.163265306122449</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>-0.1895446333247326</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>0.015625</v>
       </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
       <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>7</v>
+      </c>
+      <c r="M2">
         <v>0.2343750000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1305,31 +1317,31 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F3">
         <v>0.9183673469387755</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>0.2017200455808207</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>0.04687500000000001</v>
       </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
       <c r="K3">
+        <v>7</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
         <v>0.2343750000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1340,31 +1352,31 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F4">
         <v>0.6122448979591837</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>0.04052501671806824</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>0.04687500000000001</v>
       </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>7</v>
-      </c>
       <c r="K4">
+        <v>7</v>
+      </c>
+      <c r="L4">
+        <v>7</v>
+      </c>
+      <c r="M4">
         <v>0.2343750000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1375,31 +1387,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F5">
         <v>0.7755102040816326</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>0.12256369925543</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>0.109375</v>
       </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>7</v>
-      </c>
       <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
         <v>0.4101562500000001</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1410,31 +1422,31 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F6">
         <v>0.2448979591836735</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>-0.1596588599641741</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>0.2187500000000001</v>
       </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
       <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
         <v>0.4687500000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1445,31 +1457,31 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F7">
         <v>0.6530612244897959</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>0.1692604200258208</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>0.2187500000000001</v>
       </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>7</v>
-      </c>
       <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
         <v>0.4687500000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1480,31 +1492,31 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F8">
         <v>0.2040816326530612</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>-0.07909445693915869</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>0.2187500000000001</v>
       </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
       <c r="K8">
+        <v>7</v>
+      </c>
+      <c r="L8">
+        <v>7</v>
+      </c>
+      <c r="M8">
         <v>0.4687500000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1515,31 +1527,31 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F9">
         <v>0.2448979591836735</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>-0.04210645234594217</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>0.2968750000000001</v>
       </c>
-      <c r="I9">
-        <v>7</v>
-      </c>
-      <c r="J9">
-        <v>7</v>
-      </c>
       <c r="K9">
+        <v>7</v>
+      </c>
+      <c r="L9">
+        <v>7</v>
+      </c>
+      <c r="M9">
         <v>0.5566406250000001</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1550,31 +1562,31 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F10">
         <v>0.6938775510204082</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>0.05695789805693754</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>0.5781250000000001</v>
       </c>
-      <c r="I10">
-        <v>7</v>
-      </c>
-      <c r="J10">
-        <v>7</v>
-      </c>
       <c r="K10">
+        <v>7</v>
+      </c>
+      <c r="L10">
+        <v>7</v>
+      </c>
+      <c r="M10">
         <v>0.7883522727272728</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1585,31 +1597,31 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F11">
         <v>0.6326530612244898</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>-0.07482199314333263</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>0.5781250000000001</v>
       </c>
-      <c r="I11">
-        <v>7</v>
-      </c>
-      <c r="J11">
-        <v>7</v>
-      </c>
       <c r="K11">
+        <v>7</v>
+      </c>
+      <c r="L11">
+        <v>7</v>
+      </c>
+      <c r="M11">
         <v>0.7883522727272728</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1620,31 +1632,31 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F12">
         <v>0.4489795918367347</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>-0.08432245695934777</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>0.5781250000000001</v>
       </c>
-      <c r="I12">
-        <v>7</v>
-      </c>
-      <c r="J12">
-        <v>7</v>
-      </c>
       <c r="K12">
+        <v>7</v>
+      </c>
+      <c r="L12">
+        <v>7</v>
+      </c>
+      <c r="M12">
         <v>0.7883522727272728</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1655,31 +1667,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F13">
         <v>0.4489795918367347</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>-0.01489577072963743</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>0.8125000000000001</v>
       </c>
-      <c r="I13">
-        <v>7</v>
-      </c>
-      <c r="J13">
-        <v>7</v>
-      </c>
       <c r="K13">
+        <v>7</v>
+      </c>
+      <c r="L13">
+        <v>7</v>
+      </c>
+      <c r="M13">
         <v>0.8125000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1690,31 +1702,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F14">
         <v>0.5102040816326531</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>0.01932100864239882</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>0.8125000000000001</v>
       </c>
-      <c r="I14">
-        <v>7</v>
-      </c>
-      <c r="J14">
-        <v>7</v>
-      </c>
       <c r="K14">
+        <v>7</v>
+      </c>
+      <c r="L14">
+        <v>7</v>
+      </c>
+      <c r="M14">
         <v>0.8125000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1725,31 +1737,31 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F15">
         <v>0.5714285714285714</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>-0.05241491163505533</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>0.8125000000000001</v>
       </c>
-      <c r="I15">
-        <v>7</v>
-      </c>
-      <c r="J15">
-        <v>7</v>
-      </c>
       <c r="K15">
+        <v>7</v>
+      </c>
+      <c r="L15">
+        <v>7</v>
+      </c>
+      <c r="M15">
         <v>0.8125000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1760,31 +1772,31 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F16">
         <v>0.5918367346938775</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>-0.007881495365692354</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>0.8125000000000001</v>
       </c>
-      <c r="I16">
-        <v>7</v>
-      </c>
-      <c r="J16">
-        <v>7</v>
-      </c>
       <c r="K16">
+        <v>7</v>
+      </c>
+      <c r="L16">
+        <v>7</v>
+      </c>
+      <c r="M16">
         <v>0.8125000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -1795,31 +1807,31 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F17">
         <v>0.171875</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>-0.09400482455360595</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>0.007812500000000002</v>
       </c>
-      <c r="I17">
-        <v>8</v>
-      </c>
-      <c r="J17">
-        <v>8</v>
-      </c>
       <c r="K17">
+        <v>8</v>
+      </c>
+      <c r="L17">
+        <v>8</v>
+      </c>
+      <c r="M17">
         <v>0.03906250000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -1830,31 +1842,31 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F18">
         <v>0.734375</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>0.1162682800547686</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>0.007812500000000002</v>
       </c>
-      <c r="I18">
-        <v>8</v>
-      </c>
-      <c r="J18">
-        <v>8</v>
-      </c>
       <c r="K18">
+        <v>8</v>
+      </c>
+      <c r="L18">
+        <v>8</v>
+      </c>
+      <c r="M18">
         <v>0.03906250000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1865,31 +1877,31 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F19">
         <v>0.09375</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>-0.1637012459851492</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>0.007812500000000002</v>
       </c>
-      <c r="I19">
-        <v>8</v>
-      </c>
-      <c r="J19">
-        <v>8</v>
-      </c>
       <c r="K19">
+        <v>8</v>
+      </c>
+      <c r="L19">
+        <v>8</v>
+      </c>
+      <c r="M19">
         <v>0.03906250000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1900,31 +1912,31 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F20">
         <v>0.84375</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>0.1074234467393508</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>0.015625</v>
       </c>
-      <c r="I20">
-        <v>8</v>
-      </c>
-      <c r="J20">
-        <v>8</v>
-      </c>
       <c r="K20">
+        <v>8</v>
+      </c>
+      <c r="L20">
+        <v>8</v>
+      </c>
+      <c r="M20">
         <v>0.05859375000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1935,31 +1947,31 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F21">
         <v>0.171875</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>-0.1267924341333494</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>0.02343750000000001</v>
       </c>
-      <c r="I21">
-        <v>8</v>
-      </c>
-      <c r="J21">
-        <v>8</v>
-      </c>
       <c r="K21">
+        <v>8</v>
+      </c>
+      <c r="L21">
+        <v>8</v>
+      </c>
+      <c r="M21">
         <v>0.05859375000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -1970,31 +1982,31 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F22">
         <v>0.671875</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>0.07580347806601506</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>0.02343750000000001</v>
       </c>
-      <c r="I22">
-        <v>8</v>
-      </c>
-      <c r="J22">
-        <v>8</v>
-      </c>
       <c r="K22">
+        <v>8</v>
+      </c>
+      <c r="L22">
+        <v>8</v>
+      </c>
+      <c r="M22">
         <v>0.05859375000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -2005,31 +2017,31 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F23">
         <v>0.78125</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>0.09568584612090247</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>0.109375</v>
       </c>
-      <c r="I23">
-        <v>8</v>
-      </c>
-      <c r="J23">
-        <v>8</v>
-      </c>
       <c r="K23">
+        <v>8</v>
+      </c>
+      <c r="L23">
+        <v>8</v>
+      </c>
+      <c r="M23">
         <v>0.1822916666666667</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -2040,31 +2052,31 @@
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F24">
         <v>0.734375</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>0.1183212516935555</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>0.109375</v>
       </c>
-      <c r="I24">
-        <v>8</v>
-      </c>
-      <c r="J24">
-        <v>8</v>
-      </c>
       <c r="K24">
+        <v>8</v>
+      </c>
+      <c r="L24">
+        <v>8</v>
+      </c>
+      <c r="M24">
         <v>0.1822916666666667</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2075,31 +2087,31 @@
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F25">
         <v>0.125</v>
       </c>
-      <c r="G25">
+      <c r="I25">
         <v>-0.2204579449312783</v>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>0.109375</v>
       </c>
-      <c r="I25">
-        <v>8</v>
-      </c>
-      <c r="J25">
-        <v>8</v>
-      </c>
       <c r="K25">
+        <v>8</v>
+      </c>
+      <c r="L25">
+        <v>8</v>
+      </c>
+      <c r="M25">
         <v>0.1822916666666667</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -2110,31 +2122,31 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F26">
         <v>0.328125</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>-0.05309823078175435</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>0.3828125000000001</v>
       </c>
-      <c r="I26">
-        <v>8</v>
-      </c>
-      <c r="J26">
-        <v>8</v>
-      </c>
       <c r="K26">
+        <v>8</v>
+      </c>
+      <c r="L26">
+        <v>8</v>
+      </c>
+      <c r="M26">
         <v>0.5742187500000001</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -2145,31 +2157,31 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F27">
         <v>0.625</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>0.06792911749308136</v>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>0.5468750000000001</v>
       </c>
-      <c r="I27">
-        <v>8</v>
-      </c>
-      <c r="J27">
-        <v>8</v>
-      </c>
       <c r="K27">
+        <v>8</v>
+      </c>
+      <c r="L27">
+        <v>8</v>
+      </c>
+      <c r="M27">
         <v>0.7457386363636365</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -2180,31 +2192,31 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F28">
         <v>0.625</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>0.01427255853272026</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>0.7421875000000001</v>
       </c>
-      <c r="I28">
-        <v>8</v>
-      </c>
-      <c r="J28">
-        <v>8</v>
-      </c>
       <c r="K28">
+        <v>8</v>
+      </c>
+      <c r="L28">
+        <v>8</v>
+      </c>
+      <c r="M28">
         <v>0.9040178571428572</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -2215,31 +2227,31 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F29">
         <v>0.515625</v>
       </c>
-      <c r="G29">
+      <c r="I29">
         <v>-0.0052395554723993</v>
       </c>
-      <c r="H29">
+      <c r="J29">
         <v>0.8437500000000001</v>
       </c>
-      <c r="I29">
-        <v>8</v>
-      </c>
-      <c r="J29">
-        <v>8</v>
-      </c>
       <c r="K29">
+        <v>8</v>
+      </c>
+      <c r="L29">
+        <v>8</v>
+      </c>
+      <c r="M29">
         <v>0.9040178571428572</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -2250,31 +2262,31 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F30">
         <v>0.484375</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>-0.09822736654899855</v>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>0.8437500000000001</v>
       </c>
-      <c r="I30">
-        <v>8</v>
-      </c>
-      <c r="J30">
-        <v>8</v>
-      </c>
       <c r="K30">
+        <v>8</v>
+      </c>
+      <c r="L30">
+        <v>8</v>
+      </c>
+      <c r="M30">
         <v>0.9040178571428572</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -2285,31 +2297,31 @@
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F31">
         <v>0.46875</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>0.02726510512914805</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>0.9453124999999998</v>
       </c>
-      <c r="I31">
-        <v>8</v>
-      </c>
-      <c r="J31">
-        <v>8</v>
-      </c>
       <c r="K31">
+        <v>8</v>
+      </c>
+      <c r="L31">
+        <v>8</v>
+      </c>
+      <c r="M31">
         <v>0.9453124999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -2320,28 +2332,34 @@
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F32">
         <v>0.9464285714285714</v>
       </c>
+      <c r="G32">
+        <v>0.8428286733498574</v>
+      </c>
       <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="J32">
         <v>0.002175602175602176</v>
       </c>
-      <c r="I32">
-        <v>7</v>
-      </c>
-      <c r="J32">
-        <v>8</v>
-      </c>
       <c r="K32">
+        <v>7</v>
+      </c>
+      <c r="L32">
+        <v>8</v>
+      </c>
+      <c r="M32">
         <v>0.03263403263403263</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:13">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -2352,28 +2370,34 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F33">
         <v>0.8035714285714286</v>
       </c>
+      <c r="G33">
+        <v>0.5450225100788212</v>
+      </c>
       <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="J33">
         <v>0.05407925407925408</v>
       </c>
-      <c r="I33">
-        <v>7</v>
-      </c>
-      <c r="J33">
-        <v>8</v>
-      </c>
       <c r="K33">
+        <v>7</v>
+      </c>
+      <c r="L33">
+        <v>8</v>
+      </c>
+      <c r="M33">
         <v>0.2703962703962704</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:13">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -2384,28 +2408,34 @@
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F34">
         <v>0.1964285714285714</v>
       </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
       <c r="H34">
+        <v>0.4396318325697636</v>
+      </c>
+      <c r="J34">
         <v>0.05407925407925408</v>
       </c>
-      <c r="I34">
-        <v>7</v>
-      </c>
-      <c r="J34">
-        <v>8</v>
-      </c>
       <c r="K34">
+        <v>7</v>
+      </c>
+      <c r="L34">
+        <v>8</v>
+      </c>
+      <c r="M34">
         <v>0.2703962703962704</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:13">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -2416,28 +2446,34 @@
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F35">
         <v>0.2321428571428572</v>
       </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
       <c r="H35">
+        <v>0.489334554090463</v>
+      </c>
+      <c r="J35">
         <v>0.09386169386169387</v>
       </c>
-      <c r="I35">
-        <v>7</v>
-      </c>
-      <c r="J35">
-        <v>8</v>
-      </c>
       <c r="K35">
+        <v>7</v>
+      </c>
+      <c r="L35">
+        <v>8</v>
+      </c>
+      <c r="M35">
         <v>0.351981351981352</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:13">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -2448,28 +2484,34 @@
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F36">
         <v>0.7142857142857143</v>
       </c>
+      <c r="G36">
+        <v>0.4244635050108926</v>
+      </c>
       <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="J36">
         <v>0.1892773892773893</v>
       </c>
-      <c r="I36">
-        <v>7</v>
-      </c>
-      <c r="J36">
-        <v>8</v>
-      </c>
       <c r="K36">
+        <v>7</v>
+      </c>
+      <c r="L36">
+        <v>8</v>
+      </c>
+      <c r="M36">
         <v>0.5678321678321678</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:13">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -2480,28 +2522,34 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F37">
         <v>0.3571428571428572</v>
       </c>
+      <c r="G37">
+        <v>0.02625368712742985</v>
+      </c>
       <c r="H37">
+        <v>0.6880320271582845</v>
+      </c>
+      <c r="J37">
         <v>0.3968919968919969</v>
       </c>
-      <c r="I37">
-        <v>7</v>
-      </c>
-      <c r="J37">
-        <v>8</v>
-      </c>
       <c r="K37">
+        <v>7</v>
+      </c>
+      <c r="L37">
+        <v>8</v>
+      </c>
+      <c r="M37">
         <v>0.6614866614866616</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:13">
       <c r="A38" t="s">
         <v>35</v>
       </c>
@@ -2512,28 +2560,34 @@
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F38">
         <v>0.3571428571428572</v>
       </c>
+      <c r="G38">
+        <v>0.0457806290631923</v>
+      </c>
       <c r="H38">
+        <v>0.6685050852225221</v>
+      </c>
+      <c r="J38">
         <v>0.3968919968919969</v>
       </c>
-      <c r="I38">
-        <v>7</v>
-      </c>
-      <c r="J38">
-        <v>8</v>
-      </c>
       <c r="K38">
+        <v>7</v>
+      </c>
+      <c r="L38">
+        <v>8</v>
+      </c>
+      <c r="M38">
         <v>0.6614866614866616</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:13">
       <c r="A39" t="s">
         <v>35</v>
       </c>
@@ -2544,28 +2598,34 @@
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E39" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F39">
         <v>0.6428571428571429</v>
       </c>
+      <c r="G39">
+        <v>0.3353594057888329</v>
+      </c>
       <c r="H39">
+        <v>0.950354879925453</v>
+      </c>
+      <c r="J39">
         <v>0.3968919968919969</v>
       </c>
-      <c r="I39">
-        <v>7</v>
-      </c>
-      <c r="J39">
-        <v>8</v>
-      </c>
       <c r="K39">
+        <v>7</v>
+      </c>
+      <c r="L39">
+        <v>8</v>
+      </c>
+      <c r="M39">
         <v>0.6614866614866616</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:13">
       <c r="A40" t="s">
         <v>35</v>
       </c>
@@ -2576,28 +2636,34 @@
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F40">
         <v>0.6428571428571429</v>
       </c>
+      <c r="G40">
+        <v>0.3147117848880667</v>
+      </c>
       <c r="H40">
+        <v>0.9710025008262191</v>
+      </c>
+      <c r="J40">
         <v>0.3968919968919969</v>
       </c>
-      <c r="I40">
-        <v>7</v>
-      </c>
-      <c r="J40">
-        <v>8</v>
-      </c>
       <c r="K40">
+        <v>7</v>
+      </c>
+      <c r="L40">
+        <v>8</v>
+      </c>
+      <c r="M40">
         <v>0.6614866614866616</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:13">
       <c r="A41" t="s">
         <v>35</v>
       </c>
@@ -2608,28 +2674,34 @@
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F41">
         <v>0.4107142857142857</v>
       </c>
+      <c r="G41">
+        <v>0.06398588809531608</v>
+      </c>
       <c r="H41">
+        <v>0.7574426833332553</v>
+      </c>
+      <c r="J41">
         <v>0.6125874125874127</v>
       </c>
-      <c r="I41">
-        <v>7</v>
-      </c>
-      <c r="J41">
-        <v>8</v>
-      </c>
       <c r="K41">
+        <v>7</v>
+      </c>
+      <c r="L41">
+        <v>8</v>
+      </c>
+      <c r="M41">
         <v>0.8665112665112666</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:13">
       <c r="A42" t="s">
         <v>35</v>
       </c>
@@ -2640,28 +2712,34 @@
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E42" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F42">
         <v>0.4464285714285715</v>
       </c>
+      <c r="G42">
+        <v>0.1209605387903666</v>
+      </c>
       <c r="H42">
+        <v>0.7718966040667763</v>
+      </c>
+      <c r="J42">
         <v>0.7788655788655789</v>
       </c>
-      <c r="I42">
-        <v>7</v>
-      </c>
-      <c r="J42">
-        <v>8</v>
-      </c>
       <c r="K42">
+        <v>7</v>
+      </c>
+      <c r="L42">
+        <v>8</v>
+      </c>
+      <c r="M42">
         <v>0.8665112665112666</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:13">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -2672,28 +2750,34 @@
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E43" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F43">
         <v>0.4464285714285715</v>
       </c>
+      <c r="G43">
+        <v>0.1223074946289458</v>
+      </c>
       <c r="H43">
+        <v>0.770549648228197</v>
+      </c>
+      <c r="J43">
         <v>0.7788655788655789</v>
       </c>
-      <c r="I43">
-        <v>7</v>
-      </c>
-      <c r="J43">
-        <v>8</v>
-      </c>
       <c r="K43">
+        <v>7</v>
+      </c>
+      <c r="L43">
+        <v>8</v>
+      </c>
+      <c r="M43">
         <v>0.8665112665112666</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:13">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -2704,28 +2788,34 @@
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E44" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F44">
         <v>0.4642857142857143</v>
       </c>
+      <c r="G44">
+        <v>0.1477213706034705</v>
+      </c>
       <c r="H44">
+        <v>0.780850057967958</v>
+      </c>
+      <c r="J44">
         <v>0.8665112665112666</v>
       </c>
-      <c r="I44">
-        <v>7</v>
-      </c>
-      <c r="J44">
-        <v>8</v>
-      </c>
       <c r="K44">
+        <v>7</v>
+      </c>
+      <c r="L44">
+        <v>8</v>
+      </c>
+      <c r="M44">
         <v>0.8665112665112666</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:13">
       <c r="A45" t="s">
         <v>35</v>
       </c>
@@ -2736,28 +2826,34 @@
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E45" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F45">
         <v>0.5357142857142857</v>
       </c>
+      <c r="G45">
+        <v>0.1559845125452449</v>
+      </c>
       <c r="H45">
+        <v>0.9154440588833265</v>
+      </c>
+      <c r="J45">
         <v>0.8665112665112666</v>
       </c>
-      <c r="I45">
-        <v>7</v>
-      </c>
-      <c r="J45">
-        <v>8</v>
-      </c>
       <c r="K45">
+        <v>7</v>
+      </c>
+      <c r="L45">
+        <v>8</v>
+      </c>
+      <c r="M45">
         <v>0.8665112665112666</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:13">
       <c r="A46" t="s">
         <v>35</v>
       </c>
@@ -2768,28 +2864,34 @@
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E46" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F46">
         <v>0.4642857142857143</v>
       </c>
+      <c r="G46">
+        <v>0.1429662384537884</v>
+      </c>
       <c r="H46">
+        <v>0.7856051901176402</v>
+      </c>
+      <c r="J46">
         <v>0.8665112665112666</v>
       </c>
-      <c r="I46">
-        <v>7</v>
-      </c>
-      <c r="J46">
-        <v>8</v>
-      </c>
       <c r="K46">
+        <v>7</v>
+      </c>
+      <c r="L46">
+        <v>8</v>
+      </c>
+      <c r="M46">
         <v>0.8665112665112666</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:13">
       <c r="A47" t="s">
         <v>29</v>
       </c>
@@ -2800,28 +2902,34 @@
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F47">
         <v>0.8571428571428571</v>
       </c>
+      <c r="G47">
+        <v>0.6475637891268318</v>
+      </c>
       <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="J47">
         <v>0.02051282051282051</v>
       </c>
-      <c r="I47">
-        <v>7</v>
-      </c>
-      <c r="J47">
-        <v>8</v>
-      </c>
       <c r="K47">
+        <v>7</v>
+      </c>
+      <c r="L47">
+        <v>8</v>
+      </c>
+      <c r="M47">
         <v>0.3076923076923077</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:13">
       <c r="A48" t="s">
         <v>29</v>
       </c>
@@ -2832,28 +2940,34 @@
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E48" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F48">
         <v>0.7321428571428571</v>
       </c>
+      <c r="G48">
+        <v>0.4306797692550272</v>
+      </c>
       <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="J48">
         <v>0.151981351981352</v>
       </c>
-      <c r="I48">
-        <v>7</v>
-      </c>
-      <c r="J48">
-        <v>8</v>
-      </c>
       <c r="K48">
+        <v>7</v>
+      </c>
+      <c r="L48">
+        <v>8</v>
+      </c>
+      <c r="M48">
         <v>0.6951048951048951</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:13">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -2864,28 +2978,34 @@
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E49" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F49">
         <v>0.2857142857142857</v>
       </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
       <c r="H49">
+        <v>0.5862083479902463</v>
+      </c>
+      <c r="J49">
         <v>0.1892773892773893</v>
       </c>
-      <c r="I49">
-        <v>7</v>
-      </c>
-      <c r="J49">
-        <v>8</v>
-      </c>
       <c r="K49">
+        <v>7</v>
+      </c>
+      <c r="L49">
+        <v>8</v>
+      </c>
+      <c r="M49">
         <v>0.6951048951048951</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:13">
       <c r="A50" t="s">
         <v>29</v>
       </c>
@@ -2896,28 +3016,34 @@
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F50">
         <v>0.7142857142857143</v>
       </c>
+      <c r="G50">
+        <v>0.4246648403664002</v>
+      </c>
       <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="J50">
         <v>0.1892773892773893</v>
       </c>
-      <c r="I50">
-        <v>7</v>
-      </c>
-      <c r="J50">
-        <v>8</v>
-      </c>
       <c r="K50">
+        <v>7</v>
+      </c>
+      <c r="L50">
+        <v>8</v>
+      </c>
+      <c r="M50">
         <v>0.6951048951048951</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:13">
       <c r="A51" t="s">
         <v>29</v>
       </c>
@@ -2928,28 +3054,34 @@
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E51" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F51">
         <v>0.6964285714285714</v>
       </c>
+      <c r="G51">
+        <v>0.4088288029685217</v>
+      </c>
       <c r="H51">
+        <v>0.984028339888621</v>
+      </c>
+      <c r="J51">
         <v>0.2318570318570319</v>
       </c>
-      <c r="I51">
-        <v>7</v>
-      </c>
-      <c r="J51">
-        <v>8</v>
-      </c>
       <c r="K51">
+        <v>7</v>
+      </c>
+      <c r="L51">
+        <v>8</v>
+      </c>
+      <c r="M51">
         <v>0.6951048951048951</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:13">
       <c r="A52" t="s">
         <v>29</v>
       </c>
@@ -2960,28 +3092,34 @@
         <v>0</v>
       </c>
       <c r="D52" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E52" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F52">
         <v>0.3214285714285715</v>
       </c>
+      <c r="G52">
+        <v>0.02691460079391003</v>
+      </c>
       <c r="H52">
+        <v>0.6159425420632328</v>
+      </c>
+      <c r="J52">
         <v>0.280963480963481</v>
       </c>
-      <c r="I52">
-        <v>7</v>
-      </c>
-      <c r="J52">
-        <v>8</v>
-      </c>
       <c r="K52">
+        <v>7</v>
+      </c>
+      <c r="L52">
+        <v>8</v>
+      </c>
+      <c r="M52">
         <v>0.6951048951048951</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:13">
       <c r="A53" t="s">
         <v>29</v>
       </c>
@@ -2992,28 +3130,34 @@
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E53" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F53">
         <v>0.6428571428571429</v>
       </c>
+      <c r="G53">
+        <v>0.321810087146961</v>
+      </c>
       <c r="H53">
+        <v>0.9639041985673249</v>
+      </c>
+      <c r="J53">
         <v>0.3968919968919969</v>
       </c>
-      <c r="I53">
-        <v>7</v>
-      </c>
-      <c r="J53">
-        <v>8</v>
-      </c>
       <c r="K53">
+        <v>7</v>
+      </c>
+      <c r="L53">
+        <v>8</v>
+      </c>
+      <c r="M53">
         <v>0.6951048951048951</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:13">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -3024,28 +3168,34 @@
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E54" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F54">
         <v>0.3571428571428572</v>
       </c>
+      <c r="G54">
+        <v>0.02170155871430612</v>
+      </c>
       <c r="H54">
+        <v>0.6925841555714082</v>
+      </c>
+      <c r="J54">
         <v>0.3968919968919969</v>
       </c>
-      <c r="I54">
-        <v>7</v>
-      </c>
-      <c r="J54">
-        <v>8</v>
-      </c>
       <c r="K54">
+        <v>7</v>
+      </c>
+      <c r="L54">
+        <v>8</v>
+      </c>
+      <c r="M54">
         <v>0.6951048951048951</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:13">
       <c r="A55" t="s">
         <v>29</v>
       </c>
@@ -3056,28 +3206,34 @@
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E55" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F55">
         <v>0.375</v>
       </c>
+      <c r="G55">
+        <v>0.05577501947895173</v>
+      </c>
       <c r="H55">
+        <v>0.6942249805210483</v>
+      </c>
+      <c r="J55">
         <v>0.4634032634032634</v>
       </c>
-      <c r="I55">
-        <v>7</v>
-      </c>
-      <c r="J55">
-        <v>8</v>
-      </c>
       <c r="K55">
+        <v>7</v>
+      </c>
+      <c r="L55">
+        <v>8</v>
+      </c>
+      <c r="M55">
         <v>0.6951048951048951</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:13">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -3088,28 +3244,34 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E56" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F56">
         <v>0.625</v>
       </c>
+      <c r="G56">
+        <v>0.2917394638544177</v>
+      </c>
       <c r="H56">
+        <v>0.9582605361455823</v>
+      </c>
+      <c r="J56">
         <v>0.4634032634032634</v>
       </c>
-      <c r="I56">
-        <v>7</v>
-      </c>
-      <c r="J56">
-        <v>8</v>
-      </c>
       <c r="K56">
+        <v>7</v>
+      </c>
+      <c r="L56">
+        <v>8</v>
+      </c>
+      <c r="M56">
         <v>0.6951048951048951</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:13">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -3120,28 +3282,34 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E57" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F57">
         <v>0.4464285714285715</v>
       </c>
+      <c r="G57">
+        <v>0.1224875119029264</v>
+      </c>
       <c r="H57">
+        <v>0.7703696309542165</v>
+      </c>
+      <c r="J57">
         <v>0.7788655788655789</v>
       </c>
-      <c r="I57">
-        <v>7</v>
-      </c>
-      <c r="J57">
-        <v>8</v>
-      </c>
       <c r="K57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+        <v>7</v>
+      </c>
+      <c r="L57">
+        <v>8</v>
+      </c>
+      <c r="M57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" t="s">
         <v>29</v>
       </c>
@@ -3152,28 +3320,34 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E58" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F58">
         <v>0.5178571428571429</v>
       </c>
+      <c r="G58">
+        <v>0.1705404285423149</v>
+      </c>
       <c r="H58">
+        <v>0.8651738571719709</v>
+      </c>
+      <c r="J58">
         <v>0.9550893550893549</v>
       </c>
-      <c r="I58">
-        <v>7</v>
-      </c>
-      <c r="J58">
-        <v>8</v>
-      </c>
       <c r="K58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+        <v>7</v>
+      </c>
+      <c r="L58">
+        <v>8</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" t="s">
         <v>29</v>
       </c>
@@ -3184,28 +3358,34 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E59" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F59">
         <v>0.5178571428571429</v>
       </c>
+      <c r="G59">
+        <v>0.1878505808955027</v>
+      </c>
       <c r="H59">
+        <v>0.847863704818783</v>
+      </c>
+      <c r="J59">
         <v>0.9550893550893549</v>
       </c>
-      <c r="I59">
-        <v>7</v>
-      </c>
-      <c r="J59">
-        <v>8</v>
-      </c>
       <c r="K59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+        <v>7</v>
+      </c>
+      <c r="L59">
+        <v>8</v>
+      </c>
+      <c r="M59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" t="s">
         <v>29</v>
       </c>
@@ -3216,28 +3396,34 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E60" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F60">
         <v>0.4821428571428572</v>
       </c>
+      <c r="G60">
+        <v>0.161550349382151</v>
+      </c>
       <c r="H60">
+        <v>0.8027353649035632</v>
+      </c>
+      <c r="J60">
         <v>0.9550893550893552</v>
       </c>
-      <c r="I60">
-        <v>7</v>
-      </c>
-      <c r="J60">
-        <v>8</v>
-      </c>
       <c r="K60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+        <v>7</v>
+      </c>
+      <c r="L60">
+        <v>8</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" t="s">
         <v>29</v>
       </c>
@@ -3248,28 +3434,34 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E61" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F61">
         <v>0.5</v>
       </c>
+      <c r="G61">
+        <v>0.1760589404743549</v>
+      </c>
       <c r="H61">
-        <v>1</v>
-      </c>
-      <c r="I61">
-        <v>7</v>
+        <v>0.8239410595256451</v>
       </c>
       <c r="J61">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>7</v>
+      </c>
+      <c r="L61">
+        <v>8</v>
+      </c>
+      <c r="M61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" t="s">
         <v>31</v>
       </c>
@@ -3280,28 +3472,34 @@
         <v>0</v>
       </c>
       <c r="D62" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E62" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F62">
         <v>0.7857142857142857</v>
       </c>
+      <c r="G62">
+        <v>0.5221380220170376</v>
+      </c>
       <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="J62">
         <v>0.07210567210567211</v>
       </c>
-      <c r="I62">
-        <v>7</v>
-      </c>
-      <c r="J62">
-        <v>8</v>
-      </c>
       <c r="K62">
+        <v>7</v>
+      </c>
+      <c r="L62">
+        <v>8</v>
+      </c>
+      <c r="M62">
         <v>0.7097902097902099</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:13">
       <c r="A63" t="s">
         <v>31</v>
       </c>
@@ -3312,28 +3510,34 @@
         <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E63" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F63">
         <v>0.75</v>
       </c>
+      <c r="G63">
+        <v>0.4260589404743549</v>
+      </c>
       <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="J63">
         <v>0.1205905205905206</v>
       </c>
-      <c r="I63">
-        <v>7</v>
-      </c>
-      <c r="J63">
-        <v>8</v>
-      </c>
       <c r="K63">
+        <v>7</v>
+      </c>
+      <c r="L63">
+        <v>8</v>
+      </c>
+      <c r="M63">
         <v>0.7097902097902099</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:13">
       <c r="A64" t="s">
         <v>31</v>
       </c>
@@ -3344,28 +3548,34 @@
         <v>0</v>
       </c>
       <c r="D64" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E64" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F64">
         <v>0.2678571428571428</v>
       </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
       <c r="H64">
+        <v>0.5479561431753368</v>
+      </c>
+      <c r="J64">
         <v>0.151981351981352</v>
       </c>
-      <c r="I64">
-        <v>7</v>
-      </c>
-      <c r="J64">
-        <v>8</v>
-      </c>
       <c r="K64">
+        <v>7</v>
+      </c>
+      <c r="L64">
+        <v>8</v>
+      </c>
+      <c r="M64">
         <v>0.7097902097902099</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:13">
       <c r="A65" t="s">
         <v>31</v>
       </c>
@@ -3376,28 +3586,34 @@
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E65" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F65">
         <v>0.2857142857142857</v>
       </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
       <c r="H65">
+        <v>0.5746293809979307</v>
+      </c>
+      <c r="J65">
         <v>0.1892773892773893</v>
       </c>
-      <c r="I65">
-        <v>7</v>
-      </c>
-      <c r="J65">
-        <v>8</v>
-      </c>
       <c r="K65">
+        <v>7</v>
+      </c>
+      <c r="L65">
+        <v>8</v>
+      </c>
+      <c r="M65">
         <v>0.7097902097902099</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:13">
       <c r="A66" t="s">
         <v>31</v>
       </c>
@@ -3408,28 +3624,34 @@
         <v>0</v>
       </c>
       <c r="D66" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E66" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F66">
         <v>0.6428571428571429</v>
       </c>
+      <c r="G66">
+        <v>0.335739032769462</v>
+      </c>
       <c r="H66">
+        <v>0.9499752529448239</v>
+      </c>
+      <c r="J66">
         <v>0.3968919968919969</v>
       </c>
-      <c r="I66">
-        <v>7</v>
-      </c>
-      <c r="J66">
-        <v>8</v>
-      </c>
       <c r="K66">
+        <v>7</v>
+      </c>
+      <c r="L66">
+        <v>8</v>
+      </c>
+      <c r="M66">
         <v>0.7441724941724943</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:13">
       <c r="A67" t="s">
         <v>31</v>
       </c>
@@ -3440,28 +3662,34 @@
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E67" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F67">
         <v>0.6428571428571429</v>
       </c>
+      <c r="G67">
+        <v>0.3356440820452618</v>
+      </c>
       <c r="H67">
+        <v>0.9500702036690241</v>
+      </c>
+      <c r="J67">
         <v>0.3968919968919969</v>
       </c>
-      <c r="I67">
-        <v>7</v>
-      </c>
-      <c r="J67">
-        <v>8</v>
-      </c>
       <c r="K67">
+        <v>7</v>
+      </c>
+      <c r="L67">
+        <v>8</v>
+      </c>
+      <c r="M67">
         <v>0.7441724941724943</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:13">
       <c r="A68" t="s">
         <v>31</v>
       </c>
@@ -3472,28 +3700,34 @@
         <v>0</v>
       </c>
       <c r="D68" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E68" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F68">
         <v>0.6428571428571429</v>
       </c>
+      <c r="G68">
+        <v>0.335739032769462</v>
+      </c>
       <c r="H68">
+        <v>0.9499752529448239</v>
+      </c>
+      <c r="J68">
         <v>0.3968919968919969</v>
       </c>
-      <c r="I68">
-        <v>7</v>
-      </c>
-      <c r="J68">
-        <v>8</v>
-      </c>
       <c r="K68">
+        <v>7</v>
+      </c>
+      <c r="L68">
+        <v>8</v>
+      </c>
+      <c r="M68">
         <v>0.7441724941724943</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:13">
       <c r="A69" t="s">
         <v>31</v>
       </c>
@@ -3504,28 +3738,34 @@
         <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E69" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F69">
         <v>0.3571428571428572</v>
       </c>
+      <c r="G69">
+        <v>0.04503216108881539</v>
+      </c>
       <c r="H69">
+        <v>0.6692535531968989</v>
+      </c>
+      <c r="J69">
         <v>0.3968919968919969</v>
       </c>
-      <c r="I69">
-        <v>7</v>
-      </c>
-      <c r="J69">
-        <v>8</v>
-      </c>
       <c r="K69">
+        <v>7</v>
+      </c>
+      <c r="L69">
+        <v>8</v>
+      </c>
+      <c r="M69">
         <v>0.7441724941724943</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:13">
       <c r="A70" t="s">
         <v>31</v>
       </c>
@@ -3536,28 +3776,34 @@
         <v>0</v>
       </c>
       <c r="D70" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E70" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F70">
         <v>0.375</v>
       </c>
+      <c r="G70">
+        <v>0.05668996828106859</v>
+      </c>
       <c r="H70">
+        <v>0.6933100317189314</v>
+      </c>
+      <c r="J70">
         <v>0.4634032634032634</v>
       </c>
-      <c r="I70">
-        <v>7</v>
-      </c>
-      <c r="J70">
-        <v>8</v>
-      </c>
       <c r="K70">
+        <v>7</v>
+      </c>
+      <c r="L70">
+        <v>8</v>
+      </c>
+      <c r="M70">
         <v>0.7723387723387725</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:13">
       <c r="A71" t="s">
         <v>31</v>
       </c>
@@ -3568,28 +3814,34 @@
         <v>0</v>
       </c>
       <c r="D71" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E71" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F71">
         <v>0.5714285714285714</v>
       </c>
+      <c r="G71">
+        <v>0.2485697233669305</v>
+      </c>
       <c r="H71">
+        <v>0.8942874194902123</v>
+      </c>
+      <c r="J71">
         <v>0.6943278943278944</v>
       </c>
-      <c r="I71">
-        <v>7</v>
-      </c>
-      <c r="J71">
-        <v>8</v>
-      </c>
       <c r="K71">
+        <v>7</v>
+      </c>
+      <c r="L71">
+        <v>8</v>
+      </c>
+      <c r="M71">
         <v>0.867909867909868</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:13">
       <c r="A72" t="s">
         <v>31</v>
       </c>
@@ -3600,28 +3852,34 @@
         <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E72" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F72">
         <v>0.5714285714285714</v>
       </c>
+      <c r="G72">
+        <v>0.2485697233669305</v>
+      </c>
       <c r="H72">
+        <v>0.8942874194902123</v>
+      </c>
+      <c r="J72">
         <v>0.6943278943278944</v>
       </c>
-      <c r="I72">
-        <v>7</v>
-      </c>
-      <c r="J72">
-        <v>8</v>
-      </c>
       <c r="K72">
+        <v>7</v>
+      </c>
+      <c r="L72">
+        <v>8</v>
+      </c>
+      <c r="M72">
         <v>0.867909867909868</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:13">
       <c r="A73" t="s">
         <v>31</v>
       </c>
@@ -3632,28 +3890,34 @@
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E73" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F73">
         <v>0.4285714285714285</v>
       </c>
+      <c r="G73">
+        <v>0.1149691555813418</v>
+      </c>
       <c r="H73">
+        <v>0.7421737015615153</v>
+      </c>
+      <c r="J73">
         <v>0.6943278943278944</v>
       </c>
-      <c r="I73">
-        <v>7</v>
-      </c>
-      <c r="J73">
-        <v>8</v>
-      </c>
       <c r="K73">
+        <v>7</v>
+      </c>
+      <c r="L73">
+        <v>8</v>
+      </c>
+      <c r="M73">
         <v>0.867909867909868</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:13">
       <c r="A74" t="s">
         <v>31</v>
       </c>
@@ -3664,28 +3928,34 @@
         <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E74" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F74">
         <v>0.4642857142857143</v>
       </c>
+      <c r="G74">
+        <v>0.139894798885058</v>
+      </c>
       <c r="H74">
+        <v>0.7886766296863706</v>
+      </c>
+      <c r="J74">
         <v>0.8665112665112666</v>
       </c>
-      <c r="I74">
-        <v>7</v>
-      </c>
-      <c r="J74">
-        <v>8</v>
-      </c>
       <c r="K74">
+        <v>7</v>
+      </c>
+      <c r="L74">
+        <v>8</v>
+      </c>
+      <c r="M74">
         <v>0.9284049284049285</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:13">
       <c r="A75" t="s">
         <v>31</v>
       </c>
@@ -3696,28 +3966,34 @@
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E75" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F75">
         <v>0.4642857142857143</v>
       </c>
+      <c r="G75">
+        <v>0.1396251845578111</v>
+      </c>
       <c r="H75">
+        <v>0.7889462440136176</v>
+      </c>
+      <c r="J75">
         <v>0.8665112665112666</v>
       </c>
-      <c r="I75">
-        <v>7</v>
-      </c>
-      <c r="J75">
-        <v>8</v>
-      </c>
       <c r="K75">
+        <v>7</v>
+      </c>
+      <c r="L75">
+        <v>8</v>
+      </c>
+      <c r="M75">
         <v>0.9284049284049285</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:13">
       <c r="A76" t="s">
         <v>31</v>
       </c>
@@ -3728,28 +4004,34 @@
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E76" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F76">
         <v>0.4821428571428572</v>
       </c>
+      <c r="G76">
+        <v>0.1621878013846009</v>
+      </c>
       <c r="H76">
+        <v>0.8020979129011134</v>
+      </c>
+      <c r="J76">
         <v>0.9550893550893552</v>
       </c>
-      <c r="I76">
-        <v>7</v>
-      </c>
-      <c r="J76">
-        <v>8</v>
-      </c>
       <c r="K76">
+        <v>7</v>
+      </c>
+      <c r="L76">
+        <v>8</v>
+      </c>
+      <c r="M76">
         <v>0.9550893550893552</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:13">
       <c r="A77" t="s">
         <v>21</v>
       </c>
@@ -3760,31 +4042,31 @@
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E77" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F77">
         <v>0.8611111111111112</v>
       </c>
-      <c r="G77">
+      <c r="I77">
         <v>0.1726841728124711</v>
       </c>
-      <c r="H77">
+      <c r="J77">
         <v>0.06250000000000003</v>
       </c>
-      <c r="I77">
+      <c r="K77">
         <v>6</v>
       </c>
-      <c r="J77">
+      <c r="L77">
         <v>6</v>
       </c>
-      <c r="K77">
+      <c r="M77">
         <v>0.7812500000000002</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:13">
       <c r="A78" t="s">
         <v>21</v>
       </c>
@@ -3795,31 +4077,31 @@
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E78" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F78">
         <v>0.8333333333333334</v>
       </c>
-      <c r="G78">
+      <c r="I78">
         <v>0.1066412365018345</v>
       </c>
-      <c r="H78">
+      <c r="J78">
         <v>0.1562500000000001</v>
       </c>
-      <c r="I78">
+      <c r="K78">
         <v>6</v>
       </c>
-      <c r="J78">
+      <c r="L78">
         <v>6</v>
       </c>
-      <c r="K78">
+      <c r="M78">
         <v>0.7812500000000002</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:13">
       <c r="A79" t="s">
         <v>21</v>
       </c>
@@ -3830,31 +4112,31 @@
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E79" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F79">
         <v>0.3333333333333333</v>
       </c>
-      <c r="G79">
+      <c r="I79">
         <v>-0.1451396763010954</v>
       </c>
-      <c r="H79">
+      <c r="J79">
         <v>0.1562500000000001</v>
       </c>
-      <c r="I79">
+      <c r="K79">
         <v>6</v>
       </c>
-      <c r="J79">
+      <c r="L79">
         <v>6</v>
       </c>
-      <c r="K79">
+      <c r="M79">
         <v>0.7812500000000002</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:13">
       <c r="A80" t="s">
         <v>21</v>
       </c>
@@ -3865,31 +4147,31 @@
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E80" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F80">
         <v>0.6944444444444444</v>
       </c>
-      <c r="G80">
+      <c r="I80">
         <v>0.1813157859027815</v>
       </c>
-      <c r="H80">
+      <c r="J80">
         <v>0.3125000000000001</v>
       </c>
-      <c r="I80">
+      <c r="K80">
         <v>6</v>
       </c>
-      <c r="J80">
+      <c r="L80">
         <v>6</v>
       </c>
-      <c r="K80">
+      <c r="M80">
         <v>0.7812500000000002</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:13">
       <c r="A81" t="s">
         <v>21</v>
       </c>
@@ -3900,31 +4182,31 @@
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E81" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F81">
         <v>0.2777777777777778</v>
       </c>
-      <c r="G81">
+      <c r="I81">
         <v>-0.06229167852528958</v>
       </c>
-      <c r="H81">
+      <c r="J81">
         <v>0.3125000000000001</v>
       </c>
-      <c r="I81">
+      <c r="K81">
         <v>6</v>
       </c>
-      <c r="J81">
+      <c r="L81">
         <v>6</v>
       </c>
-      <c r="K81">
+      <c r="M81">
         <v>0.7812500000000002</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:13">
       <c r="A82" t="s">
         <v>21</v>
       </c>
@@ -3935,31 +4217,31 @@
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E82" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F82">
         <v>0.1944444444444444</v>
       </c>
-      <c r="G82">
+      <c r="I82">
         <v>-0.1076335027443761</v>
       </c>
-      <c r="H82">
+      <c r="J82">
         <v>0.3125000000000001</v>
       </c>
-      <c r="I82">
+      <c r="K82">
         <v>6</v>
       </c>
-      <c r="J82">
+      <c r="L82">
         <v>6</v>
       </c>
-      <c r="K82">
+      <c r="M82">
         <v>0.7812500000000002</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:13">
       <c r="A83" t="s">
         <v>21</v>
       </c>
@@ -3970,31 +4252,31 @@
         <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E83" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F83">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G83">
+      <c r="I83">
         <v>0.1326734954674455</v>
       </c>
-      <c r="H83">
+      <c r="J83">
         <v>0.4375000000000002</v>
       </c>
-      <c r="I83">
+      <c r="K83">
         <v>6</v>
       </c>
-      <c r="J83">
+      <c r="L83">
         <v>6</v>
       </c>
-      <c r="K83">
+      <c r="M83">
         <v>0.8437500000000003</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:13">
       <c r="A84" t="s">
         <v>21</v>
       </c>
@@ -4005,31 +4287,31 @@
         <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E84" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F84">
         <v>0.5555555555555556</v>
       </c>
-      <c r="G84">
+      <c r="I84">
         <v>0.01776047608298494</v>
       </c>
-      <c r="H84">
+      <c r="J84">
         <v>0.5625000000000002</v>
       </c>
-      <c r="I84">
+      <c r="K84">
         <v>6</v>
       </c>
-      <c r="J84">
+      <c r="L84">
         <v>6</v>
       </c>
-      <c r="K84">
+      <c r="M84">
         <v>0.8437500000000003</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:13">
       <c r="A85" t="s">
         <v>21</v>
       </c>
@@ -4040,31 +4322,31 @@
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E85" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F85">
         <v>0.6944444444444444</v>
       </c>
-      <c r="G85">
+      <c r="I85">
         <v>0.1221424491899613</v>
       </c>
-      <c r="H85">
+      <c r="J85">
         <v>0.5625000000000002</v>
       </c>
-      <c r="I85">
+      <c r="K85">
         <v>6</v>
       </c>
-      <c r="J85">
+      <c r="L85">
         <v>6</v>
       </c>
-      <c r="K85">
+      <c r="M85">
         <v>0.8437500000000003</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:13">
       <c r="A86" t="s">
         <v>21</v>
       </c>
@@ -4075,31 +4357,31 @@
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E86" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F86">
         <v>0.6388888888888888</v>
       </c>
-      <c r="G86">
+      <c r="I86">
         <v>0.08681461636921775</v>
       </c>
-      <c r="H86">
+      <c r="J86">
         <v>0.6875000000000002</v>
       </c>
-      <c r="I86">
+      <c r="K86">
         <v>6</v>
       </c>
-      <c r="J86">
+      <c r="L86">
         <v>6</v>
       </c>
-      <c r="K86">
+      <c r="M86">
         <v>0.8437500000000003</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:13">
       <c r="A87" t="s">
         <v>21</v>
       </c>
@@ -4110,31 +4392,31 @@
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E87" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F87">
         <v>0.4722222222222222</v>
       </c>
-      <c r="G87">
+      <c r="I87">
         <v>-0.05147354144125908</v>
       </c>
-      <c r="H87">
+      <c r="J87">
         <v>0.6875000000000002</v>
       </c>
-      <c r="I87">
+      <c r="K87">
         <v>6</v>
       </c>
-      <c r="J87">
+      <c r="L87">
         <v>6</v>
       </c>
-      <c r="K87">
+      <c r="M87">
         <v>0.8437500000000003</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:13">
       <c r="A88" t="s">
         <v>21</v>
       </c>
@@ -4145,31 +4427,31 @@
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E88" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F88">
         <v>0.5277777777777778</v>
       </c>
-      <c r="G88">
+      <c r="I88">
         <v>-0.04559408890641857</v>
       </c>
-      <c r="H88">
+      <c r="J88">
         <v>0.8437500000000003</v>
       </c>
-      <c r="I88">
+      <c r="K88">
         <v>6</v>
       </c>
-      <c r="J88">
+      <c r="L88">
         <v>6</v>
       </c>
-      <c r="K88">
+      <c r="M88">
         <v>0.8437500000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:13">
       <c r="A89" t="s">
         <v>21</v>
       </c>
@@ -4180,31 +4462,31 @@
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E89" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F89">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G89">
+      <c r="I89">
         <v>0.04772559282893921</v>
       </c>
-      <c r="H89">
+      <c r="J89">
         <v>0.8437500000000003</v>
       </c>
-      <c r="I89">
+      <c r="K89">
         <v>6</v>
       </c>
-      <c r="J89">
+      <c r="L89">
         <v>6</v>
       </c>
-      <c r="K89">
+      <c r="M89">
         <v>0.8437500000000003</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:13">
       <c r="A90" t="s">
         <v>21</v>
       </c>
@@ -4215,31 +4497,31 @@
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E90" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F90">
         <v>0.3333333333333333</v>
       </c>
-      <c r="G90">
+      <c r="I90">
         <v>-0.04915417246721927</v>
       </c>
-      <c r="H90">
+      <c r="J90">
         <v>0.8437500000000003</v>
       </c>
-      <c r="I90">
+      <c r="K90">
         <v>6</v>
       </c>
-      <c r="J90">
+      <c r="L90">
         <v>6</v>
       </c>
-      <c r="K90">
+      <c r="M90">
         <v>0.8437500000000003</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:13">
       <c r="A91" t="s">
         <v>21</v>
       </c>
@@ -4250,31 +4532,31 @@
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E91" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F91">
         <v>0.5</v>
       </c>
-      <c r="G91">
+      <c r="I91">
         <v>-0.002860536960869783</v>
       </c>
-      <c r="H91">
+      <c r="J91">
         <v>0.8437500000000003</v>
       </c>
-      <c r="I91">
+      <c r="K91">
         <v>6</v>
       </c>
-      <c r="J91">
+      <c r="L91">
         <v>6</v>
       </c>
-      <c r="K91">
+      <c r="M91">
         <v>0.8437500000000003</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:13">
       <c r="A92" t="s">
         <v>23</v>
       </c>
@@ -4285,31 +4567,31 @@
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E92" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F92">
         <v>0.734375</v>
       </c>
-      <c r="G92">
+      <c r="I92">
         <v>0.06099995628669049</v>
       </c>
-      <c r="H92">
+      <c r="J92">
         <v>0.07812500000000001</v>
       </c>
-      <c r="I92">
-        <v>8</v>
-      </c>
-      <c r="J92">
-        <v>8</v>
-      </c>
       <c r="K92">
+        <v>8</v>
+      </c>
+      <c r="L92">
+        <v>8</v>
+      </c>
+      <c r="M92">
         <v>0.8735795454545455</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:13">
       <c r="A93" t="s">
         <v>23</v>
       </c>
@@ -4320,31 +4602,31 @@
         <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E93" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F93">
         <v>0.609375</v>
       </c>
-      <c r="G93">
+      <c r="I93">
         <v>0.08853865778819013</v>
       </c>
-      <c r="H93">
+      <c r="J93">
         <v>0.1953125</v>
       </c>
-      <c r="I93">
-        <v>8</v>
-      </c>
-      <c r="J93">
-        <v>8</v>
-      </c>
       <c r="K93">
+        <v>8</v>
+      </c>
+      <c r="L93">
+        <v>8</v>
+      </c>
+      <c r="M93">
         <v>0.8735795454545455</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:13">
       <c r="A94" t="s">
         <v>23</v>
       </c>
@@ -4355,31 +4637,31 @@
         <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E94" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F94">
         <v>0.65625</v>
       </c>
-      <c r="G94">
+      <c r="I94">
         <v>0.03478632577803124</v>
       </c>
-      <c r="H94">
+      <c r="J94">
         <v>0.2500000000000001</v>
       </c>
-      <c r="I94">
-        <v>8</v>
-      </c>
-      <c r="J94">
-        <v>8</v>
-      </c>
       <c r="K94">
+        <v>8</v>
+      </c>
+      <c r="L94">
+        <v>8</v>
+      </c>
+      <c r="M94">
         <v>0.8735795454545455</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:13">
       <c r="A95" t="s">
         <v>23</v>
       </c>
@@ -4390,31 +4672,31 @@
         <v>1</v>
       </c>
       <c r="D95" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E95" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F95">
         <v>0.59375</v>
       </c>
-      <c r="G95">
+      <c r="I95">
         <v>0.04024573245569871</v>
       </c>
-      <c r="H95">
+      <c r="J95">
         <v>0.3125000000000001</v>
       </c>
-      <c r="I95">
-        <v>8</v>
-      </c>
-      <c r="J95">
-        <v>8</v>
-      </c>
       <c r="K95">
+        <v>8</v>
+      </c>
+      <c r="L95">
+        <v>8</v>
+      </c>
+      <c r="M95">
         <v>0.8735795454545455</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:13">
       <c r="A96" t="s">
         <v>23</v>
       </c>
@@ -4425,31 +4707,31 @@
         <v>1</v>
       </c>
       <c r="D96" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E96" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F96">
         <v>0.390625</v>
       </c>
-      <c r="G96">
+      <c r="I96">
         <v>-0.03318643260852032</v>
       </c>
-      <c r="H96">
+      <c r="J96">
         <v>0.4609375000000001</v>
       </c>
-      <c r="I96">
-        <v>8</v>
-      </c>
-      <c r="J96">
-        <v>8</v>
-      </c>
       <c r="K96">
+        <v>8</v>
+      </c>
+      <c r="L96">
+        <v>8</v>
+      </c>
+      <c r="M96">
         <v>0.8735795454545455</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:13">
       <c r="A97" t="s">
         <v>23</v>
       </c>
@@ -4460,31 +4742,31 @@
         <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E97" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F97">
         <v>0.390625</v>
       </c>
-      <c r="G97">
+      <c r="I97">
         <v>-0.03802187304407005</v>
       </c>
-      <c r="H97">
+      <c r="J97">
         <v>0.5468750000000001</v>
       </c>
-      <c r="I97">
-        <v>8</v>
-      </c>
-      <c r="J97">
-        <v>8</v>
-      </c>
       <c r="K97">
+        <v>8</v>
+      </c>
+      <c r="L97">
+        <v>8</v>
+      </c>
+      <c r="M97">
         <v>0.8735795454545455</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:13">
       <c r="A98" t="s">
         <v>23</v>
       </c>
@@ -4495,31 +4777,31 @@
         <v>1</v>
       </c>
       <c r="D98" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E98" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F98">
         <v>0.4375</v>
       </c>
-      <c r="G98">
+      <c r="I98">
         <v>-0.01661325647678491</v>
       </c>
-      <c r="H98">
+      <c r="J98">
         <v>0.6406250000000001</v>
       </c>
-      <c r="I98">
-        <v>8</v>
-      </c>
-      <c r="J98">
-        <v>8</v>
-      </c>
       <c r="K98">
+        <v>8</v>
+      </c>
+      <c r="L98">
+        <v>8</v>
+      </c>
+      <c r="M98">
         <v>0.8735795454545455</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:13">
       <c r="A99" t="s">
         <v>23</v>
       </c>
@@ -4530,31 +4812,31 @@
         <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E99" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F99">
         <v>0.421875</v>
       </c>
-      <c r="G99">
+      <c r="I99">
         <v>-0.02619076159136435</v>
       </c>
-      <c r="H99">
+      <c r="J99">
         <v>0.6406250000000001</v>
       </c>
-      <c r="I99">
-        <v>8</v>
-      </c>
-      <c r="J99">
-        <v>8</v>
-      </c>
       <c r="K99">
+        <v>8</v>
+      </c>
+      <c r="L99">
+        <v>8</v>
+      </c>
+      <c r="M99">
         <v>0.8735795454545455</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:13">
       <c r="A100" t="s">
         <v>23</v>
       </c>
@@ -4565,31 +4847,31 @@
         <v>1</v>
       </c>
       <c r="D100" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E100" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F100">
         <v>0.34375</v>
       </c>
-      <c r="G100">
+      <c r="I100">
         <v>-0.1124340209448966</v>
       </c>
-      <c r="H100">
+      <c r="J100">
         <v>0.6406250000000001</v>
       </c>
-      <c r="I100">
-        <v>8</v>
-      </c>
-      <c r="J100">
-        <v>8</v>
-      </c>
       <c r="K100">
+        <v>8</v>
+      </c>
+      <c r="L100">
+        <v>8</v>
+      </c>
+      <c r="M100">
         <v>0.8735795454545455</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:13">
       <c r="A101" t="s">
         <v>23</v>
       </c>
@@ -4600,31 +4882,31 @@
         <v>1</v>
       </c>
       <c r="D101" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E101" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F101">
         <v>0.65625</v>
       </c>
-      <c r="G101">
+      <c r="I101">
         <v>0.09049223067312329</v>
       </c>
-      <c r="H101">
+      <c r="J101">
         <v>0.6406250000000001</v>
       </c>
-      <c r="I101">
-        <v>8</v>
-      </c>
-      <c r="J101">
-        <v>8</v>
-      </c>
       <c r="K101">
+        <v>8</v>
+      </c>
+      <c r="L101">
+        <v>8</v>
+      </c>
+      <c r="M101">
         <v>0.8735795454545455</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:13">
       <c r="A102" t="s">
         <v>23</v>
       </c>
@@ -4635,31 +4917,31 @@
         <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E102" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F102">
         <v>0.625</v>
       </c>
-      <c r="G102">
+      <c r="I102">
         <v>0.007953079027062937</v>
       </c>
-      <c r="H102">
+      <c r="J102">
         <v>0.6406250000000001</v>
       </c>
-      <c r="I102">
-        <v>8</v>
-      </c>
-      <c r="J102">
-        <v>8</v>
-      </c>
       <c r="K102">
+        <v>8</v>
+      </c>
+      <c r="L102">
+        <v>8</v>
+      </c>
+      <c r="M102">
         <v>0.8735795454545455</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:13">
       <c r="A103" t="s">
         <v>23</v>
       </c>
@@ -4670,31 +4952,31 @@
         <v>1</v>
       </c>
       <c r="D103" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E103" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F103">
         <v>0.578125</v>
       </c>
-      <c r="G103">
+      <c r="I103">
         <v>0.04476056869555671</v>
       </c>
-      <c r="H103">
+      <c r="J103">
         <v>0.7421875000000001</v>
       </c>
-      <c r="I103">
-        <v>8</v>
-      </c>
-      <c r="J103">
-        <v>8</v>
-      </c>
       <c r="K103">
+        <v>8</v>
+      </c>
+      <c r="L103">
+        <v>8</v>
+      </c>
+      <c r="M103">
         <v>0.9040178571428572</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:13">
       <c r="A104" t="s">
         <v>23</v>
       </c>
@@ -4705,31 +4987,31 @@
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E104" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F104">
         <v>0.515625</v>
       </c>
-      <c r="G104">
+      <c r="I104">
         <v>-0.01729494621730936</v>
       </c>
-      <c r="H104">
+      <c r="J104">
         <v>0.8437500000000001</v>
       </c>
-      <c r="I104">
-        <v>8</v>
-      </c>
-      <c r="J104">
-        <v>8</v>
-      </c>
       <c r="K104">
+        <v>8</v>
+      </c>
+      <c r="L104">
+        <v>8</v>
+      </c>
+      <c r="M104">
         <v>0.9040178571428572</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:13">
       <c r="A105" t="s">
         <v>23</v>
       </c>
@@ -4740,31 +5022,31 @@
         <v>1</v>
       </c>
       <c r="D105" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E105" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F105">
         <v>0.453125</v>
       </c>
-      <c r="G105">
+      <c r="I105">
         <v>-0.01027380439512042</v>
       </c>
-      <c r="H105">
+      <c r="J105">
         <v>0.8437500000000001</v>
       </c>
-      <c r="I105">
-        <v>8</v>
-      </c>
-      <c r="J105">
-        <v>8</v>
-      </c>
       <c r="K105">
+        <v>8</v>
+      </c>
+      <c r="L105">
+        <v>8</v>
+      </c>
+      <c r="M105">
         <v>0.9040178571428572</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:13">
       <c r="A106" t="s">
         <v>23</v>
       </c>
@@ -4775,31 +5057,31 @@
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E106" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F106">
         <v>0.453125</v>
       </c>
-      <c r="G106">
+      <c r="I106">
         <v>5.638777027187902E-05</v>
       </c>
-      <c r="H106">
+      <c r="J106">
         <v>0.9453124999999998</v>
       </c>
-      <c r="I106">
-        <v>8</v>
-      </c>
-      <c r="J106">
-        <v>8</v>
-      </c>
       <c r="K106">
+        <v>8</v>
+      </c>
+      <c r="L106">
+        <v>8</v>
+      </c>
+      <c r="M106">
         <v>0.9453124999999998</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:13">
       <c r="A107" t="s">
         <v>33</v>
       </c>
@@ -4810,28 +5092,34 @@
         <v>0</v>
       </c>
       <c r="D107" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E107" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F107">
         <v>0.8333333333333334</v>
       </c>
+      <c r="G107">
+        <v>0.5934465623571782</v>
+      </c>
       <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="J107">
         <v>0.04262404262404262</v>
       </c>
-      <c r="I107">
+      <c r="K107">
         <v>6</v>
       </c>
-      <c r="J107">
-        <v>8</v>
-      </c>
-      <c r="K107">
+      <c r="L107">
+        <v>8</v>
+      </c>
+      <c r="M107">
         <v>0.6393606393606394</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:13">
       <c r="A108" t="s">
         <v>33</v>
       </c>
@@ -4842,28 +5130,34 @@
         <v>0</v>
       </c>
       <c r="D108" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E108" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F108">
         <v>0.7083333333333334</v>
       </c>
+      <c r="G108">
+        <v>0.3978215499456805</v>
+      </c>
       <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="J108">
         <v>0.2284382284382285</v>
       </c>
-      <c r="I108">
+      <c r="K108">
         <v>6</v>
       </c>
-      <c r="J108">
-        <v>8</v>
-      </c>
-      <c r="K108">
+      <c r="L108">
+        <v>8</v>
+      </c>
+      <c r="M108">
         <v>0.8471528471528473</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:13">
       <c r="A109" t="s">
         <v>33</v>
       </c>
@@ -4874,28 +5168,34 @@
         <v>0</v>
       </c>
       <c r="D109" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E109" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F109">
         <v>0.6875</v>
       </c>
+      <c r="G109">
+        <v>0.3408865807228488</v>
+      </c>
       <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="J109">
         <v>0.2823842823842824</v>
       </c>
-      <c r="I109">
+      <c r="K109">
         <v>6</v>
       </c>
-      <c r="J109">
-        <v>8</v>
-      </c>
-      <c r="K109">
+      <c r="L109">
+        <v>8</v>
+      </c>
+      <c r="M109">
         <v>0.8471528471528473</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:13">
       <c r="A110" t="s">
         <v>33</v>
       </c>
@@ -4906,28 +5206,34 @@
         <v>0</v>
       </c>
       <c r="D110" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E110" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F110">
         <v>0.3125</v>
       </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
       <c r="H110">
+        <v>0.653292228224337</v>
+      </c>
+      <c r="J110">
         <v>0.2823842823842824</v>
       </c>
-      <c r="I110">
+      <c r="K110">
         <v>6</v>
       </c>
-      <c r="J110">
-        <v>8</v>
-      </c>
-      <c r="K110">
+      <c r="L110">
+        <v>8</v>
+      </c>
+      <c r="M110">
         <v>0.8471528471528473</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:13">
       <c r="A111" t="s">
         <v>33</v>
       </c>
@@ -4938,28 +5244,34 @@
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E111" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F111">
         <v>0.3125</v>
       </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
       <c r="H111">
+        <v>0.639889005382374</v>
+      </c>
+      <c r="J111">
         <v>0.2823842823842824</v>
       </c>
-      <c r="I111">
+      <c r="K111">
         <v>6</v>
       </c>
-      <c r="J111">
-        <v>8</v>
-      </c>
-      <c r="K111">
+      <c r="L111">
+        <v>8</v>
+      </c>
+      <c r="M111">
         <v>0.8471528471528473</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:13">
       <c r="A112" t="s">
         <v>33</v>
       </c>
@@ -4970,28 +5282,34 @@
         <v>0</v>
       </c>
       <c r="D112" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E112" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F112">
         <v>0.625</v>
       </c>
+      <c r="G112">
+        <v>0.269833642034704</v>
+      </c>
       <c r="H112">
+        <v>0.9801663579652961</v>
+      </c>
+      <c r="J112">
         <v>0.4908424908424909</v>
       </c>
-      <c r="I112">
+      <c r="K112">
         <v>6</v>
       </c>
-      <c r="J112">
-        <v>8</v>
-      </c>
-      <c r="K112">
+      <c r="L112">
+        <v>8</v>
+      </c>
+      <c r="M112">
         <v>0.9546009546009547</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:13">
       <c r="A113" t="s">
         <v>33</v>
       </c>
@@ -5002,28 +5320,34 @@
         <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E113" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F113">
         <v>0.3958333333333333</v>
       </c>
+      <c r="G113">
+        <v>0.0550411051089964</v>
+      </c>
       <c r="H113">
+        <v>0.7366255615576702</v>
+      </c>
+      <c r="J113">
         <v>0.5727605727605728</v>
       </c>
-      <c r="I113">
+      <c r="K113">
         <v>6</v>
       </c>
-      <c r="J113">
-        <v>8</v>
-      </c>
-      <c r="K113">
+      <c r="L113">
+        <v>8</v>
+      </c>
+      <c r="M113">
         <v>0.9546009546009547</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:13">
       <c r="A114" t="s">
         <v>33</v>
       </c>
@@ -5034,28 +5358,34 @@
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E114" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F114">
         <v>0.6041666666666666</v>
       </c>
+      <c r="G114">
+        <v>0.2698663135289662</v>
+      </c>
       <c r="H114">
+        <v>0.9384670198043671</v>
+      </c>
+      <c r="J114">
         <v>0.5727605727605728</v>
       </c>
-      <c r="I114">
+      <c r="K114">
         <v>6</v>
       </c>
-      <c r="J114">
-        <v>8</v>
-      </c>
-      <c r="K114">
+      <c r="L114">
+        <v>8</v>
+      </c>
+      <c r="M114">
         <v>0.9546009546009547</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:13">
       <c r="A115" t="s">
         <v>33</v>
       </c>
@@ -5066,28 +5396,34 @@
         <v>0</v>
       </c>
       <c r="D115" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E115" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F115">
         <v>0.3958333333333333</v>
       </c>
+      <c r="G115">
+        <v>0.04921991405618208</v>
+      </c>
       <c r="H115">
+        <v>0.7424467526104845</v>
+      </c>
+      <c r="J115">
         <v>0.5727605727605728</v>
       </c>
-      <c r="I115">
+      <c r="K115">
         <v>6</v>
       </c>
-      <c r="J115">
-        <v>8</v>
-      </c>
-      <c r="K115">
+      <c r="L115">
+        <v>8</v>
+      </c>
+      <c r="M115">
         <v>0.9546009546009547</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:13">
       <c r="A116" t="s">
         <v>33</v>
       </c>
@@ -5098,28 +5434,34 @@
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E116" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F116">
         <v>0.4166666666666667</v>
       </c>
+      <c r="G116">
+        <v>0.02892602137359861</v>
+      </c>
       <c r="H116">
+        <v>0.8044073119597348</v>
+      </c>
+      <c r="J116">
         <v>0.662004662004662</v>
       </c>
-      <c r="I116">
+      <c r="K116">
         <v>6</v>
       </c>
-      <c r="J116">
-        <v>8</v>
-      </c>
-      <c r="K116">
+      <c r="L116">
+        <v>8</v>
+      </c>
+      <c r="M116">
         <v>0.993006993006993</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:13">
       <c r="A117" t="s">
         <v>33</v>
       </c>
@@ -5130,28 +5472,34 @@
         <v>0</v>
       </c>
       <c r="D117" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E117" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F117">
         <v>0.5416666666666666</v>
       </c>
+      <c r="G117">
+        <v>0.1835616877720909</v>
+      </c>
       <c r="H117">
+        <v>0.8997716455612423</v>
+      </c>
+      <c r="J117">
         <v>0.8518148518148518</v>
       </c>
-      <c r="I117">
+      <c r="K117">
         <v>6</v>
       </c>
-      <c r="J117">
-        <v>8</v>
-      </c>
-      <c r="K117">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11">
+      <c r="L117">
+        <v>8</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13">
       <c r="A118" t="s">
         <v>33</v>
       </c>
@@ -5162,28 +5510,34 @@
         <v>0</v>
       </c>
       <c r="D118" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E118" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F118">
         <v>0.5416666666666666</v>
       </c>
+      <c r="G118">
+        <v>0.2015740742207652</v>
+      </c>
       <c r="H118">
+        <v>0.8817592591125681</v>
+      </c>
+      <c r="J118">
         <v>0.8518148518148518</v>
       </c>
-      <c r="I118">
+      <c r="K118">
         <v>6</v>
       </c>
-      <c r="J118">
-        <v>8</v>
-      </c>
-      <c r="K118">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11">
+      <c r="L118">
+        <v>8</v>
+      </c>
+      <c r="M118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13">
       <c r="A119" t="s">
         <v>33</v>
       </c>
@@ -5194,28 +5548,34 @@
         <v>0</v>
       </c>
       <c r="D119" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E119" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F119">
         <v>0.4791666666666667</v>
       </c>
+      <c r="G119">
+        <v>0.1383744384423298</v>
+      </c>
       <c r="H119">
+        <v>0.8199588948910036</v>
+      </c>
+      <c r="J119">
         <v>0.9497169497169498</v>
       </c>
-      <c r="I119">
+      <c r="K119">
         <v>6</v>
       </c>
-      <c r="J119">
-        <v>8</v>
-      </c>
-      <c r="K119">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11">
+      <c r="L119">
+        <v>8</v>
+      </c>
+      <c r="M119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13">
       <c r="A120" t="s">
         <v>33</v>
       </c>
@@ -5226,28 +5586,34 @@
         <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E120" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F120">
         <v>0.4791666666666667</v>
       </c>
+      <c r="G120">
+        <v>0.1367011441190805</v>
+      </c>
       <c r="H120">
+        <v>0.821632189214253</v>
+      </c>
+      <c r="J120">
         <v>0.9497169497169498</v>
       </c>
-      <c r="I120">
+      <c r="K120">
         <v>6</v>
       </c>
-      <c r="J120">
-        <v>8</v>
-      </c>
-      <c r="K120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11">
+      <c r="L120">
+        <v>8</v>
+      </c>
+      <c r="M120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13">
       <c r="A121" t="s">
         <v>33</v>
       </c>
@@ -5258,24 +5624,30 @@
         <v>0</v>
       </c>
       <c r="D121" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E121" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F121">
         <v>0.5</v>
       </c>
+      <c r="G121">
+        <v>0.1329607286706863</v>
+      </c>
       <c r="H121">
-        <v>1</v>
-      </c>
-      <c r="I121">
+        <v>0.8670392713293138</v>
+      </c>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="K121">
         <v>6</v>
       </c>
-      <c r="J121">
-        <v>8</v>
-      </c>
-      <c r="K121">
+      <c r="L121">
+        <v>8</v>
+      </c>
+      <c r="M121">
         <v>1</v>
       </c>
     </row>
@@ -5297,21 +5669,21 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -5322,13 +5694,13 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -5339,13 +5711,13 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -5356,13 +5728,13 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5373,13 +5745,13 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -5390,13 +5762,13 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -5407,13 +5779,13 @@
         <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -5424,13 +5796,13 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -5441,13 +5813,13 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -5458,13 +5830,13 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -5475,13 +5847,13 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C12">
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5492,13 +5864,13 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13">
         <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5509,13 +5881,13 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C14">
         <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5533,24 +5905,24 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -5565,596 +5937,596 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" t="s">
         <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B34" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B36" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C37" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B39" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C39" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B40" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B41" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C41" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B42" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B43" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C43" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B45" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B46" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B47" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C47" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C48" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B49" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C49" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B50" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C50" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C51" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C52" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B53" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C53" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B54" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C54" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/04_Network/03_Classify/c_data/03_classify.xlsx
+++ b/04_Network/03_Classify/c_data/03_classify.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="180">
   <si>
     <t>sheet</t>
   </si>
@@ -36,7 +36,7 @@
     <t>auc</t>
   </si>
   <si>
-    <t>Per module and task: AUC, median paired change (paired tasks), Wilcoxon p and BH FDR.</t>
+    <t>Per module and task: AUC, median paired change (paired tasks), Wilcoxon p, BH and Storey q.</t>
   </si>
   <si>
     <t>plot_index</t>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t>fdr</t>
+  </si>
+  <si>
+    <t>qvalue</t>
   </si>
   <si>
     <t>blue</t>
@@ -1227,10 +1230,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1">
+    <row r="1" spans="1:14" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -1270,8 +1273,11 @@
       <c r="M1" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1282,10 +1288,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2">
         <v>0.163265306122449</v>
@@ -1305,8 +1311,11 @@
       <c r="M2">
         <v>0.2343750000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2">
+        <v>0.2343750000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1317,10 +1326,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3">
         <v>0.9183673469387755</v>
@@ -1340,8 +1349,11 @@
       <c r="M3">
         <v>0.2343750000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3">
+        <v>0.2343750000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1352,10 +1364,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F4">
         <v>0.6122448979591837</v>
@@ -1375,8 +1387,11 @@
       <c r="M4">
         <v>0.2343750000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4">
+        <v>0.2343750000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1387,10 +1402,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F5">
         <v>0.7755102040816326</v>
@@ -1410,8 +1425,11 @@
       <c r="M5">
         <v>0.4101562500000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5">
+        <v>0.4101562500000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1422,10 +1440,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6">
         <v>0.2448979591836735</v>
@@ -1445,8 +1463,11 @@
       <c r="M6">
         <v>0.4687500000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6">
+        <v>0.4687500000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1457,10 +1478,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7">
         <v>0.6530612244897959</v>
@@ -1480,8 +1501,11 @@
       <c r="M7">
         <v>0.4687500000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>0.4687500000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1492,10 +1516,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F8">
         <v>0.2040816326530612</v>
@@ -1515,8 +1539,11 @@
       <c r="M8">
         <v>0.4687500000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8">
+        <v>0.4687500000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1527,10 +1554,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F9">
         <v>0.2448979591836735</v>
@@ -1550,8 +1577,11 @@
       <c r="M9">
         <v>0.5566406250000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9">
+        <v>0.5566406250000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1562,10 +1592,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F10">
         <v>0.6938775510204082</v>
@@ -1585,8 +1615,11 @@
       <c r="M10">
         <v>0.7883522727272728</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10">
+        <v>0.7883522727272728</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1597,10 +1630,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F11">
         <v>0.6326530612244898</v>
@@ -1620,8 +1653,11 @@
       <c r="M11">
         <v>0.7883522727272728</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11">
+        <v>0.7883522727272728</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1632,10 +1668,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12">
         <v>0.4489795918367347</v>
@@ -1655,8 +1691,11 @@
       <c r="M12">
         <v>0.7883522727272728</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12">
+        <v>0.7883522727272728</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1667,10 +1706,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F13">
         <v>0.4489795918367347</v>
@@ -1690,8 +1729,11 @@
       <c r="M13">
         <v>0.8125000000000001</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13">
+        <v>0.8125000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1702,10 +1744,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F14">
         <v>0.5102040816326531</v>
@@ -1725,8 +1767,11 @@
       <c r="M14">
         <v>0.8125000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N14">
+        <v>0.8125000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1737,10 +1782,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F15">
         <v>0.5714285714285714</v>
@@ -1760,8 +1805,11 @@
       <c r="M15">
         <v>0.8125000000000001</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15">
+        <v>0.8125000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1772,10 +1820,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F16">
         <v>0.5918367346938775</v>
@@ -1795,8 +1843,11 @@
       <c r="M16">
         <v>0.8125000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16">
+        <v>0.8125000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -1807,10 +1858,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F17">
         <v>0.171875</v>
@@ -1830,8 +1881,11 @@
       <c r="M17">
         <v>0.03906250000000001</v>
       </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17">
+        <v>0.03906250000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -1842,10 +1896,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18">
         <v>0.734375</v>
@@ -1865,8 +1919,11 @@
       <c r="M18">
         <v>0.03906250000000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18">
+        <v>0.03906250000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1877,10 +1934,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F19">
         <v>0.09375</v>
@@ -1900,8 +1957,11 @@
       <c r="M19">
         <v>0.03906250000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19">
+        <v>0.03906250000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1912,10 +1972,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F20">
         <v>0.84375</v>
@@ -1935,8 +1995,11 @@
       <c r="M20">
         <v>0.05859375000000001</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20">
+        <v>0.05859375000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1947,10 +2010,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F21">
         <v>0.171875</v>
@@ -1970,8 +2033,11 @@
       <c r="M21">
         <v>0.05859375000000001</v>
       </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21">
+        <v>0.05859375000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -1982,10 +2048,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F22">
         <v>0.671875</v>
@@ -2005,8 +2071,11 @@
       <c r="M22">
         <v>0.05859375000000001</v>
       </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22">
+        <v>0.05859375000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -2017,10 +2086,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23">
         <v>0.78125</v>
@@ -2040,8 +2109,11 @@
       <c r="M23">
         <v>0.1822916666666667</v>
       </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23">
+        <v>0.1822916666666667</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -2052,10 +2124,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F24">
         <v>0.734375</v>
@@ -2075,8 +2147,11 @@
       <c r="M24">
         <v>0.1822916666666667</v>
       </c>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24">
+        <v>0.1822916666666667</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2087,10 +2162,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25">
         <v>0.125</v>
@@ -2110,8 +2185,11 @@
       <c r="M25">
         <v>0.1822916666666667</v>
       </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25">
+        <v>0.1822916666666667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -2122,10 +2200,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F26">
         <v>0.328125</v>
@@ -2145,8 +2223,11 @@
       <c r="M26">
         <v>0.5742187500000001</v>
       </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26">
+        <v>0.5742187500000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -2157,10 +2238,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F27">
         <v>0.625</v>
@@ -2180,8 +2261,11 @@
       <c r="M27">
         <v>0.7457386363636365</v>
       </c>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27">
+        <v>0.7457386363636365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -2192,10 +2276,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F28">
         <v>0.625</v>
@@ -2215,8 +2299,11 @@
       <c r="M28">
         <v>0.9040178571428572</v>
       </c>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="N28">
+        <v>0.9040178571428572</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -2227,10 +2314,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F29">
         <v>0.515625</v>
@@ -2250,8 +2337,11 @@
       <c r="M29">
         <v>0.9040178571428572</v>
       </c>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29">
+        <v>0.9040178571428572</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -2262,10 +2352,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F30">
         <v>0.484375</v>
@@ -2285,8 +2375,11 @@
       <c r="M30">
         <v>0.9040178571428572</v>
       </c>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30">
+        <v>0.9040178571428572</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -2297,10 +2390,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F31">
         <v>0.46875</v>
@@ -2320,8 +2413,11 @@
       <c r="M31">
         <v>0.9453124999999998</v>
       </c>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="N31">
+        <v>0.9453124999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -2332,10 +2428,10 @@
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32">
         <v>0.9464285714285714</v>
@@ -2358,8 +2454,11 @@
       <c r="M32">
         <v>0.03263403263403263</v>
       </c>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="N32">
+        <v>0.03263403263403263</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -2370,10 +2469,10 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F33">
         <v>0.8035714285714286</v>
@@ -2396,8 +2495,11 @@
       <c r="M33">
         <v>0.2703962703962704</v>
       </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33">
+        <v>0.2703962703962704</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -2408,10 +2510,10 @@
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F34">
         <v>0.1964285714285714</v>
@@ -2434,8 +2536,11 @@
       <c r="M34">
         <v>0.2703962703962704</v>
       </c>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="N34">
+        <v>0.2703962703962704</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -2446,10 +2551,10 @@
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F35">
         <v>0.2321428571428572</v>
@@ -2472,8 +2577,11 @@
       <c r="M35">
         <v>0.351981351981352</v>
       </c>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="N35">
+        <v>0.351981351981352</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -2484,10 +2592,10 @@
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F36">
         <v>0.7142857142857143</v>
@@ -2510,8 +2618,11 @@
       <c r="M36">
         <v>0.5678321678321678</v>
       </c>
-    </row>
-    <row r="37" spans="1:13">
+      <c r="N36">
+        <v>0.5678321678321678</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -2522,10 +2633,10 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F37">
         <v>0.3571428571428572</v>
@@ -2548,8 +2659,11 @@
       <c r="M37">
         <v>0.6614866614866616</v>
       </c>
-    </row>
-    <row r="38" spans="1:13">
+      <c r="N37">
+        <v>0.6614866614866616</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
         <v>35</v>
       </c>
@@ -2560,10 +2674,10 @@
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F38">
         <v>0.3571428571428572</v>
@@ -2586,8 +2700,11 @@
       <c r="M38">
         <v>0.6614866614866616</v>
       </c>
-    </row>
-    <row r="39" spans="1:13">
+      <c r="N38">
+        <v>0.6614866614866616</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
         <v>35</v>
       </c>
@@ -2598,10 +2715,10 @@
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F39">
         <v>0.6428571428571429</v>
@@ -2624,8 +2741,11 @@
       <c r="M39">
         <v>0.6614866614866616</v>
       </c>
-    </row>
-    <row r="40" spans="1:13">
+      <c r="N39">
+        <v>0.6614866614866616</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
         <v>35</v>
       </c>
@@ -2636,10 +2756,10 @@
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F40">
         <v>0.6428571428571429</v>
@@ -2662,8 +2782,11 @@
       <c r="M40">
         <v>0.6614866614866616</v>
       </c>
-    </row>
-    <row r="41" spans="1:13">
+      <c r="N40">
+        <v>0.6614866614866616</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
         <v>35</v>
       </c>
@@ -2674,10 +2797,10 @@
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F41">
         <v>0.4107142857142857</v>
@@ -2700,8 +2823,11 @@
       <c r="M41">
         <v>0.8665112665112666</v>
       </c>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="N41">
+        <v>0.8665112665112666</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
         <v>35</v>
       </c>
@@ -2712,10 +2838,10 @@
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F42">
         <v>0.4464285714285715</v>
@@ -2738,8 +2864,11 @@
       <c r="M42">
         <v>0.8665112665112666</v>
       </c>
-    </row>
-    <row r="43" spans="1:13">
+      <c r="N42">
+        <v>0.8665112665112666</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -2750,10 +2879,10 @@
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F43">
         <v>0.4464285714285715</v>
@@ -2776,8 +2905,11 @@
       <c r="M43">
         <v>0.8665112665112666</v>
       </c>
-    </row>
-    <row r="44" spans="1:13">
+      <c r="N43">
+        <v>0.8665112665112666</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -2788,10 +2920,10 @@
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F44">
         <v>0.4642857142857143</v>
@@ -2814,8 +2946,11 @@
       <c r="M44">
         <v>0.8665112665112666</v>
       </c>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="N44">
+        <v>0.8665112665112666</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
         <v>35</v>
       </c>
@@ -2826,10 +2961,10 @@
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F45">
         <v>0.5357142857142857</v>
@@ -2852,8 +2987,11 @@
       <c r="M45">
         <v>0.8665112665112666</v>
       </c>
-    </row>
-    <row r="46" spans="1:13">
+      <c r="N45">
+        <v>0.8665112665112666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
         <v>35</v>
       </c>
@@ -2864,10 +3002,10 @@
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E46" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F46">
         <v>0.4642857142857143</v>
@@ -2890,8 +3028,11 @@
       <c r="M46">
         <v>0.8665112665112666</v>
       </c>
-    </row>
-    <row r="47" spans="1:13">
+      <c r="N46">
+        <v>0.8665112665112666</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
         <v>29</v>
       </c>
@@ -2902,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F47">
         <v>0.8571428571428571</v>
@@ -2928,8 +3069,11 @@
       <c r="M47">
         <v>0.3076923076923077</v>
       </c>
-    </row>
-    <row r="48" spans="1:13">
+      <c r="N47">
+        <v>0.3076923076923077</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
         <v>29</v>
       </c>
@@ -2940,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F48">
         <v>0.7321428571428571</v>
@@ -2966,8 +3110,11 @@
       <c r="M48">
         <v>0.6951048951048951</v>
       </c>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="N48">
+        <v>0.6951048951048951</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -2978,10 +3125,10 @@
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F49">
         <v>0.2857142857142857</v>
@@ -3004,8 +3151,11 @@
       <c r="M49">
         <v>0.6951048951048951</v>
       </c>
-    </row>
-    <row r="50" spans="1:13">
+      <c r="N49">
+        <v>0.6951048951048951</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
         <v>29</v>
       </c>
@@ -3016,10 +3166,10 @@
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F50">
         <v>0.7142857142857143</v>
@@ -3042,8 +3192,11 @@
       <c r="M50">
         <v>0.6951048951048951</v>
       </c>
-    </row>
-    <row r="51" spans="1:13">
+      <c r="N50">
+        <v>0.6951048951048951</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
         <v>29</v>
       </c>
@@ -3054,10 +3207,10 @@
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F51">
         <v>0.6964285714285714</v>
@@ -3080,8 +3233,11 @@
       <c r="M51">
         <v>0.6951048951048951</v>
       </c>
-    </row>
-    <row r="52" spans="1:13">
+      <c r="N51">
+        <v>0.6951048951048951</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
         <v>29</v>
       </c>
@@ -3092,10 +3248,10 @@
         <v>0</v>
       </c>
       <c r="D52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F52">
         <v>0.3214285714285715</v>
@@ -3118,8 +3274,11 @@
       <c r="M52">
         <v>0.6951048951048951</v>
       </c>
-    </row>
-    <row r="53" spans="1:13">
+      <c r="N52">
+        <v>0.6951048951048951</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" t="s">
         <v>29</v>
       </c>
@@ -3130,10 +3289,10 @@
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F53">
         <v>0.6428571428571429</v>
@@ -3156,8 +3315,11 @@
       <c r="M53">
         <v>0.6951048951048951</v>
       </c>
-    </row>
-    <row r="54" spans="1:13">
+      <c r="N53">
+        <v>0.6951048951048951</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -3168,10 +3330,10 @@
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F54">
         <v>0.3571428571428572</v>
@@ -3194,8 +3356,11 @@
       <c r="M54">
         <v>0.6951048951048951</v>
       </c>
-    </row>
-    <row r="55" spans="1:13">
+      <c r="N54">
+        <v>0.6951048951048951</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
         <v>29</v>
       </c>
@@ -3206,10 +3371,10 @@
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F55">
         <v>0.375</v>
@@ -3232,8 +3397,11 @@
       <c r="M55">
         <v>0.6951048951048951</v>
       </c>
-    </row>
-    <row r="56" spans="1:13">
+      <c r="N55">
+        <v>0.6951048951048951</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -3244,10 +3412,10 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E56" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F56">
         <v>0.625</v>
@@ -3270,8 +3438,11 @@
       <c r="M56">
         <v>0.6951048951048951</v>
       </c>
-    </row>
-    <row r="57" spans="1:13">
+      <c r="N56">
+        <v>0.6951048951048951</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -3282,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E57" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F57">
         <v>0.4464285714285715</v>
@@ -3308,8 +3479,11 @@
       <c r="M57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:13">
+      <c r="N57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" t="s">
         <v>29</v>
       </c>
@@ -3320,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F58">
         <v>0.5178571428571429</v>
@@ -3346,8 +3520,11 @@
       <c r="M58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:13">
+      <c r="N58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59" t="s">
         <v>29</v>
       </c>
@@ -3358,10 +3535,10 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E59" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F59">
         <v>0.5178571428571429</v>
@@ -3384,8 +3561,11 @@
       <c r="M59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:13">
+      <c r="N59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" t="s">
         <v>29</v>
       </c>
@@ -3396,10 +3576,10 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E60" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F60">
         <v>0.4821428571428572</v>
@@ -3422,8 +3602,11 @@
       <c r="M60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:13">
+      <c r="N60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" t="s">
         <v>29</v>
       </c>
@@ -3434,10 +3617,10 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F61">
         <v>0.5</v>
@@ -3460,8 +3643,11 @@
       <c r="M61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:13">
+      <c r="N61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62" t="s">
         <v>31</v>
       </c>
@@ -3472,10 +3658,10 @@
         <v>0</v>
       </c>
       <c r="D62" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E62" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F62">
         <v>0.7857142857142857</v>
@@ -3498,8 +3684,11 @@
       <c r="M62">
         <v>0.7097902097902099</v>
       </c>
-    </row>
-    <row r="63" spans="1:13">
+      <c r="N62">
+        <v>0.7097902097902099</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63" t="s">
         <v>31</v>
       </c>
@@ -3510,10 +3699,10 @@
         <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F63">
         <v>0.75</v>
@@ -3536,8 +3725,11 @@
       <c r="M63">
         <v>0.7097902097902099</v>
       </c>
-    </row>
-    <row r="64" spans="1:13">
+      <c r="N63">
+        <v>0.7097902097902099</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64" t="s">
         <v>31</v>
       </c>
@@ -3548,10 +3740,10 @@
         <v>0</v>
       </c>
       <c r="D64" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E64" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F64">
         <v>0.2678571428571428</v>
@@ -3574,8 +3766,11 @@
       <c r="M64">
         <v>0.7097902097902099</v>
       </c>
-    </row>
-    <row r="65" spans="1:13">
+      <c r="N64">
+        <v>0.7097902097902099</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65" t="s">
         <v>31</v>
       </c>
@@ -3586,10 +3781,10 @@
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F65">
         <v>0.2857142857142857</v>
@@ -3612,8 +3807,11 @@
       <c r="M65">
         <v>0.7097902097902099</v>
       </c>
-    </row>
-    <row r="66" spans="1:13">
+      <c r="N65">
+        <v>0.7097902097902099</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66" t="s">
         <v>31</v>
       </c>
@@ -3624,10 +3822,10 @@
         <v>0</v>
       </c>
       <c r="D66" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E66" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F66">
         <v>0.6428571428571429</v>
@@ -3650,8 +3848,11 @@
       <c r="M66">
         <v>0.7441724941724943</v>
       </c>
-    </row>
-    <row r="67" spans="1:13">
+      <c r="N66">
+        <v>0.7441724941724943</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
       <c r="A67" t="s">
         <v>31</v>
       </c>
@@ -3662,10 +3863,10 @@
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E67" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F67">
         <v>0.6428571428571429</v>
@@ -3688,8 +3889,11 @@
       <c r="M67">
         <v>0.7441724941724943</v>
       </c>
-    </row>
-    <row r="68" spans="1:13">
+      <c r="N67">
+        <v>0.7441724941724943</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68" t="s">
         <v>31</v>
       </c>
@@ -3700,10 +3904,10 @@
         <v>0</v>
       </c>
       <c r="D68" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E68" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F68">
         <v>0.6428571428571429</v>
@@ -3726,8 +3930,11 @@
       <c r="M68">
         <v>0.7441724941724943</v>
       </c>
-    </row>
-    <row r="69" spans="1:13">
+      <c r="N68">
+        <v>0.7441724941724943</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69" t="s">
         <v>31</v>
       </c>
@@ -3738,10 +3945,10 @@
         <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E69" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F69">
         <v>0.3571428571428572</v>
@@ -3764,8 +3971,11 @@
       <c r="M69">
         <v>0.7441724941724943</v>
       </c>
-    </row>
-    <row r="70" spans="1:13">
+      <c r="N69">
+        <v>0.7441724941724943</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70" t="s">
         <v>31</v>
       </c>
@@ -3776,10 +3986,10 @@
         <v>0</v>
       </c>
       <c r="D70" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E70" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F70">
         <v>0.375</v>
@@ -3802,8 +4012,11 @@
       <c r="M70">
         <v>0.7723387723387725</v>
       </c>
-    </row>
-    <row r="71" spans="1:13">
+      <c r="N70">
+        <v>0.7723387723387725</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71" t="s">
         <v>31</v>
       </c>
@@ -3814,10 +4027,10 @@
         <v>0</v>
       </c>
       <c r="D71" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E71" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F71">
         <v>0.5714285714285714</v>
@@ -3840,8 +4053,11 @@
       <c r="M71">
         <v>0.867909867909868</v>
       </c>
-    </row>
-    <row r="72" spans="1:13">
+      <c r="N71">
+        <v>0.867909867909868</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72" t="s">
         <v>31</v>
       </c>
@@ -3852,10 +4068,10 @@
         <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E72" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F72">
         <v>0.5714285714285714</v>
@@ -3878,8 +4094,11 @@
       <c r="M72">
         <v>0.867909867909868</v>
       </c>
-    </row>
-    <row r="73" spans="1:13">
+      <c r="N72">
+        <v>0.867909867909868</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73" t="s">
         <v>31</v>
       </c>
@@ -3890,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E73" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F73">
         <v>0.4285714285714285</v>
@@ -3916,8 +4135,11 @@
       <c r="M73">
         <v>0.867909867909868</v>
       </c>
-    </row>
-    <row r="74" spans="1:13">
+      <c r="N73">
+        <v>0.867909867909868</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74" t="s">
         <v>31</v>
       </c>
@@ -3928,10 +4150,10 @@
         <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E74" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F74">
         <v>0.4642857142857143</v>
@@ -3954,8 +4176,11 @@
       <c r="M74">
         <v>0.9284049284049285</v>
       </c>
-    </row>
-    <row r="75" spans="1:13">
+      <c r="N74">
+        <v>0.9284049284049285</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75" t="s">
         <v>31</v>
       </c>
@@ -3966,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E75" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F75">
         <v>0.4642857142857143</v>
@@ -3992,8 +4217,11 @@
       <c r="M75">
         <v>0.9284049284049285</v>
       </c>
-    </row>
-    <row r="76" spans="1:13">
+      <c r="N75">
+        <v>0.9284049284049285</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
       <c r="A76" t="s">
         <v>31</v>
       </c>
@@ -4004,10 +4232,10 @@
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E76" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F76">
         <v>0.4821428571428572</v>
@@ -4030,8 +4258,11 @@
       <c r="M76">
         <v>0.9550893550893552</v>
       </c>
-    </row>
-    <row r="77" spans="1:13">
+      <c r="N76">
+        <v>0.9550893550893552</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
       <c r="A77" t="s">
         <v>21</v>
       </c>
@@ -4042,10 +4273,10 @@
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E77" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F77">
         <v>0.8611111111111112</v>
@@ -4065,8 +4296,11 @@
       <c r="M77">
         <v>0.7812500000000002</v>
       </c>
-    </row>
-    <row r="78" spans="1:13">
+      <c r="N77">
+        <v>0.7812500000000002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
       <c r="A78" t="s">
         <v>21</v>
       </c>
@@ -4077,10 +4311,10 @@
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E78" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F78">
         <v>0.8333333333333334</v>
@@ -4100,8 +4334,11 @@
       <c r="M78">
         <v>0.7812500000000002</v>
       </c>
-    </row>
-    <row r="79" spans="1:13">
+      <c r="N78">
+        <v>0.7812500000000002</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
       <c r="A79" t="s">
         <v>21</v>
       </c>
@@ -4112,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E79" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F79">
         <v>0.3333333333333333</v>
@@ -4135,8 +4372,11 @@
       <c r="M79">
         <v>0.7812500000000002</v>
       </c>
-    </row>
-    <row r="80" spans="1:13">
+      <c r="N79">
+        <v>0.7812500000000002</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
       <c r="A80" t="s">
         <v>21</v>
       </c>
@@ -4147,10 +4387,10 @@
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E80" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F80">
         <v>0.6944444444444444</v>
@@ -4170,8 +4410,11 @@
       <c r="M80">
         <v>0.7812500000000002</v>
       </c>
-    </row>
-    <row r="81" spans="1:13">
+      <c r="N80">
+        <v>0.7812500000000002</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81" t="s">
         <v>21</v>
       </c>
@@ -4182,10 +4425,10 @@
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E81" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F81">
         <v>0.2777777777777778</v>
@@ -4205,8 +4448,11 @@
       <c r="M81">
         <v>0.7812500000000002</v>
       </c>
-    </row>
-    <row r="82" spans="1:13">
+      <c r="N81">
+        <v>0.7812500000000002</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
       <c r="A82" t="s">
         <v>21</v>
       </c>
@@ -4217,10 +4463,10 @@
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E82" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F82">
         <v>0.1944444444444444</v>
@@ -4240,8 +4486,11 @@
       <c r="M82">
         <v>0.7812500000000002</v>
       </c>
-    </row>
-    <row r="83" spans="1:13">
+      <c r="N82">
+        <v>0.7812500000000002</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
       <c r="A83" t="s">
         <v>21</v>
       </c>
@@ -4252,10 +4501,10 @@
         <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E83" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F83">
         <v>0.6666666666666666</v>
@@ -4275,8 +4524,11 @@
       <c r="M83">
         <v>0.8437500000000003</v>
       </c>
-    </row>
-    <row r="84" spans="1:13">
+      <c r="N83">
+        <v>0.8437500000000003</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
       <c r="A84" t="s">
         <v>21</v>
       </c>
@@ -4287,10 +4539,10 @@
         <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E84" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F84">
         <v>0.5555555555555556</v>
@@ -4310,8 +4562,11 @@
       <c r="M84">
         <v>0.8437500000000003</v>
       </c>
-    </row>
-    <row r="85" spans="1:13">
+      <c r="N84">
+        <v>0.8437500000000003</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
       <c r="A85" t="s">
         <v>21</v>
       </c>
@@ -4322,10 +4577,10 @@
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E85" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F85">
         <v>0.6944444444444444</v>
@@ -4345,8 +4600,11 @@
       <c r="M85">
         <v>0.8437500000000003</v>
       </c>
-    </row>
-    <row r="86" spans="1:13">
+      <c r="N85">
+        <v>0.8437500000000003</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
       <c r="A86" t="s">
         <v>21</v>
       </c>
@@ -4357,10 +4615,10 @@
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E86" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F86">
         <v>0.6388888888888888</v>
@@ -4380,8 +4638,11 @@
       <c r="M86">
         <v>0.8437500000000003</v>
       </c>
-    </row>
-    <row r="87" spans="1:13">
+      <c r="N86">
+        <v>0.8437500000000003</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
       <c r="A87" t="s">
         <v>21</v>
       </c>
@@ -4392,10 +4653,10 @@
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E87" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F87">
         <v>0.4722222222222222</v>
@@ -4415,8 +4676,11 @@
       <c r="M87">
         <v>0.8437500000000003</v>
       </c>
-    </row>
-    <row r="88" spans="1:13">
+      <c r="N87">
+        <v>0.8437500000000003</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
       <c r="A88" t="s">
         <v>21</v>
       </c>
@@ -4427,10 +4691,10 @@
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E88" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F88">
         <v>0.5277777777777778</v>
@@ -4450,8 +4714,11 @@
       <c r="M88">
         <v>0.8437500000000003</v>
       </c>
-    </row>
-    <row r="89" spans="1:13">
+      <c r="N88">
+        <v>0.8437500000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
       <c r="A89" t="s">
         <v>21</v>
       </c>
@@ -4462,10 +4729,10 @@
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E89" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F89">
         <v>0.6666666666666666</v>
@@ -4485,8 +4752,11 @@
       <c r="M89">
         <v>0.8437500000000003</v>
       </c>
-    </row>
-    <row r="90" spans="1:13">
+      <c r="N89">
+        <v>0.8437500000000003</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
       <c r="A90" t="s">
         <v>21</v>
       </c>
@@ -4497,10 +4767,10 @@
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E90" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F90">
         <v>0.3333333333333333</v>
@@ -4520,8 +4790,11 @@
       <c r="M90">
         <v>0.8437500000000003</v>
       </c>
-    </row>
-    <row r="91" spans="1:13">
+      <c r="N90">
+        <v>0.8437500000000003</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
       <c r="A91" t="s">
         <v>21</v>
       </c>
@@ -4532,10 +4805,10 @@
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E91" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F91">
         <v>0.5</v>
@@ -4555,8 +4828,11 @@
       <c r="M91">
         <v>0.8437500000000003</v>
       </c>
-    </row>
-    <row r="92" spans="1:13">
+      <c r="N91">
+        <v>0.8437500000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
       <c r="A92" t="s">
         <v>23</v>
       </c>
@@ -4567,10 +4843,10 @@
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E92" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F92">
         <v>0.734375</v>
@@ -4590,8 +4866,11 @@
       <c r="M92">
         <v>0.8735795454545455</v>
       </c>
-    </row>
-    <row r="93" spans="1:13">
+      <c r="N92">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
       <c r="A93" t="s">
         <v>23</v>
       </c>
@@ -4602,10 +4881,10 @@
         <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E93" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F93">
         <v>0.609375</v>
@@ -4625,8 +4904,11 @@
       <c r="M93">
         <v>0.8735795454545455</v>
       </c>
-    </row>
-    <row r="94" spans="1:13">
+      <c r="N93">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
       <c r="A94" t="s">
         <v>23</v>
       </c>
@@ -4637,10 +4919,10 @@
         <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E94" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F94">
         <v>0.65625</v>
@@ -4660,8 +4942,11 @@
       <c r="M94">
         <v>0.8735795454545455</v>
       </c>
-    </row>
-    <row r="95" spans="1:13">
+      <c r="N94">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
       <c r="A95" t="s">
         <v>23</v>
       </c>
@@ -4672,10 +4957,10 @@
         <v>1</v>
       </c>
       <c r="D95" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E95" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F95">
         <v>0.59375</v>
@@ -4695,8 +4980,11 @@
       <c r="M95">
         <v>0.8735795454545455</v>
       </c>
-    </row>
-    <row r="96" spans="1:13">
+      <c r="N95">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
       <c r="A96" t="s">
         <v>23</v>
       </c>
@@ -4707,10 +4995,10 @@
         <v>1</v>
       </c>
       <c r="D96" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E96" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F96">
         <v>0.390625</v>
@@ -4730,8 +5018,11 @@
       <c r="M96">
         <v>0.8735795454545455</v>
       </c>
-    </row>
-    <row r="97" spans="1:13">
+      <c r="N96">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
       <c r="A97" t="s">
         <v>23</v>
       </c>
@@ -4742,10 +5033,10 @@
         <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E97" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F97">
         <v>0.390625</v>
@@ -4765,8 +5056,11 @@
       <c r="M97">
         <v>0.8735795454545455</v>
       </c>
-    </row>
-    <row r="98" spans="1:13">
+      <c r="N97">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
       <c r="A98" t="s">
         <v>23</v>
       </c>
@@ -4777,10 +5071,10 @@
         <v>1</v>
       </c>
       <c r="D98" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E98" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F98">
         <v>0.4375</v>
@@ -4800,8 +5094,11 @@
       <c r="M98">
         <v>0.8735795454545455</v>
       </c>
-    </row>
-    <row r="99" spans="1:13">
+      <c r="N98">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
       <c r="A99" t="s">
         <v>23</v>
       </c>
@@ -4812,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E99" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F99">
         <v>0.421875</v>
@@ -4835,8 +5132,11 @@
       <c r="M99">
         <v>0.8735795454545455</v>
       </c>
-    </row>
-    <row r="100" spans="1:13">
+      <c r="N99">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
       <c r="A100" t="s">
         <v>23</v>
       </c>
@@ -4847,10 +5147,10 @@
         <v>1</v>
       </c>
       <c r="D100" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E100" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F100">
         <v>0.34375</v>
@@ -4870,8 +5170,11 @@
       <c r="M100">
         <v>0.8735795454545455</v>
       </c>
-    </row>
-    <row r="101" spans="1:13">
+      <c r="N100">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
       <c r="A101" t="s">
         <v>23</v>
       </c>
@@ -4882,10 +5185,10 @@
         <v>1</v>
       </c>
       <c r="D101" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E101" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F101">
         <v>0.65625</v>
@@ -4905,8 +5208,11 @@
       <c r="M101">
         <v>0.8735795454545455</v>
       </c>
-    </row>
-    <row r="102" spans="1:13">
+      <c r="N101">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
       <c r="A102" t="s">
         <v>23</v>
       </c>
@@ -4917,10 +5223,10 @@
         <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E102" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F102">
         <v>0.625</v>
@@ -4940,8 +5246,11 @@
       <c r="M102">
         <v>0.8735795454545455</v>
       </c>
-    </row>
-    <row r="103" spans="1:13">
+      <c r="N102">
+        <v>0.8735795454545455</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
       <c r="A103" t="s">
         <v>23</v>
       </c>
@@ -4952,10 +5261,10 @@
         <v>1</v>
       </c>
       <c r="D103" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E103" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F103">
         <v>0.578125</v>
@@ -4975,8 +5284,11 @@
       <c r="M103">
         <v>0.9040178571428572</v>
       </c>
-    </row>
-    <row r="104" spans="1:13">
+      <c r="N103">
+        <v>0.9040178571428572</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
       <c r="A104" t="s">
         <v>23</v>
       </c>
@@ -4987,10 +5299,10 @@
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E104" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F104">
         <v>0.515625</v>
@@ -5010,8 +5322,11 @@
       <c r="M104">
         <v>0.9040178571428572</v>
       </c>
-    </row>
-    <row r="105" spans="1:13">
+      <c r="N104">
+        <v>0.9040178571428572</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
       <c r="A105" t="s">
         <v>23</v>
       </c>
@@ -5022,10 +5337,10 @@
         <v>1</v>
       </c>
       <c r="D105" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E105" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F105">
         <v>0.453125</v>
@@ -5045,8 +5360,11 @@
       <c r="M105">
         <v>0.9040178571428572</v>
       </c>
-    </row>
-    <row r="106" spans="1:13">
+      <c r="N105">
+        <v>0.9040178571428572</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14">
       <c r="A106" t="s">
         <v>23</v>
       </c>
@@ -5057,10 +5375,10 @@
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E106" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F106">
         <v>0.453125</v>
@@ -5080,8 +5398,11 @@
       <c r="M106">
         <v>0.9453124999999998</v>
       </c>
-    </row>
-    <row r="107" spans="1:13">
+      <c r="N106">
+        <v>0.9453124999999998</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14">
       <c r="A107" t="s">
         <v>33</v>
       </c>
@@ -5092,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="D107" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E107" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F107">
         <v>0.8333333333333334</v>
@@ -5118,8 +5439,11 @@
       <c r="M107">
         <v>0.6393606393606394</v>
       </c>
-    </row>
-    <row r="108" spans="1:13">
+      <c r="N107">
+        <v>0.6393606393606394</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14">
       <c r="A108" t="s">
         <v>33</v>
       </c>
@@ -5130,10 +5454,10 @@
         <v>0</v>
       </c>
       <c r="D108" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E108" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F108">
         <v>0.7083333333333334</v>
@@ -5156,8 +5480,11 @@
       <c r="M108">
         <v>0.8471528471528473</v>
       </c>
-    </row>
-    <row r="109" spans="1:13">
+      <c r="N108">
+        <v>0.8471528471528473</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14">
       <c r="A109" t="s">
         <v>33</v>
       </c>
@@ -5168,10 +5495,10 @@
         <v>0</v>
       </c>
       <c r="D109" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E109" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F109">
         <v>0.6875</v>
@@ -5194,8 +5521,11 @@
       <c r="M109">
         <v>0.8471528471528473</v>
       </c>
-    </row>
-    <row r="110" spans="1:13">
+      <c r="N109">
+        <v>0.8471528471528473</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14">
       <c r="A110" t="s">
         <v>33</v>
       </c>
@@ -5206,10 +5536,10 @@
         <v>0</v>
       </c>
       <c r="D110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F110">
         <v>0.3125</v>
@@ -5232,8 +5562,11 @@
       <c r="M110">
         <v>0.8471528471528473</v>
       </c>
-    </row>
-    <row r="111" spans="1:13">
+      <c r="N110">
+        <v>0.8471528471528473</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14">
       <c r="A111" t="s">
         <v>33</v>
       </c>
@@ -5244,10 +5577,10 @@
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E111" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F111">
         <v>0.3125</v>
@@ -5270,8 +5603,11 @@
       <c r="M111">
         <v>0.8471528471528473</v>
       </c>
-    </row>
-    <row r="112" spans="1:13">
+      <c r="N111">
+        <v>0.8471528471528473</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14">
       <c r="A112" t="s">
         <v>33</v>
       </c>
@@ -5282,10 +5618,10 @@
         <v>0</v>
       </c>
       <c r="D112" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E112" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F112">
         <v>0.625</v>
@@ -5308,8 +5644,11 @@
       <c r="M112">
         <v>0.9546009546009547</v>
       </c>
-    </row>
-    <row r="113" spans="1:13">
+      <c r="N112">
+        <v>0.9546009546009547</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14">
       <c r="A113" t="s">
         <v>33</v>
       </c>
@@ -5320,10 +5659,10 @@
         <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E113" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F113">
         <v>0.3958333333333333</v>
@@ -5346,8 +5685,11 @@
       <c r="M113">
         <v>0.9546009546009547</v>
       </c>
-    </row>
-    <row r="114" spans="1:13">
+      <c r="N113">
+        <v>0.9546009546009547</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14">
       <c r="A114" t="s">
         <v>33</v>
       </c>
@@ -5358,10 +5700,10 @@
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E114" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F114">
         <v>0.6041666666666666</v>
@@ -5384,8 +5726,11 @@
       <c r="M114">
         <v>0.9546009546009547</v>
       </c>
-    </row>
-    <row r="115" spans="1:13">
+      <c r="N114">
+        <v>0.9546009546009547</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14">
       <c r="A115" t="s">
         <v>33</v>
       </c>
@@ -5396,10 +5741,10 @@
         <v>0</v>
       </c>
       <c r="D115" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E115" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F115">
         <v>0.3958333333333333</v>
@@ -5422,8 +5767,11 @@
       <c r="M115">
         <v>0.9546009546009547</v>
       </c>
-    </row>
-    <row r="116" spans="1:13">
+      <c r="N115">
+        <v>0.9546009546009547</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14">
       <c r="A116" t="s">
         <v>33</v>
       </c>
@@ -5434,10 +5782,10 @@
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E116" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F116">
         <v>0.4166666666666667</v>
@@ -5460,8 +5808,11 @@
       <c r="M116">
         <v>0.993006993006993</v>
       </c>
-    </row>
-    <row r="117" spans="1:13">
+      <c r="N116">
+        <v>0.993006993006993</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14">
       <c r="A117" t="s">
         <v>33</v>
       </c>
@@ -5472,10 +5823,10 @@
         <v>0</v>
       </c>
       <c r="D117" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E117" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F117">
         <v>0.5416666666666666</v>
@@ -5498,8 +5849,11 @@
       <c r="M117">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:13">
+      <c r="N117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14">
       <c r="A118" t="s">
         <v>33</v>
       </c>
@@ -5510,10 +5864,10 @@
         <v>0</v>
       </c>
       <c r="D118" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E118" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F118">
         <v>0.5416666666666666</v>
@@ -5536,8 +5890,11 @@
       <c r="M118">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:13">
+      <c r="N118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14">
       <c r="A119" t="s">
         <v>33</v>
       </c>
@@ -5548,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="D119" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E119" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F119">
         <v>0.4791666666666667</v>
@@ -5574,8 +5931,11 @@
       <c r="M119">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:13">
+      <c r="N119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14">
       <c r="A120" t="s">
         <v>33</v>
       </c>
@@ -5586,10 +5946,10 @@
         <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E120" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F120">
         <v>0.4791666666666667</v>
@@ -5612,8 +5972,11 @@
       <c r="M120">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:13">
+      <c r="N120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14">
       <c r="A121" t="s">
         <v>33</v>
       </c>
@@ -5624,10 +5987,10 @@
         <v>0</v>
       </c>
       <c r="D121" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E121" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F121">
         <v>0.5</v>
@@ -5648,6 +6011,9 @@
         <v>8</v>
       </c>
       <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="N121">
         <v>1</v>
       </c>
     </row>
@@ -5669,21 +6035,21 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -5694,13 +6060,13 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -5711,13 +6077,13 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -5728,13 +6094,13 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5745,13 +6111,13 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -5762,13 +6128,13 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -5779,13 +6145,13 @@
         <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -5796,13 +6162,13 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -5813,13 +6179,13 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -5830,13 +6196,13 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -5847,13 +6213,13 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12">
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5864,13 +6230,13 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13">
         <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5881,13 +6247,13 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14">
         <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5905,24 +6271,24 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -5937,596 +6303,596 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
         <v>78</v>
-      </c>
-      <c r="B4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B38" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C41" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C44" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C46" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C49" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C52" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B54" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C54" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/04_Network/03_Classify/c_data/03_classify.xlsx
+++ b/04_Network/03_Classify/c_data/03_classify.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="175">
   <si>
     <t>sheet</t>
   </si>
@@ -156,51 +156,36 @@
     <t>qvalue</t>
   </si>
   <si>
+    <t>turquoise</t>
+  </si>
+  <si>
     <t>blue</t>
   </si>
   <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>brown</t>
+  </si>
+  <si>
     <t>purple</t>
   </si>
   <si>
-    <t>turquoise</t>
+    <t>black</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>magenta</t>
+  </si>
+  <si>
+    <t>yellow</t>
   </si>
   <si>
     <t>pink</t>
   </si>
   <si>
-    <t>brown</t>
-  </si>
-  <si>
-    <t>green</t>
-  </si>
-  <si>
-    <t>magenta</t>
-  </si>
-  <si>
-    <t>salmon</t>
-  </si>
-  <si>
-    <t>black</t>
-  </si>
-  <si>
-    <t>greenyellow</t>
-  </si>
-  <si>
-    <t>red</t>
-  </si>
-  <si>
-    <t>cyan</t>
-  </si>
-  <si>
-    <t>midnightblue</t>
-  </si>
-  <si>
-    <t>tan</t>
-  </si>
-  <si>
-    <t>yellow</t>
-  </si>
-  <si>
     <t>pdf_page</t>
   </si>
   <si>
@@ -228,7 +213,7 @@
     <t>04_Network/01_Build_Modules/c_data/modules.rds</t>
   </si>
   <si>
-    <t>78dd0603e90231fb458e53f5f2d172b9</t>
+    <t>25cd43ced16098e9558525cfe4c1ef5e</t>
   </si>
   <si>
     <t>package</t>
@@ -1011,7 +996,7 @@
         <v>0.03125</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1040,7 +1025,7 @@
         <v>0.0078125</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1069,10 +1054,10 @@
         <v>0.015625</v>
       </c>
       <c r="G4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1098,13 +1083,13 @@
         <v>0.0078125</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1127,10 +1112,10 @@
         <v>0.0003108003108003108</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1156,7 +1141,7 @@
         <v>0.0003108003108003108</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1185,10 +1170,10 @@
         <v>0.000666000666000666</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1214,13 +1199,13 @@
         <v>0.0003108003108003108</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1230,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N121"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1">
@@ -1294,10 +1279,10 @@
         <v>45</v>
       </c>
       <c r="F2">
-        <v>0.163265306122449</v>
+        <v>0.1224489795918367</v>
       </c>
       <c r="I2">
-        <v>-0.1895446333247326</v>
+        <v>-0.1631883480763229</v>
       </c>
       <c r="J2">
         <v>0.015625</v>
@@ -1309,10 +1294,10 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>0.2343750000000001</v>
+        <v>0.15625</v>
       </c>
       <c r="N2">
-        <v>0.2343750000000001</v>
+        <v>0.15625</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1332,13 +1317,13 @@
         <v>46</v>
       </c>
       <c r="F3">
-        <v>0.9183673469387755</v>
+        <v>0.6122448979591837</v>
       </c>
       <c r="I3">
-        <v>0.2017200455808207</v>
+        <v>0.04173642723174621</v>
       </c>
       <c r="J3">
-        <v>0.04687500000000001</v>
+        <v>0.07812500000000003</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -1347,10 +1332,10 @@
         <v>7</v>
       </c>
       <c r="M3">
-        <v>0.2343750000000001</v>
+        <v>0.2187500000000001</v>
       </c>
       <c r="N3">
-        <v>0.2343750000000001</v>
+        <v>0.2187500000000001</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1370,13 +1355,13 @@
         <v>47</v>
       </c>
       <c r="F4">
-        <v>0.6122448979591837</v>
+        <v>0.7959183673469388</v>
       </c>
       <c r="I4">
-        <v>0.04052501671806824</v>
+        <v>0.1584973608866614</v>
       </c>
       <c r="J4">
-        <v>0.04687500000000001</v>
+        <v>0.07812500000000003</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -1385,10 +1370,10 @@
         <v>7</v>
       </c>
       <c r="M4">
-        <v>0.2343750000000001</v>
+        <v>0.2187500000000001</v>
       </c>
       <c r="N4">
-        <v>0.2343750000000001</v>
+        <v>0.2187500000000001</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1408,10 +1393,10 @@
         <v>48</v>
       </c>
       <c r="F5">
-        <v>0.7755102040816326</v>
+        <v>0.2244897959183673</v>
       </c>
       <c r="I5">
-        <v>0.12256369925543</v>
+        <v>-0.1642253936163896</v>
       </c>
       <c r="J5">
         <v>0.109375</v>
@@ -1423,10 +1408,10 @@
         <v>7</v>
       </c>
       <c r="M5">
-        <v>0.4101562500000001</v>
+        <v>0.2187500000000001</v>
       </c>
       <c r="N5">
-        <v>0.4101562500000001</v>
+        <v>0.2187500000000001</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1446,25 +1431,25 @@
         <v>49</v>
       </c>
       <c r="F6">
-        <v>0.2448979591836735</v>
+        <v>0.7551020408163265</v>
       </c>
       <c r="I6">
-        <v>-0.1596588599641741</v>
+        <v>0.24427926241918</v>
       </c>
       <c r="J6">
+        <v>0.109375</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
         <v>0.2187500000000001</v>
       </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>0.4687500000000001</v>
-      </c>
       <c r="N6">
-        <v>0.4687500000000001</v>
+        <v>0.2187500000000001</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1484,13 +1469,13 @@
         <v>50</v>
       </c>
       <c r="F7">
-        <v>0.6530612244897959</v>
+        <v>0.7959183673469388</v>
       </c>
       <c r="I7">
-        <v>0.1692604200258208</v>
+        <v>0.1587285173271667</v>
       </c>
       <c r="J7">
-        <v>0.2187500000000001</v>
+        <v>0.15625</v>
       </c>
       <c r="K7">
         <v>7</v>
@@ -1499,10 +1484,10 @@
         <v>7</v>
       </c>
       <c r="M7">
-        <v>0.4687500000000001</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="N7">
-        <v>0.4687500000000001</v>
+        <v>0.2604166666666667</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1522,13 +1507,13 @@
         <v>51</v>
       </c>
       <c r="F8">
-        <v>0.2040816326530612</v>
+        <v>0.673469387755102</v>
       </c>
       <c r="I8">
-        <v>-0.07909445693915869</v>
+        <v>0.05829043031481017</v>
       </c>
       <c r="J8">
-        <v>0.2187500000000001</v>
+        <v>0.2968750000000001</v>
       </c>
       <c r="K8">
         <v>7</v>
@@ -1537,10 +1522,10 @@
         <v>7</v>
       </c>
       <c r="M8">
-        <v>0.4687500000000001</v>
+        <v>0.424107142857143</v>
       </c>
       <c r="N8">
-        <v>0.4687500000000001</v>
+        <v>0.424107142857143</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1560,13 +1545,13 @@
         <v>52</v>
       </c>
       <c r="F9">
-        <v>0.2448979591836735</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="I9">
-        <v>-0.04210645234594217</v>
+        <v>-0.06910386693429196</v>
       </c>
       <c r="J9">
-        <v>0.2968750000000001</v>
+        <v>0.4687500000000001</v>
       </c>
       <c r="K9">
         <v>7</v>
@@ -1575,10 +1560,10 @@
         <v>7</v>
       </c>
       <c r="M9">
-        <v>0.5566406250000001</v>
+        <v>0.5859375000000001</v>
       </c>
       <c r="N9">
-        <v>0.5566406250000001</v>
+        <v>0.5859375000000001</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1598,10 +1583,10 @@
         <v>53</v>
       </c>
       <c r="F10">
-        <v>0.6938775510204082</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="I10">
-        <v>0.05695789805693754</v>
+        <v>-0.003149896836118618</v>
       </c>
       <c r="J10">
         <v>0.5781250000000001</v>
@@ -1613,10 +1598,10 @@
         <v>7</v>
       </c>
       <c r="M10">
-        <v>0.7883522727272728</v>
+        <v>0.6423611111111113</v>
       </c>
       <c r="N10">
-        <v>0.7883522727272728</v>
+        <v>0.6423611111111113</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1636,13 +1621,13 @@
         <v>54</v>
       </c>
       <c r="F11">
-        <v>0.6326530612244898</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="I11">
-        <v>-0.07482199314333263</v>
+        <v>0.03855612192826063</v>
       </c>
       <c r="J11">
-        <v>0.5781250000000001</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>7</v>
@@ -1651,200 +1636,200 @@
         <v>7</v>
       </c>
       <c r="M11">
-        <v>0.7883522727272728</v>
+        <v>1</v>
       </c>
       <c r="N11">
-        <v>0.7883522727272728</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" t="b">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F12">
-        <v>0.4489795918367347</v>
+        <v>0.796875</v>
       </c>
       <c r="I12">
-        <v>-0.08432245695934777</v>
+        <v>0.105919289094324</v>
       </c>
       <c r="J12">
-        <v>0.5781250000000001</v>
+        <v>0.007812500000000002</v>
       </c>
       <c r="K12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>0.7883522727272728</v>
+        <v>0.03906250000000001</v>
       </c>
       <c r="N12">
-        <v>0.7883522727272728</v>
+        <v>0.03906250000000001</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F13">
-        <v>0.4489795918367347</v>
+        <v>0.25</v>
       </c>
       <c r="I13">
-        <v>-0.01489577072963743</v>
+        <v>-0.08389092646089329</v>
       </c>
       <c r="J13">
-        <v>0.8125000000000001</v>
+        <v>0.007812500000000002</v>
       </c>
       <c r="K13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>0.8125000000000001</v>
+        <v>0.03906250000000001</v>
       </c>
       <c r="N13">
-        <v>0.8125000000000001</v>
+        <v>0.03906250000000001</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" t="b">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F14">
-        <v>0.5102040816326531</v>
+        <v>0.796875</v>
       </c>
       <c r="I14">
-        <v>0.01932100864239882</v>
+        <v>0.1008109718001743</v>
       </c>
       <c r="J14">
-        <v>0.8125000000000001</v>
+        <v>0.07812500000000001</v>
       </c>
       <c r="K14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>0.8125000000000001</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="N14">
-        <v>0.8125000000000001</v>
+        <v>0.2604166666666667</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C15" t="b">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F15">
-        <v>0.5714285714285714</v>
+        <v>0.734375</v>
       </c>
       <c r="I15">
-        <v>-0.05241491163505533</v>
+        <v>0.1004499458660228</v>
       </c>
       <c r="J15">
-        <v>0.8125000000000001</v>
+        <v>0.1484375</v>
       </c>
       <c r="K15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>0.8125000000000001</v>
+        <v>0.3710937500000001</v>
       </c>
       <c r="N15">
-        <v>0.8125000000000001</v>
+        <v>0.3710937500000001</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" t="b">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F16">
-        <v>0.5918367346938775</v>
+        <v>0.203125</v>
       </c>
       <c r="I16">
-        <v>-0.007881495365692354</v>
+        <v>-0.1014399092514522</v>
       </c>
       <c r="J16">
-        <v>0.8125000000000001</v>
+        <v>0.1953125</v>
       </c>
       <c r="K16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>0.8125000000000001</v>
+        <v>0.3906250000000001</v>
       </c>
       <c r="N16">
-        <v>0.8125000000000001</v>
+        <v>0.3906250000000001</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1858,19 +1843,19 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F17">
-        <v>0.171875</v>
+        <v>0.609375</v>
       </c>
       <c r="I17">
-        <v>-0.09400482455360595</v>
+        <v>0.1280532934180013</v>
       </c>
       <c r="J17">
-        <v>0.007812500000000002</v>
+        <v>0.2500000000000001</v>
       </c>
       <c r="K17">
         <v>8</v>
@@ -1879,10 +1864,10 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>0.03906250000000001</v>
+        <v>0.3906250000000001</v>
       </c>
       <c r="N17">
-        <v>0.03906250000000001</v>
+        <v>0.3906250000000001</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1896,19 +1881,19 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F18">
-        <v>0.734375</v>
+        <v>0.3125</v>
       </c>
       <c r="I18">
-        <v>0.1162682800547686</v>
+        <v>-0.09632178564207593</v>
       </c>
       <c r="J18">
-        <v>0.007812500000000002</v>
+        <v>0.3125000000000001</v>
       </c>
       <c r="K18">
         <v>8</v>
@@ -1917,10 +1902,10 @@
         <v>8</v>
       </c>
       <c r="M18">
-        <v>0.03906250000000001</v>
+        <v>0.3906250000000001</v>
       </c>
       <c r="N18">
-        <v>0.03906250000000001</v>
+        <v>0.3906250000000001</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1934,19 +1919,19 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F19">
-        <v>0.09375</v>
+        <v>0.328125</v>
       </c>
       <c r="I19">
-        <v>-0.1637012459851492</v>
+        <v>-0.04480551280497284</v>
       </c>
       <c r="J19">
-        <v>0.007812500000000002</v>
+        <v>0.3125000000000001</v>
       </c>
       <c r="K19">
         <v>8</v>
@@ -1955,10 +1940,10 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>0.03906250000000001</v>
+        <v>0.3906250000000001</v>
       </c>
       <c r="N19">
-        <v>0.03906250000000001</v>
+        <v>0.3906250000000001</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1972,19 +1957,19 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F20">
-        <v>0.84375</v>
+        <v>0.4375</v>
       </c>
       <c r="I20">
-        <v>0.1074234467393508</v>
+        <v>-0.04330327845684476</v>
       </c>
       <c r="J20">
-        <v>0.015625</v>
+        <v>0.3828125000000001</v>
       </c>
       <c r="K20">
         <v>8</v>
@@ -1993,10 +1978,10 @@
         <v>8</v>
       </c>
       <c r="M20">
-        <v>0.05859375000000001</v>
+        <v>0.4253472222222223</v>
       </c>
       <c r="N20">
-        <v>0.05859375000000001</v>
+        <v>0.4253472222222223</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -2010,19 +1995,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F21">
-        <v>0.171875</v>
+        <v>0.390625</v>
       </c>
       <c r="I21">
-        <v>-0.1267924341333494</v>
+        <v>-0.114464079878509</v>
       </c>
       <c r="J21">
-        <v>0.02343750000000001</v>
+        <v>0.5468750000000001</v>
       </c>
       <c r="K21">
         <v>8</v>
@@ -2031,97 +2016,103 @@
         <v>8</v>
       </c>
       <c r="M21">
-        <v>0.05859375000000001</v>
+        <v>0.5468750000000001</v>
       </c>
       <c r="N21">
-        <v>0.05859375000000001</v>
+        <v>0.5468750000000001</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F22">
-        <v>0.671875</v>
-      </c>
-      <c r="I22">
-        <v>0.07580347806601506</v>
+        <v>0.7678571428571429</v>
+      </c>
+      <c r="G22">
+        <v>0.5106654459095371</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0.02343750000000001</v>
+        <v>0.09386169386169387</v>
       </c>
       <c r="K22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>8</v>
       </c>
       <c r="M22">
-        <v>0.05859375000000001</v>
+        <v>0.5594405594405596</v>
       </c>
       <c r="N22">
-        <v>0.05859375000000001</v>
+        <v>0.5594405594405596</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F23">
-        <v>0.78125</v>
-      </c>
-      <c r="I23">
-        <v>0.09568584612090247</v>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0.6048478893963298</v>
       </c>
       <c r="J23">
-        <v>0.109375</v>
+        <v>0.1892773892773893</v>
       </c>
       <c r="K23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>8</v>
       </c>
       <c r="M23">
-        <v>0.1822916666666667</v>
+        <v>0.5594405594405596</v>
       </c>
       <c r="N23">
-        <v>0.1822916666666667</v>
+        <v>0.5594405594405596</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="s">
         <v>46</v>
@@ -2130,226 +2121,244 @@
         <v>46</v>
       </c>
       <c r="F24">
-        <v>0.734375</v>
-      </c>
-      <c r="I24">
-        <v>0.1183212516935555</v>
+        <v>0.6964285714285714</v>
+      </c>
+      <c r="G24">
+        <v>0.3862864562454674</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0.109375</v>
+        <v>0.2318570318570319</v>
       </c>
       <c r="K24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>8</v>
       </c>
       <c r="M24">
-        <v>0.1822916666666667</v>
+        <v>0.5594405594405596</v>
       </c>
       <c r="N24">
-        <v>0.1822916666666667</v>
+        <v>0.5594405594405596</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F25">
-        <v>0.125</v>
-      </c>
-      <c r="I25">
-        <v>-0.2204579449312783</v>
+        <v>0.3214285714285715</v>
+      </c>
+      <c r="G25">
+        <v>0.02297970397885189</v>
+      </c>
+      <c r="H25">
+        <v>0.6198774388782911</v>
       </c>
       <c r="J25">
-        <v>0.109375</v>
+        <v>0.280963480963481</v>
       </c>
       <c r="K25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>8</v>
       </c>
       <c r="M25">
-        <v>0.1822916666666667</v>
+        <v>0.5594405594405596</v>
       </c>
       <c r="N25">
-        <v>0.1822916666666667</v>
+        <v>0.5594405594405596</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F26">
-        <v>0.328125</v>
-      </c>
-      <c r="I26">
-        <v>-0.05309823078175435</v>
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="G26">
+        <v>0.3513160786367077</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>0.3828125000000001</v>
+        <v>0.280963480963481</v>
       </c>
       <c r="K26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>8</v>
       </c>
       <c r="M26">
-        <v>0.5742187500000001</v>
+        <v>0.5594405594405596</v>
       </c>
       <c r="N26">
-        <v>0.5742187500000001</v>
+        <v>0.5594405594405596</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F27">
-        <v>0.625</v>
-      </c>
-      <c r="I27">
-        <v>0.06792911749308136</v>
+        <v>0.6607142857142857</v>
+      </c>
+      <c r="G27">
+        <v>0.351325400824016</v>
+      </c>
+      <c r="H27">
+        <v>0.9701031706045554</v>
       </c>
       <c r="J27">
-        <v>0.5468750000000001</v>
+        <v>0.3356643356643357</v>
       </c>
       <c r="K27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>8</v>
       </c>
       <c r="M27">
-        <v>0.7457386363636365</v>
+        <v>0.5594405594405596</v>
       </c>
       <c r="N27">
-        <v>0.7457386363636365</v>
+        <v>0.5594405594405596</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F28">
-        <v>0.625</v>
-      </c>
-      <c r="I28">
-        <v>0.01427255853272026</v>
+        <v>0.375</v>
+      </c>
+      <c r="G28">
+        <v>0.0552273067847763</v>
+      </c>
+      <c r="H28">
+        <v>0.6947726932152237</v>
       </c>
       <c r="J28">
-        <v>0.7421875000000001</v>
+        <v>0.4634032634032634</v>
       </c>
       <c r="K28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>8</v>
       </c>
       <c r="M28">
-        <v>0.9040178571428572</v>
+        <v>0.662004662004662</v>
       </c>
       <c r="N28">
-        <v>0.9040178571428572</v>
+        <v>0.662004662004662</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F29">
-        <v>0.515625</v>
-      </c>
-      <c r="I29">
-        <v>-0.0052395554723993</v>
+        <v>0.4107142857142857</v>
+      </c>
+      <c r="G29">
+        <v>0.08695334355565193</v>
+      </c>
+      <c r="H29">
+        <v>0.7344752278729194</v>
       </c>
       <c r="J29">
-        <v>0.8437500000000001</v>
+        <v>0.6125874125874127</v>
       </c>
       <c r="K29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>8</v>
       </c>
       <c r="M29">
-        <v>0.9040178571428572</v>
+        <v>0.7657342657342658</v>
       </c>
       <c r="N29">
-        <v>0.9040178571428572</v>
+        <v>0.7657342657342658</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="s">
         <v>47</v>
@@ -2358,92 +2367,98 @@
         <v>47</v>
       </c>
       <c r="F30">
-        <v>0.484375</v>
-      </c>
-      <c r="I30">
-        <v>-0.09822736654899855</v>
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="G30">
+        <v>0.218965732331447</v>
+      </c>
+      <c r="H30">
+        <v>0.8524628390971244</v>
       </c>
       <c r="J30">
-        <v>0.8437500000000001</v>
+        <v>0.8665112665112666</v>
       </c>
       <c r="K30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>8</v>
       </c>
       <c r="M30">
-        <v>0.9040178571428572</v>
+        <v>0.9550893550893552</v>
       </c>
       <c r="N30">
-        <v>0.9040178571428572</v>
+        <v>0.9550893550893552</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F31">
-        <v>0.46875</v>
-      </c>
-      <c r="I31">
-        <v>0.02726510512914805</v>
+        <v>0.4821428571428572</v>
+      </c>
+      <c r="G31">
+        <v>0.1433275961452411</v>
+      </c>
+      <c r="H31">
+        <v>0.8209581181404731</v>
       </c>
       <c r="J31">
-        <v>0.9453124999999998</v>
+        <v>0.9550893550893552</v>
       </c>
       <c r="K31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>8</v>
       </c>
       <c r="M31">
-        <v>0.9453124999999998</v>
+        <v>0.9550893550893552</v>
       </c>
       <c r="N31">
-        <v>0.9453124999999998</v>
+        <v>0.9550893550893552</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F32">
-        <v>0.9464285714285714</v>
+        <v>0.7321428571428571</v>
       </c>
       <c r="G32">
-        <v>0.8428286733498574</v>
+        <v>0.4559233864950541</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="J32">
-        <v>0.002175602175602176</v>
+        <v>0.151981351981352</v>
       </c>
       <c r="K32">
         <v>7</v>
@@ -2452,39 +2467,39 @@
         <v>8</v>
       </c>
       <c r="M32">
-        <v>0.03263403263403263</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="N32">
-        <v>0.03263403263403263</v>
+        <v>0.9550893550893549</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E33" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F33">
-        <v>0.8035714285714286</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="G33">
-        <v>0.5450225100788212</v>
+        <v>0.02210148079325802</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0.6207556620638849</v>
       </c>
       <c r="J33">
-        <v>0.05407925407925408</v>
+        <v>0.280963480963481</v>
       </c>
       <c r="K33">
         <v>7</v>
@@ -2493,39 +2508,39 @@
         <v>8</v>
       </c>
       <c r="M33">
-        <v>0.2703962703962704</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="N33">
-        <v>0.2703962703962704</v>
+        <v>0.9550893550893549</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E34" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F34">
-        <v>0.1964285714285714</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>0.340428134237563</v>
       </c>
       <c r="H34">
-        <v>0.4396318325697636</v>
+        <v>0.9452861514767229</v>
       </c>
       <c r="J34">
-        <v>0.05407925407925408</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="K34">
         <v>7</v>
@@ -2534,39 +2549,39 @@
         <v>8</v>
       </c>
       <c r="M34">
-        <v>0.2703962703962704</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="N34">
-        <v>0.2703962703962704</v>
+        <v>0.9550893550893549</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E35" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F35">
-        <v>0.2321428571428572</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>0.3274927849685472</v>
       </c>
       <c r="H35">
-        <v>0.489334554090463</v>
+        <v>0.9582215007457385</v>
       </c>
       <c r="J35">
-        <v>0.09386169386169387</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="K35">
         <v>7</v>
@@ -2575,39 +2590,39 @@
         <v>8</v>
       </c>
       <c r="M35">
-        <v>0.351981351981352</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="N35">
-        <v>0.351981351981352</v>
+        <v>0.9550893550893549</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C36" t="b">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E36" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F36">
-        <v>0.7142857142857143</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="G36">
-        <v>0.4244635050108926</v>
+        <v>0.2957806290631922</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>0.9185050852225219</v>
       </c>
       <c r="J36">
-        <v>0.1892773892773893</v>
+        <v>0.5358197358197359</v>
       </c>
       <c r="K36">
         <v>7</v>
@@ -2616,39 +2631,39 @@
         <v>8</v>
       </c>
       <c r="M36">
-        <v>0.5678321678321678</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="N36">
-        <v>0.5678321678321678</v>
+        <v>0.9550893550893549</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C37" t="b">
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E37" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F37">
-        <v>0.3571428571428572</v>
+        <v>0.4107142857142857</v>
       </c>
       <c r="G37">
-        <v>0.02625368712742985</v>
+        <v>0.1001962405565971</v>
       </c>
       <c r="H37">
-        <v>0.6880320271582845</v>
+        <v>0.7212323308719744</v>
       </c>
       <c r="J37">
-        <v>0.3968919968919969</v>
+        <v>0.6125874125874127</v>
       </c>
       <c r="K37">
         <v>7</v>
@@ -2657,39 +2672,39 @@
         <v>8</v>
       </c>
       <c r="M37">
-        <v>0.6614866614866616</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="N37">
-        <v>0.6614866614866616</v>
+        <v>0.9550893550893549</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C38" t="b">
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F38">
-        <v>0.3571428571428572</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="G38">
-        <v>0.0457806290631923</v>
+        <v>0.1305098075604843</v>
       </c>
       <c r="H38">
-        <v>0.6685050852225221</v>
+        <v>0.7623473352966585</v>
       </c>
       <c r="J38">
-        <v>0.3968919968919969</v>
+        <v>0.7788655788655789</v>
       </c>
       <c r="K38">
         <v>7</v>
@@ -2698,39 +2713,39 @@
         <v>8</v>
       </c>
       <c r="M38">
-        <v>0.6614866614866616</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="N38">
-        <v>0.6614866614866616</v>
+        <v>0.9550893550893549</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C39" t="b">
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E39" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F39">
-        <v>0.6428571428571429</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="G39">
-        <v>0.3353594057888329</v>
+        <v>0.1921122954681302</v>
       </c>
       <c r="H39">
-        <v>0.950354879925453</v>
+        <v>0.8793162759604413</v>
       </c>
       <c r="J39">
-        <v>0.3968919968919969</v>
+        <v>0.8665112665112666</v>
       </c>
       <c r="K39">
         <v>7</v>
@@ -2739,39 +2754,39 @@
         <v>8</v>
       </c>
       <c r="M39">
-        <v>0.6614866614866616</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="N39">
-        <v>0.6614866614866616</v>
+        <v>0.9550893550893549</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C40" t="b">
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F40">
-        <v>0.6428571428571429</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="G40">
-        <v>0.3147117848880667</v>
+        <v>0.2052661250511946</v>
       </c>
       <c r="H40">
-        <v>0.9710025008262191</v>
+        <v>0.8661624463773768</v>
       </c>
       <c r="J40">
-        <v>0.3968919968919969</v>
+        <v>0.8665112665112666</v>
       </c>
       <c r="K40">
         <v>7</v>
@@ -2780,39 +2795,39 @@
         <v>8</v>
       </c>
       <c r="M40">
-        <v>0.6614866614866616</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="N40">
-        <v>0.6614866614866616</v>
+        <v>0.9550893550893549</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C41" t="b">
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F41">
-        <v>0.4107142857142857</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="G41">
-        <v>0.06398588809531608</v>
+        <v>0.1833736281570906</v>
       </c>
       <c r="H41">
-        <v>0.7574426833332553</v>
+        <v>0.8523406575571952</v>
       </c>
       <c r="J41">
-        <v>0.6125874125874127</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="K41">
         <v>7</v>
@@ -2821,39 +2836,39 @@
         <v>8</v>
       </c>
       <c r="M41">
-        <v>0.8665112665112666</v>
+        <v>0.9550893550893549</v>
       </c>
       <c r="N41">
-        <v>0.8665112665112666</v>
+        <v>0.9550893550893549</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C42" t="b">
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F42">
-        <v>0.4464285714285715</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="G42">
-        <v>0.1209605387903666</v>
+        <v>0.02790656713717648</v>
       </c>
       <c r="H42">
-        <v>0.7718966040667763</v>
+        <v>0.6149505757199665</v>
       </c>
       <c r="J42">
-        <v>0.7788655788655789</v>
+        <v>0.280963480963481</v>
       </c>
       <c r="K42">
         <v>7</v>
@@ -2862,39 +2877,39 @@
         <v>8</v>
       </c>
       <c r="M42">
-        <v>0.8665112665112666</v>
+        <v>0.8751248751248752</v>
       </c>
       <c r="N42">
-        <v>0.8665112665112666</v>
+        <v>0.8751248751248752</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C43" t="b">
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E43" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F43">
-        <v>0.4464285714285715</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="G43">
-        <v>0.1223074946289458</v>
+        <v>0.3219009452372791</v>
       </c>
       <c r="H43">
-        <v>0.770549648228197</v>
+        <v>0.9638133404770066</v>
       </c>
       <c r="J43">
-        <v>0.7788655788655789</v>
+        <v>0.3968919968919969</v>
       </c>
       <c r="K43">
         <v>7</v>
@@ -2903,39 +2918,39 @@
         <v>8</v>
       </c>
       <c r="M43">
-        <v>0.8665112665112666</v>
+        <v>0.8751248751248752</v>
       </c>
       <c r="N43">
-        <v>0.8665112665112666</v>
+        <v>0.8751248751248752</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C44" t="b">
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F44">
-        <v>0.4642857142857143</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="G44">
-        <v>0.1477213706034705</v>
+        <v>0.06373555583802107</v>
       </c>
       <c r="H44">
-        <v>0.780850057967958</v>
+        <v>0.7219787298762647</v>
       </c>
       <c r="J44">
-        <v>0.8665112665112666</v>
+        <v>0.5358197358197359</v>
       </c>
       <c r="K44">
         <v>7</v>
@@ -2944,39 +2959,39 @@
         <v>8</v>
       </c>
       <c r="M44">
-        <v>0.8665112665112666</v>
+        <v>0.8751248751248752</v>
       </c>
       <c r="N44">
-        <v>0.8665112665112666</v>
+        <v>0.8751248751248752</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C45" t="b">
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F45">
-        <v>0.5357142857142857</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="G45">
-        <v>0.1559845125452449</v>
+        <v>0.2915935890314613</v>
       </c>
       <c r="H45">
-        <v>0.9154440588833265</v>
+        <v>0.9226921252542529</v>
       </c>
       <c r="J45">
-        <v>0.8665112665112666</v>
+        <v>0.5358197358197359</v>
       </c>
       <c r="K45">
         <v>7</v>
@@ -2985,39 +3000,39 @@
         <v>8</v>
       </c>
       <c r="M45">
-        <v>0.8665112665112666</v>
+        <v>0.8751248751248752</v>
       </c>
       <c r="N45">
-        <v>0.8665112665112666</v>
+        <v>0.8751248751248752</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C46" t="b">
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F46">
-        <v>0.4642857142857143</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="G46">
-        <v>0.1429662384537884</v>
+        <v>0.2780212701237353</v>
       </c>
       <c r="H46">
-        <v>0.7856051901176402</v>
+        <v>0.9362644441619788</v>
       </c>
       <c r="J46">
-        <v>0.8665112665112666</v>
+        <v>0.5358197358197359</v>
       </c>
       <c r="K46">
         <v>7</v>
@@ -3026,39 +3041,39 @@
         <v>8</v>
       </c>
       <c r="M46">
-        <v>0.8665112665112666</v>
+        <v>0.8751248751248752</v>
       </c>
       <c r="N46">
-        <v>0.8665112665112666</v>
+        <v>0.8751248751248752</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C47" t="b">
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E47" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F47">
-        <v>0.8571428571428571</v>
+        <v>0.4107142857142857</v>
       </c>
       <c r="G47">
-        <v>0.6475637891268318</v>
+        <v>0.07833006067301745</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0.7430985107555539</v>
       </c>
       <c r="J47">
-        <v>0.02051282051282051</v>
+        <v>0.6125874125874127</v>
       </c>
       <c r="K47">
         <v>7</v>
@@ -3067,39 +3082,39 @@
         <v>8</v>
       </c>
       <c r="M47">
-        <v>0.3076923076923077</v>
+        <v>0.8751248751248752</v>
       </c>
       <c r="N47">
-        <v>0.3076923076923077</v>
+        <v>0.8751248751248752</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C48" t="b">
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E48" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F48">
-        <v>0.7321428571428571</v>
+        <v>0.5892857142857143</v>
       </c>
       <c r="G48">
-        <v>0.4306797692550272</v>
+        <v>0.2663365434224571</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0.9122348851489716</v>
       </c>
       <c r="J48">
-        <v>0.151981351981352</v>
+        <v>0.6125874125874127</v>
       </c>
       <c r="K48">
         <v>7</v>
@@ -3108,39 +3123,39 @@
         <v>8</v>
       </c>
       <c r="M48">
-        <v>0.6951048951048951</v>
+        <v>0.8751248751248752</v>
       </c>
       <c r="N48">
-        <v>0.6951048951048951</v>
+        <v>0.8751248751248752</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C49" t="b">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E49" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F49">
-        <v>0.2857142857142857</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>0.1226676292699377</v>
       </c>
       <c r="H49">
-        <v>0.5862083479902463</v>
+        <v>0.7701895135872052</v>
       </c>
       <c r="J49">
-        <v>0.1892773892773893</v>
+        <v>0.7788655788655789</v>
       </c>
       <c r="K49">
         <v>7</v>
@@ -3149,39 +3164,39 @@
         <v>8</v>
       </c>
       <c r="M49">
-        <v>0.6951048951048951</v>
+        <v>0.9735819735819737</v>
       </c>
       <c r="N49">
-        <v>0.6951048951048951</v>
+        <v>0.9735819735819737</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C50" t="b">
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E50" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F50">
-        <v>0.7142857142857143</v>
+        <v>0.4821428571428572</v>
       </c>
       <c r="G50">
-        <v>0.4246648403664002</v>
+        <v>0.1524900000652349</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0.8117957142204795</v>
       </c>
       <c r="J50">
-        <v>0.1892773892773893</v>
+        <v>0.9550893550893552</v>
       </c>
       <c r="K50">
         <v>7</v>
@@ -3190,39 +3205,39 @@
         <v>8</v>
       </c>
       <c r="M50">
-        <v>0.6951048951048951</v>
+        <v>1</v>
       </c>
       <c r="N50">
-        <v>0.6951048951048951</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C51" t="b">
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E51" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F51">
-        <v>0.6964285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="G51">
-        <v>0.4088288029685217</v>
+        <v>0.1760589404743549</v>
       </c>
       <c r="H51">
-        <v>0.984028339888621</v>
+        <v>0.8239410595256451</v>
       </c>
       <c r="J51">
-        <v>0.2318570318570319</v>
+        <v>1</v>
       </c>
       <c r="K51">
         <v>7</v>
@@ -3231,226 +3246,211 @@
         <v>8</v>
       </c>
       <c r="M51">
-        <v>0.6951048951048951</v>
+        <v>1</v>
       </c>
       <c r="N51">
-        <v>0.6951048951048951</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E52" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F52">
-        <v>0.3214285714285715</v>
-      </c>
-      <c r="G52">
-        <v>0.02691460079391003</v>
-      </c>
-      <c r="H52">
-        <v>0.6159425420632328</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="I52">
+        <v>0.1100758418500569</v>
       </c>
       <c r="J52">
-        <v>0.280963480963481</v>
+        <v>0.09375000000000004</v>
       </c>
       <c r="K52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L52">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M52">
-        <v>0.6951048951048951</v>
+        <v>0.6250000000000002</v>
       </c>
       <c r="N52">
-        <v>0.6951048951048951</v>
+        <v>0.6250000000000002</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E53" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F53">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="G53">
-        <v>0.321810087146961</v>
-      </c>
-      <c r="H53">
-        <v>0.9639041985673249</v>
+        <v>0.1944444444444444</v>
+      </c>
+      <c r="I53">
+        <v>-0.0966364488910323</v>
       </c>
       <c r="J53">
-        <v>0.3968919968919969</v>
+        <v>0.2187500000000001</v>
       </c>
       <c r="K53">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L53">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M53">
-        <v>0.6951048951048951</v>
+        <v>0.6250000000000002</v>
       </c>
       <c r="N53">
-        <v>0.6951048951048951</v>
+        <v>0.6250000000000002</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E54" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F54">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="G54">
-        <v>0.02170155871430612</v>
-      </c>
-      <c r="H54">
-        <v>0.6925841555714082</v>
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="I54">
+        <v>0.1562375766367236</v>
       </c>
       <c r="J54">
-        <v>0.3968919968919969</v>
+        <v>0.2187500000000001</v>
       </c>
       <c r="K54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L54">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M54">
-        <v>0.6951048951048951</v>
+        <v>0.6250000000000002</v>
       </c>
       <c r="N54">
-        <v>0.6951048951048951</v>
+        <v>0.6250000000000002</v>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E55" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F55">
-        <v>0.375</v>
-      </c>
-      <c r="G55">
-        <v>0.05577501947895173</v>
-      </c>
-      <c r="H55">
-        <v>0.6942249805210483</v>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I55">
+        <v>-0.126096243866158</v>
       </c>
       <c r="J55">
-        <v>0.4634032634032634</v>
+        <v>0.3125000000000001</v>
       </c>
       <c r="K55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L55">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M55">
-        <v>0.6951048951048951</v>
+        <v>0.6250000000000002</v>
       </c>
       <c r="N55">
-        <v>0.6951048951048951</v>
+        <v>0.6250000000000002</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B56" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E56" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F56">
-        <v>0.625</v>
-      </c>
-      <c r="G56">
-        <v>0.2917394638544177</v>
-      </c>
-      <c r="H56">
-        <v>0.9582605361455823</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="I56">
+        <v>0.1430715713199889</v>
       </c>
       <c r="J56">
-        <v>0.4634032634032634</v>
+        <v>0.3125000000000001</v>
       </c>
       <c r="K56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L56">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M56">
-        <v>0.6951048951048951</v>
+        <v>0.6250000000000002</v>
       </c>
       <c r="N56">
-        <v>0.6951048951048951</v>
+        <v>0.6250000000000002</v>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" t="s">
         <v>49</v>
@@ -3459,39 +3459,36 @@
         <v>49</v>
       </c>
       <c r="F57">
-        <v>0.4464285714285715</v>
-      </c>
-      <c r="G57">
-        <v>0.1224875119029264</v>
-      </c>
-      <c r="H57">
-        <v>0.7703696309542165</v>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="I57">
+        <v>-0.04603932312137895</v>
       </c>
       <c r="J57">
-        <v>0.7788655788655789</v>
+        <v>0.4375000000000002</v>
       </c>
       <c r="K57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L57">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M57">
-        <v>1</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="N57">
-        <v>1</v>
+        <v>0.729166666666667</v>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" t="s">
         <v>48</v>
@@ -3500,569 +3497,527 @@
         <v>48</v>
       </c>
       <c r="F58">
-        <v>0.5178571428571429</v>
-      </c>
-      <c r="G58">
-        <v>0.1705404285423149</v>
-      </c>
-      <c r="H58">
-        <v>0.8651738571719709</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I58">
+        <v>0.06612624956927893</v>
       </c>
       <c r="J58">
-        <v>0.9550893550893549</v>
+        <v>0.5625000000000002</v>
       </c>
       <c r="K58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L58">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M58">
-        <v>1</v>
+        <v>0.8035714285714289</v>
       </c>
       <c r="N58">
-        <v>1</v>
+        <v>0.8035714285714289</v>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E59" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F59">
-        <v>0.5178571428571429</v>
-      </c>
-      <c r="G59">
-        <v>0.1878505808955027</v>
-      </c>
-      <c r="H59">
-        <v>0.847863704818783</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="I59">
+        <v>-0.07121282407553874</v>
       </c>
       <c r="J59">
-        <v>0.9550893550893549</v>
+        <v>0.6875000000000002</v>
       </c>
       <c r="K59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L59">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M59">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
       <c r="N59">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F60">
-        <v>0.4821428571428572</v>
-      </c>
-      <c r="G60">
-        <v>0.161550349382151</v>
-      </c>
-      <c r="H60">
-        <v>0.8027353649035632</v>
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="I60">
+        <v>-0.04182772820924956</v>
       </c>
       <c r="J60">
-        <v>0.9550893550893552</v>
+        <v>0.8437500000000003</v>
       </c>
       <c r="K60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L60">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M60">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
       <c r="N60">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E61" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F61">
-        <v>0.5</v>
-      </c>
-      <c r="G61">
-        <v>0.1760589404743549</v>
-      </c>
-      <c r="H61">
-        <v>0.8239410595256451</v>
+        <v>0.5277777777777778</v>
+      </c>
+      <c r="I61">
+        <v>-0.02525129224535298</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
       <c r="K61">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L61">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M61">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>0.8437500000000003</v>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E62" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F62">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="G62">
-        <v>0.5221380220170376</v>
-      </c>
-      <c r="H62">
-        <v>1</v>
+        <v>0.75</v>
+      </c>
+      <c r="I62">
+        <v>0.06492385987838871</v>
       </c>
       <c r="J62">
-        <v>0.07210567210567211</v>
+        <v>0.07812500000000001</v>
       </c>
       <c r="K62">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L62">
         <v>8</v>
       </c>
       <c r="M62">
-        <v>0.7097902097902099</v>
+        <v>0.5468750000000001</v>
       </c>
       <c r="N62">
-        <v>0.7097902097902099</v>
+        <v>0.5468750000000001</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E63" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F63">
-        <v>0.75</v>
-      </c>
-      <c r="G63">
-        <v>0.4260589404743549</v>
-      </c>
-      <c r="H63">
-        <v>1</v>
+        <v>0.6875</v>
+      </c>
+      <c r="I63">
+        <v>0.1364195519584422</v>
       </c>
       <c r="J63">
-        <v>0.1205905205905206</v>
+        <v>0.109375</v>
       </c>
       <c r="K63">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L63">
         <v>8</v>
       </c>
       <c r="M63">
-        <v>0.7097902097902099</v>
+        <v>0.5468750000000001</v>
       </c>
       <c r="N63">
-        <v>0.7097902097902099</v>
+        <v>0.5468750000000001</v>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E64" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F64">
-        <v>0.2678571428571428</v>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0.5479561431753368</v>
+        <v>0.640625</v>
+      </c>
+      <c r="I64">
+        <v>0.02009462858329572</v>
       </c>
       <c r="J64">
-        <v>0.151981351981352</v>
+        <v>0.3828125000000001</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L64">
         <v>8</v>
       </c>
       <c r="M64">
-        <v>0.7097902097902099</v>
+        <v>0.9277343750000001</v>
       </c>
       <c r="N64">
-        <v>0.7097902097902099</v>
+        <v>0.9277343750000001</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E65" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F65">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0.5746293809979307</v>
+        <v>0.328125</v>
+      </c>
+      <c r="I65">
+        <v>-0.08442962898265197</v>
       </c>
       <c r="J65">
-        <v>0.1892773892773893</v>
+        <v>0.5468750000000001</v>
       </c>
       <c r="K65">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L65">
         <v>8</v>
       </c>
       <c r="M65">
-        <v>0.7097902097902099</v>
+        <v>0.9277343750000001</v>
       </c>
       <c r="N65">
-        <v>0.7097902097902099</v>
+        <v>0.9277343750000001</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B66" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E66" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F66">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="G66">
-        <v>0.335739032769462</v>
-      </c>
-      <c r="H66">
-        <v>0.9499752529448239</v>
+        <v>0.40625</v>
+      </c>
+      <c r="I66">
+        <v>-0.01790835391860771</v>
       </c>
       <c r="J66">
-        <v>0.3968919968919969</v>
+        <v>0.5468750000000001</v>
       </c>
       <c r="K66">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L66">
         <v>8</v>
       </c>
       <c r="M66">
-        <v>0.7441724941724943</v>
+        <v>0.9277343750000001</v>
       </c>
       <c r="N66">
-        <v>0.7441724941724943</v>
+        <v>0.9277343750000001</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E67" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F67">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="G67">
-        <v>0.3356440820452618</v>
-      </c>
-      <c r="H67">
-        <v>0.9500702036690241</v>
+        <v>0.53125</v>
+      </c>
+      <c r="I67">
+        <v>-0.06060553912085608</v>
       </c>
       <c r="J67">
-        <v>0.3968919968919969</v>
+        <v>0.7421875000000001</v>
       </c>
       <c r="K67">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L67">
         <v>8</v>
       </c>
       <c r="M67">
-        <v>0.7441724941724943</v>
+        <v>0.9277343750000001</v>
       </c>
       <c r="N67">
-        <v>0.7441724941724943</v>
+        <v>0.9277343750000001</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E68" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F68">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="G68">
-        <v>0.335739032769462</v>
-      </c>
-      <c r="H68">
-        <v>0.9499752529448239</v>
+        <v>0.46875</v>
+      </c>
+      <c r="I68">
+        <v>0.002836060540285679</v>
       </c>
       <c r="J68">
-        <v>0.3968919968919969</v>
+        <v>0.7421875000000001</v>
       </c>
       <c r="K68">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L68">
         <v>8</v>
       </c>
       <c r="M68">
-        <v>0.7441724941724943</v>
+        <v>0.9277343750000001</v>
       </c>
       <c r="N68">
-        <v>0.7441724941724943</v>
+        <v>0.9277343750000001</v>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B69" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E69" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F69">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="G69">
-        <v>0.04503216108881539</v>
-      </c>
-      <c r="H69">
-        <v>0.6692535531968989</v>
+        <v>0.515625</v>
+      </c>
+      <c r="I69">
+        <v>0.002950798903759995</v>
       </c>
       <c r="J69">
-        <v>0.3968919968919969</v>
+        <v>0.7421875000000001</v>
       </c>
       <c r="K69">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L69">
         <v>8</v>
       </c>
       <c r="M69">
-        <v>0.7441724941724943</v>
+        <v>0.9277343750000001</v>
       </c>
       <c r="N69">
-        <v>0.7441724941724943</v>
+        <v>0.9277343750000001</v>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E70" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F70">
-        <v>0.375</v>
-      </c>
-      <c r="G70">
-        <v>0.05668996828106859</v>
-      </c>
-      <c r="H70">
-        <v>0.6933100317189314</v>
+        <v>0.53125</v>
+      </c>
+      <c r="I70">
+        <v>0.07165895725936534</v>
       </c>
       <c r="J70">
-        <v>0.4634032634032634</v>
+        <v>0.8437500000000001</v>
       </c>
       <c r="K70">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L70">
         <v>8</v>
       </c>
       <c r="M70">
-        <v>0.7723387723387725</v>
+        <v>0.9375000000000001</v>
       </c>
       <c r="N70">
-        <v>0.7723387723387725</v>
+        <v>0.9375000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E71" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F71">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="G71">
-        <v>0.2485697233669305</v>
-      </c>
-      <c r="H71">
-        <v>0.8942874194902123</v>
+        <v>0.640625</v>
+      </c>
+      <c r="I71">
+        <v>0.05103361556941876</v>
       </c>
       <c r="J71">
-        <v>0.6943278943278944</v>
+        <v>0.9453124999999998</v>
       </c>
       <c r="K71">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L71">
         <v>8</v>
       </c>
       <c r="M71">
-        <v>0.867909867909868</v>
+        <v>0.9453124999999998</v>
       </c>
       <c r="N71">
-        <v>0.867909867909868</v>
+        <v>0.9453124999999998</v>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C72" t="b">
         <v>0</v>
@@ -4074,241 +4029,244 @@
         <v>54</v>
       </c>
       <c r="F72">
-        <v>0.5714285714285714</v>
+        <v>0.75</v>
       </c>
       <c r="G72">
-        <v>0.2485697233669305</v>
+        <v>0.422174766568861</v>
       </c>
       <c r="H72">
-        <v>0.8942874194902123</v>
+        <v>1</v>
       </c>
       <c r="J72">
-        <v>0.6943278943278944</v>
+        <v>0.1418581418581419</v>
       </c>
       <c r="K72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L72">
         <v>8</v>
       </c>
       <c r="M72">
-        <v>0.867909867909868</v>
+        <v>0.6893106893106894</v>
       </c>
       <c r="N72">
-        <v>0.867909867909868</v>
+        <v>0.6893106893106894</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C73" t="b">
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E73" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F73">
-        <v>0.4285714285714285</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="G73">
-        <v>0.1149691555813418</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>0.7421737015615153</v>
+        <v>0.567055561531443</v>
       </c>
       <c r="J73">
-        <v>0.6943278943278944</v>
+        <v>0.1811521811521812</v>
       </c>
       <c r="K73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L73">
         <v>8</v>
       </c>
       <c r="M73">
-        <v>0.867909867909868</v>
+        <v>0.6893106893106894</v>
       </c>
       <c r="N73">
-        <v>0.867909867909868</v>
+        <v>0.6893106893106894</v>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C74" t="b">
         <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E74" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F74">
-        <v>0.4642857142857143</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G74">
-        <v>0.139894798885058</v>
+        <v>0.3984358171810527</v>
       </c>
       <c r="H74">
-        <v>0.7886766296863706</v>
+        <v>1</v>
       </c>
       <c r="J74">
-        <v>0.8665112665112666</v>
+        <v>0.2284382284382285</v>
       </c>
       <c r="K74">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L74">
         <v>8</v>
       </c>
       <c r="M74">
-        <v>0.9284049284049285</v>
+        <v>0.6893106893106894</v>
       </c>
       <c r="N74">
-        <v>0.9284049284049285</v>
+        <v>0.6893106893106894</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C75" t="b">
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E75" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F75">
-        <v>0.4642857142857143</v>
+        <v>0.3125</v>
       </c>
       <c r="G75">
-        <v>0.1396251845578111</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>0.7889462440136176</v>
+        <v>0.6343122719002462</v>
       </c>
       <c r="J75">
-        <v>0.8665112665112666</v>
+        <v>0.2823842823842824</v>
       </c>
       <c r="K75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L75">
         <v>8</v>
       </c>
       <c r="M75">
-        <v>0.9284049284049285</v>
+        <v>0.6893106893106894</v>
       </c>
       <c r="N75">
-        <v>0.9284049284049285</v>
+        <v>0.6893106893106894</v>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C76" t="b">
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E76" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F76">
-        <v>0.4821428571428572</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G76">
-        <v>0.1621878013846009</v>
+        <v>0.02374340784359895</v>
       </c>
       <c r="H76">
-        <v>0.8020979129011134</v>
+        <v>0.6429232588230677</v>
       </c>
       <c r="J76">
-        <v>0.9550893550893552</v>
+        <v>0.344988344988345</v>
       </c>
       <c r="K76">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L76">
         <v>8</v>
       </c>
       <c r="M76">
-        <v>0.9550893550893552</v>
+        <v>0.6893106893106894</v>
       </c>
       <c r="N76">
-        <v>0.9550893550893552</v>
+        <v>0.6893106893106894</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E77" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F77">
-        <v>0.8611111111111112</v>
-      </c>
-      <c r="I77">
-        <v>0.1726841728124711</v>
+        <v>0.3541666666666667</v>
+      </c>
+      <c r="G77">
+        <v>0.02911409795761959</v>
+      </c>
+      <c r="H77">
+        <v>0.6792192353757138</v>
       </c>
       <c r="J77">
-        <v>0.06250000000000003</v>
+        <v>0.4135864135864136</v>
       </c>
       <c r="K77">
         <v>6</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M77">
-        <v>0.7812500000000002</v>
+        <v>0.6893106893106894</v>
       </c>
       <c r="N77">
-        <v>0.7812500000000002</v>
+        <v>0.6893106893106894</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" t="s">
         <v>45</v>
@@ -4317,1704 +4275,151 @@
         <v>45</v>
       </c>
       <c r="F78">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="I78">
-        <v>0.1066412365018345</v>
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="G78">
+        <v>0.245662833021885</v>
+      </c>
+      <c r="H78">
+        <v>0.9626705003114483</v>
       </c>
       <c r="J78">
-        <v>0.1562500000000001</v>
+        <v>0.5727605727605728</v>
       </c>
       <c r="K78">
         <v>6</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M78">
-        <v>0.7812500000000002</v>
+        <v>0.8182293896579611</v>
       </c>
       <c r="N78">
-        <v>0.7812500000000002</v>
+        <v>0.8182293896579611</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E79" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F79">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="I79">
-        <v>-0.1451396763010954</v>
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="G79">
+        <v>0.08844975600567559</v>
+      </c>
+      <c r="H79">
+        <v>0.828216910660991</v>
       </c>
       <c r="J79">
-        <v>0.1562500000000001</v>
+        <v>0.8518148518148518</v>
       </c>
       <c r="K79">
         <v>6</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M79">
-        <v>0.7812500000000002</v>
+        <v>0.9497169497169498</v>
       </c>
       <c r="N79">
-        <v>0.7812500000000002</v>
+        <v>0.9497169497169498</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B80" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E80" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F80">
-        <v>0.6944444444444444</v>
-      </c>
-      <c r="I80">
-        <v>0.1813157859027815</v>
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="G80">
+        <v>0.1928628194902629</v>
+      </c>
+      <c r="H80">
+        <v>0.8488038471764039</v>
       </c>
       <c r="J80">
-        <v>0.3125000000000001</v>
+        <v>0.9497169497169498</v>
       </c>
       <c r="K80">
         <v>6</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M80">
-        <v>0.7812500000000002</v>
+        <v>0.9497169497169498</v>
       </c>
       <c r="N80">
-        <v>0.7812500000000002</v>
+        <v>0.9497169497169498</v>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B81" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E81" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F81">
-        <v>0.2777777777777778</v>
-      </c>
-      <c r="I81">
-        <v>-0.06229167852528958</v>
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="G81">
+        <v>0.1914135392808862</v>
+      </c>
+      <c r="H81">
+        <v>0.8502531273857805</v>
       </c>
       <c r="J81">
-        <v>0.3125000000000001</v>
+        <v>0.9497169497169498</v>
       </c>
       <c r="K81">
         <v>6</v>
       </c>
       <c r="L81">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M81">
-        <v>0.7812500000000002</v>
+        <v>0.9497169497169498</v>
       </c>
       <c r="N81">
-        <v>0.7812500000000002</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14">
-      <c r="A82" t="s">
-        <v>21</v>
-      </c>
-      <c r="B82" t="s">
-        <v>22</v>
-      </c>
-      <c r="C82" t="b">
-        <v>1</v>
-      </c>
-      <c r="D82" t="s">
-        <v>47</v>
-      </c>
-      <c r="E82" t="s">
-        <v>47</v>
-      </c>
-      <c r="F82">
-        <v>0.1944444444444444</v>
-      </c>
-      <c r="I82">
-        <v>-0.1076335027443761</v>
-      </c>
-      <c r="J82">
-        <v>0.3125000000000001</v>
-      </c>
-      <c r="K82">
-        <v>6</v>
-      </c>
-      <c r="L82">
-        <v>6</v>
-      </c>
-      <c r="M82">
-        <v>0.7812500000000002</v>
-      </c>
-      <c r="N82">
-        <v>0.7812500000000002</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14">
-      <c r="A83" t="s">
-        <v>21</v>
-      </c>
-      <c r="B83" t="s">
-        <v>22</v>
-      </c>
-      <c r="C83" t="b">
-        <v>1</v>
-      </c>
-      <c r="D83" t="s">
-        <v>56</v>
-      </c>
-      <c r="E83" t="s">
-        <v>56</v>
-      </c>
-      <c r="F83">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="I83">
-        <v>0.1326734954674455</v>
-      </c>
-      <c r="J83">
-        <v>0.4375000000000002</v>
-      </c>
-      <c r="K83">
-        <v>6</v>
-      </c>
-      <c r="L83">
-        <v>6</v>
-      </c>
-      <c r="M83">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="N83">
-        <v>0.8437500000000003</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14">
-      <c r="A84" t="s">
-        <v>21</v>
-      </c>
-      <c r="B84" t="s">
-        <v>22</v>
-      </c>
-      <c r="C84" t="b">
-        <v>1</v>
-      </c>
-      <c r="D84" t="s">
-        <v>46</v>
-      </c>
-      <c r="E84" t="s">
-        <v>46</v>
-      </c>
-      <c r="F84">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="I84">
-        <v>0.01776047608298494</v>
-      </c>
-      <c r="J84">
-        <v>0.5625000000000002</v>
-      </c>
-      <c r="K84">
-        <v>6</v>
-      </c>
-      <c r="L84">
-        <v>6</v>
-      </c>
-      <c r="M84">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="N84">
-        <v>0.8437500000000003</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14">
-      <c r="A85" t="s">
-        <v>21</v>
-      </c>
-      <c r="B85" t="s">
-        <v>22</v>
-      </c>
-      <c r="C85" t="b">
-        <v>1</v>
-      </c>
-      <c r="D85" t="s">
-        <v>52</v>
-      </c>
-      <c r="E85" t="s">
-        <v>52</v>
-      </c>
-      <c r="F85">
-        <v>0.6944444444444444</v>
-      </c>
-      <c r="I85">
-        <v>0.1221424491899613</v>
-      </c>
-      <c r="J85">
-        <v>0.5625000000000002</v>
-      </c>
-      <c r="K85">
-        <v>6</v>
-      </c>
-      <c r="L85">
-        <v>6</v>
-      </c>
-      <c r="M85">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="N85">
-        <v>0.8437500000000003</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14">
-      <c r="A86" t="s">
-        <v>21</v>
-      </c>
-      <c r="B86" t="s">
-        <v>22</v>
-      </c>
-      <c r="C86" t="b">
-        <v>1</v>
-      </c>
-      <c r="D86" t="s">
-        <v>49</v>
-      </c>
-      <c r="E86" t="s">
-        <v>49</v>
-      </c>
-      <c r="F86">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="I86">
-        <v>0.08681461636921775</v>
-      </c>
-      <c r="J86">
-        <v>0.6875000000000002</v>
-      </c>
-      <c r="K86">
-        <v>6</v>
-      </c>
-      <c r="L86">
-        <v>6</v>
-      </c>
-      <c r="M86">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="N86">
-        <v>0.8437500000000003</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14">
-      <c r="A87" t="s">
-        <v>21</v>
-      </c>
-      <c r="B87" t="s">
-        <v>22</v>
-      </c>
-      <c r="C87" t="b">
-        <v>1</v>
-      </c>
-      <c r="D87" t="s">
-        <v>48</v>
-      </c>
-      <c r="E87" t="s">
-        <v>48</v>
-      </c>
-      <c r="F87">
-        <v>0.4722222222222222</v>
-      </c>
-      <c r="I87">
-        <v>-0.05147354144125908</v>
-      </c>
-      <c r="J87">
-        <v>0.6875000000000002</v>
-      </c>
-      <c r="K87">
-        <v>6</v>
-      </c>
-      <c r="L87">
-        <v>6</v>
-      </c>
-      <c r="M87">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="N87">
-        <v>0.8437500000000003</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14">
-      <c r="A88" t="s">
-        <v>21</v>
-      </c>
-      <c r="B88" t="s">
-        <v>22</v>
-      </c>
-      <c r="C88" t="b">
-        <v>1</v>
-      </c>
-      <c r="D88" t="s">
-        <v>54</v>
-      </c>
-      <c r="E88" t="s">
-        <v>54</v>
-      </c>
-      <c r="F88">
-        <v>0.5277777777777778</v>
-      </c>
-      <c r="I88">
-        <v>-0.04559408890641857</v>
-      </c>
-      <c r="J88">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="K88">
-        <v>6</v>
-      </c>
-      <c r="L88">
-        <v>6</v>
-      </c>
-      <c r="M88">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="N88">
-        <v>0.8437500000000003</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14">
-      <c r="A89" t="s">
-        <v>21</v>
-      </c>
-      <c r="B89" t="s">
-        <v>22</v>
-      </c>
-      <c r="C89" t="b">
-        <v>1</v>
-      </c>
-      <c r="D89" t="s">
-        <v>51</v>
-      </c>
-      <c r="E89" t="s">
-        <v>51</v>
-      </c>
-      <c r="F89">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="I89">
-        <v>0.04772559282893921</v>
-      </c>
-      <c r="J89">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="K89">
-        <v>6</v>
-      </c>
-      <c r="L89">
-        <v>6</v>
-      </c>
-      <c r="M89">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="N89">
-        <v>0.8437500000000003</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14">
-      <c r="A90" t="s">
-        <v>21</v>
-      </c>
-      <c r="B90" t="s">
-        <v>22</v>
-      </c>
-      <c r="C90" t="b">
-        <v>1</v>
-      </c>
-      <c r="D90" t="s">
-        <v>57</v>
-      </c>
-      <c r="E90" t="s">
-        <v>57</v>
-      </c>
-      <c r="F90">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="I90">
-        <v>-0.04915417246721927</v>
-      </c>
-      <c r="J90">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="K90">
-        <v>6</v>
-      </c>
-      <c r="L90">
-        <v>6</v>
-      </c>
-      <c r="M90">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="N90">
-        <v>0.8437500000000003</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14">
-      <c r="A91" t="s">
-        <v>21</v>
-      </c>
-      <c r="B91" t="s">
-        <v>22</v>
-      </c>
-      <c r="C91" t="b">
-        <v>1</v>
-      </c>
-      <c r="D91" t="s">
-        <v>55</v>
-      </c>
-      <c r="E91" t="s">
-        <v>55</v>
-      </c>
-      <c r="F91">
-        <v>0.5</v>
-      </c>
-      <c r="I91">
-        <v>-0.002860536960869783</v>
-      </c>
-      <c r="J91">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="K91">
-        <v>6</v>
-      </c>
-      <c r="L91">
-        <v>6</v>
-      </c>
-      <c r="M91">
-        <v>0.8437500000000003</v>
-      </c>
-      <c r="N91">
-        <v>0.8437500000000003</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14">
-      <c r="A92" t="s">
-        <v>23</v>
-      </c>
-      <c r="B92" t="s">
-        <v>24</v>
-      </c>
-      <c r="C92" t="b">
-        <v>1</v>
-      </c>
-      <c r="D92" t="s">
-        <v>54</v>
-      </c>
-      <c r="E92" t="s">
-        <v>54</v>
-      </c>
-      <c r="F92">
-        <v>0.734375</v>
-      </c>
-      <c r="I92">
-        <v>0.06099995628669049</v>
-      </c>
-      <c r="J92">
-        <v>0.07812500000000001</v>
-      </c>
-      <c r="K92">
-        <v>8</v>
-      </c>
-      <c r="L92">
-        <v>8</v>
-      </c>
-      <c r="M92">
-        <v>0.8735795454545455</v>
-      </c>
-      <c r="N92">
-        <v>0.8735795454545455</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14">
-      <c r="A93" t="s">
-        <v>23</v>
-      </c>
-      <c r="B93" t="s">
-        <v>24</v>
-      </c>
-      <c r="C93" t="b">
-        <v>1</v>
-      </c>
-      <c r="D93" t="s">
-        <v>55</v>
-      </c>
-      <c r="E93" t="s">
-        <v>55</v>
-      </c>
-      <c r="F93">
-        <v>0.609375</v>
-      </c>
-      <c r="I93">
-        <v>0.08853865778819013</v>
-      </c>
-      <c r="J93">
-        <v>0.1953125</v>
-      </c>
-      <c r="K93">
-        <v>8</v>
-      </c>
-      <c r="L93">
-        <v>8</v>
-      </c>
-      <c r="M93">
-        <v>0.8735795454545455</v>
-      </c>
-      <c r="N93">
-        <v>0.8735795454545455</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14">
-      <c r="A94" t="s">
-        <v>23</v>
-      </c>
-      <c r="B94" t="s">
-        <v>24</v>
-      </c>
-      <c r="C94" t="b">
-        <v>1</v>
-      </c>
-      <c r="D94" t="s">
-        <v>45</v>
-      </c>
-      <c r="E94" t="s">
-        <v>45</v>
-      </c>
-      <c r="F94">
-        <v>0.65625</v>
-      </c>
-      <c r="I94">
-        <v>0.03478632577803124</v>
-      </c>
-      <c r="J94">
-        <v>0.2500000000000001</v>
-      </c>
-      <c r="K94">
-        <v>8</v>
-      </c>
-      <c r="L94">
-        <v>8</v>
-      </c>
-      <c r="M94">
-        <v>0.8735795454545455</v>
-      </c>
-      <c r="N94">
-        <v>0.8735795454545455</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14">
-      <c r="A95" t="s">
-        <v>23</v>
-      </c>
-      <c r="B95" t="s">
-        <v>24</v>
-      </c>
-      <c r="C95" t="b">
-        <v>1</v>
-      </c>
-      <c r="D95" t="s">
-        <v>53</v>
-      </c>
-      <c r="E95" t="s">
-        <v>53</v>
-      </c>
-      <c r="F95">
-        <v>0.59375</v>
-      </c>
-      <c r="I95">
-        <v>0.04024573245569871</v>
-      </c>
-      <c r="J95">
-        <v>0.3125000000000001</v>
-      </c>
-      <c r="K95">
-        <v>8</v>
-      </c>
-      <c r="L95">
-        <v>8</v>
-      </c>
-      <c r="M95">
-        <v>0.8735795454545455</v>
-      </c>
-      <c r="N95">
-        <v>0.8735795454545455</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14">
-      <c r="A96" t="s">
-        <v>23</v>
-      </c>
-      <c r="B96" t="s">
-        <v>24</v>
-      </c>
-      <c r="C96" t="b">
-        <v>1</v>
-      </c>
-      <c r="D96" t="s">
-        <v>47</v>
-      </c>
-      <c r="E96" t="s">
-        <v>47</v>
-      </c>
-      <c r="F96">
-        <v>0.390625</v>
-      </c>
-      <c r="I96">
-        <v>-0.03318643260852032</v>
-      </c>
-      <c r="J96">
-        <v>0.4609375000000001</v>
-      </c>
-      <c r="K96">
-        <v>8</v>
-      </c>
-      <c r="L96">
-        <v>8</v>
-      </c>
-      <c r="M96">
-        <v>0.8735795454545455</v>
-      </c>
-      <c r="N96">
-        <v>0.8735795454545455</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14">
-      <c r="A97" t="s">
-        <v>23</v>
-      </c>
-      <c r="B97" t="s">
-        <v>24</v>
-      </c>
-      <c r="C97" t="b">
-        <v>1</v>
-      </c>
-      <c r="D97" t="s">
-        <v>50</v>
-      </c>
-      <c r="E97" t="s">
-        <v>50</v>
-      </c>
-      <c r="F97">
-        <v>0.390625</v>
-      </c>
-      <c r="I97">
-        <v>-0.03802187304407005</v>
-      </c>
-      <c r="J97">
-        <v>0.5468750000000001</v>
-      </c>
-      <c r="K97">
-        <v>8</v>
-      </c>
-      <c r="L97">
-        <v>8</v>
-      </c>
-      <c r="M97">
-        <v>0.8735795454545455</v>
-      </c>
-      <c r="N97">
-        <v>0.8735795454545455</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14">
-      <c r="A98" t="s">
-        <v>23</v>
-      </c>
-      <c r="B98" t="s">
-        <v>24</v>
-      </c>
-      <c r="C98" t="b">
-        <v>1</v>
-      </c>
-      <c r="D98" t="s">
-        <v>56</v>
-      </c>
-      <c r="E98" t="s">
-        <v>56</v>
-      </c>
-      <c r="F98">
-        <v>0.4375</v>
-      </c>
-      <c r="I98">
-        <v>-0.01661325647678491</v>
-      </c>
-      <c r="J98">
-        <v>0.6406250000000001</v>
-      </c>
-      <c r="K98">
-        <v>8</v>
-      </c>
-      <c r="L98">
-        <v>8</v>
-      </c>
-      <c r="M98">
-        <v>0.8735795454545455</v>
-      </c>
-      <c r="N98">
-        <v>0.8735795454545455</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14">
-      <c r="A99" t="s">
-        <v>23</v>
-      </c>
-      <c r="B99" t="s">
-        <v>24</v>
-      </c>
-      <c r="C99" t="b">
-        <v>1</v>
-      </c>
-      <c r="D99" t="s">
-        <v>57</v>
-      </c>
-      <c r="E99" t="s">
-        <v>57</v>
-      </c>
-      <c r="F99">
-        <v>0.421875</v>
-      </c>
-      <c r="I99">
-        <v>-0.02619076159136435</v>
-      </c>
-      <c r="J99">
-        <v>0.6406250000000001</v>
-      </c>
-      <c r="K99">
-        <v>8</v>
-      </c>
-      <c r="L99">
-        <v>8</v>
-      </c>
-      <c r="M99">
-        <v>0.8735795454545455</v>
-      </c>
-      <c r="N99">
-        <v>0.8735795454545455</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14">
-      <c r="A100" t="s">
-        <v>23</v>
-      </c>
-      <c r="B100" t="s">
-        <v>24</v>
-      </c>
-      <c r="C100" t="b">
-        <v>1</v>
-      </c>
-      <c r="D100" t="s">
-        <v>48</v>
-      </c>
-      <c r="E100" t="s">
-        <v>48</v>
-      </c>
-      <c r="F100">
-        <v>0.34375</v>
-      </c>
-      <c r="I100">
-        <v>-0.1124340209448966</v>
-      </c>
-      <c r="J100">
-        <v>0.6406250000000001</v>
-      </c>
-      <c r="K100">
-        <v>8</v>
-      </c>
-      <c r="L100">
-        <v>8</v>
-      </c>
-      <c r="M100">
-        <v>0.8735795454545455</v>
-      </c>
-      <c r="N100">
-        <v>0.8735795454545455</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14">
-      <c r="A101" t="s">
-        <v>23</v>
-      </c>
-      <c r="B101" t="s">
-        <v>24</v>
-      </c>
-      <c r="C101" t="b">
-        <v>1</v>
-      </c>
-      <c r="D101" t="s">
-        <v>52</v>
-      </c>
-      <c r="E101" t="s">
-        <v>52</v>
-      </c>
-      <c r="F101">
-        <v>0.65625</v>
-      </c>
-      <c r="I101">
-        <v>0.09049223067312329</v>
-      </c>
-      <c r="J101">
-        <v>0.6406250000000001</v>
-      </c>
-      <c r="K101">
-        <v>8</v>
-      </c>
-      <c r="L101">
-        <v>8</v>
-      </c>
-      <c r="M101">
-        <v>0.8735795454545455</v>
-      </c>
-      <c r="N101">
-        <v>0.8735795454545455</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14">
-      <c r="A102" t="s">
-        <v>23</v>
-      </c>
-      <c r="B102" t="s">
-        <v>24</v>
-      </c>
-      <c r="C102" t="b">
-        <v>1</v>
-      </c>
-      <c r="D102" t="s">
-        <v>59</v>
-      </c>
-      <c r="E102" t="s">
-        <v>59</v>
-      </c>
-      <c r="F102">
-        <v>0.625</v>
-      </c>
-      <c r="I102">
-        <v>0.007953079027062937</v>
-      </c>
-      <c r="J102">
-        <v>0.6406250000000001</v>
-      </c>
-      <c r="K102">
-        <v>8</v>
-      </c>
-      <c r="L102">
-        <v>8</v>
-      </c>
-      <c r="M102">
-        <v>0.8735795454545455</v>
-      </c>
-      <c r="N102">
-        <v>0.8735795454545455</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14">
-      <c r="A103" t="s">
-        <v>23</v>
-      </c>
-      <c r="B103" t="s">
-        <v>24</v>
-      </c>
-      <c r="C103" t="b">
-        <v>1</v>
-      </c>
-      <c r="D103" t="s">
-        <v>49</v>
-      </c>
-      <c r="E103" t="s">
-        <v>49</v>
-      </c>
-      <c r="F103">
-        <v>0.578125</v>
-      </c>
-      <c r="I103">
-        <v>0.04476056869555671</v>
-      </c>
-      <c r="J103">
-        <v>0.7421875000000001</v>
-      </c>
-      <c r="K103">
-        <v>8</v>
-      </c>
-      <c r="L103">
-        <v>8</v>
-      </c>
-      <c r="M103">
-        <v>0.9040178571428572</v>
-      </c>
-      <c r="N103">
-        <v>0.9040178571428572</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14">
-      <c r="A104" t="s">
-        <v>23</v>
-      </c>
-      <c r="B104" t="s">
-        <v>24</v>
-      </c>
-      <c r="C104" t="b">
-        <v>1</v>
-      </c>
-      <c r="D104" t="s">
-        <v>51</v>
-      </c>
-      <c r="E104" t="s">
-        <v>51</v>
-      </c>
-      <c r="F104">
-        <v>0.515625</v>
-      </c>
-      <c r="I104">
-        <v>-0.01729494621730936</v>
-      </c>
-      <c r="J104">
-        <v>0.8437500000000001</v>
-      </c>
-      <c r="K104">
-        <v>8</v>
-      </c>
-      <c r="L104">
-        <v>8</v>
-      </c>
-      <c r="M104">
-        <v>0.9040178571428572</v>
-      </c>
-      <c r="N104">
-        <v>0.9040178571428572</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14">
-      <c r="A105" t="s">
-        <v>23</v>
-      </c>
-      <c r="B105" t="s">
-        <v>24</v>
-      </c>
-      <c r="C105" t="b">
-        <v>1</v>
-      </c>
-      <c r="D105" t="s">
-        <v>46</v>
-      </c>
-      <c r="E105" t="s">
-        <v>46</v>
-      </c>
-      <c r="F105">
-        <v>0.453125</v>
-      </c>
-      <c r="I105">
-        <v>-0.01027380439512042</v>
-      </c>
-      <c r="J105">
-        <v>0.8437500000000001</v>
-      </c>
-      <c r="K105">
-        <v>8</v>
-      </c>
-      <c r="L105">
-        <v>8</v>
-      </c>
-      <c r="M105">
-        <v>0.9040178571428572</v>
-      </c>
-      <c r="N105">
-        <v>0.9040178571428572</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14">
-      <c r="A106" t="s">
-        <v>23</v>
-      </c>
-      <c r="B106" t="s">
-        <v>24</v>
-      </c>
-      <c r="C106" t="b">
-        <v>1</v>
-      </c>
-      <c r="D106" t="s">
-        <v>58</v>
-      </c>
-      <c r="E106" t="s">
-        <v>58</v>
-      </c>
-      <c r="F106">
-        <v>0.453125</v>
-      </c>
-      <c r="I106">
-        <v>5.638777027187902E-05</v>
-      </c>
-      <c r="J106">
-        <v>0.9453124999999998</v>
-      </c>
-      <c r="K106">
-        <v>8</v>
-      </c>
-      <c r="L106">
-        <v>8</v>
-      </c>
-      <c r="M106">
-        <v>0.9453124999999998</v>
-      </c>
-      <c r="N106">
-        <v>0.9453124999999998</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14">
-      <c r="A107" t="s">
-        <v>33</v>
-      </c>
-      <c r="B107" t="s">
-        <v>34</v>
-      </c>
-      <c r="C107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D107" t="s">
-        <v>58</v>
-      </c>
-      <c r="E107" t="s">
-        <v>58</v>
-      </c>
-      <c r="F107">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="G107">
-        <v>0.5934465623571782</v>
-      </c>
-      <c r="H107">
-        <v>1</v>
-      </c>
-      <c r="J107">
-        <v>0.04262404262404262</v>
-      </c>
-      <c r="K107">
-        <v>6</v>
-      </c>
-      <c r="L107">
-        <v>8</v>
-      </c>
-      <c r="M107">
-        <v>0.6393606393606394</v>
-      </c>
-      <c r="N107">
-        <v>0.6393606393606394</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14">
-      <c r="A108" t="s">
-        <v>33</v>
-      </c>
-      <c r="B108" t="s">
-        <v>34</v>
-      </c>
-      <c r="C108" t="b">
-        <v>0</v>
-      </c>
-      <c r="D108" t="s">
-        <v>45</v>
-      </c>
-      <c r="E108" t="s">
-        <v>45</v>
-      </c>
-      <c r="F108">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="G108">
-        <v>0.3978215499456805</v>
-      </c>
-      <c r="H108">
-        <v>1</v>
-      </c>
-      <c r="J108">
-        <v>0.2284382284382285</v>
-      </c>
-      <c r="K108">
-        <v>6</v>
-      </c>
-      <c r="L108">
-        <v>8</v>
-      </c>
-      <c r="M108">
-        <v>0.8471528471528473</v>
-      </c>
-      <c r="N108">
-        <v>0.8471528471528473</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14">
-      <c r="A109" t="s">
-        <v>33</v>
-      </c>
-      <c r="B109" t="s">
-        <v>34</v>
-      </c>
-      <c r="C109" t="b">
-        <v>0</v>
-      </c>
-      <c r="D109" t="s">
-        <v>56</v>
-      </c>
-      <c r="E109" t="s">
-        <v>56</v>
-      </c>
-      <c r="F109">
-        <v>0.6875</v>
-      </c>
-      <c r="G109">
-        <v>0.3408865807228488</v>
-      </c>
-      <c r="H109">
-        <v>1</v>
-      </c>
-      <c r="J109">
-        <v>0.2823842823842824</v>
-      </c>
-      <c r="K109">
-        <v>6</v>
-      </c>
-      <c r="L109">
-        <v>8</v>
-      </c>
-      <c r="M109">
-        <v>0.8471528471528473</v>
-      </c>
-      <c r="N109">
-        <v>0.8471528471528473</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14">
-      <c r="A110" t="s">
-        <v>33</v>
-      </c>
-      <c r="B110" t="s">
-        <v>34</v>
-      </c>
-      <c r="C110" t="b">
-        <v>0</v>
-      </c>
-      <c r="D110" t="s">
-        <v>54</v>
-      </c>
-      <c r="E110" t="s">
-        <v>54</v>
-      </c>
-      <c r="F110">
-        <v>0.3125</v>
-      </c>
-      <c r="G110">
-        <v>0</v>
-      </c>
-      <c r="H110">
-        <v>0.653292228224337</v>
-      </c>
-      <c r="J110">
-        <v>0.2823842823842824</v>
-      </c>
-      <c r="K110">
-        <v>6</v>
-      </c>
-      <c r="L110">
-        <v>8</v>
-      </c>
-      <c r="M110">
-        <v>0.8471528471528473</v>
-      </c>
-      <c r="N110">
-        <v>0.8471528471528473</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14">
-      <c r="A111" t="s">
-        <v>33</v>
-      </c>
-      <c r="B111" t="s">
-        <v>34</v>
-      </c>
-      <c r="C111" t="b">
-        <v>0</v>
-      </c>
-      <c r="D111" t="s">
-        <v>59</v>
-      </c>
-      <c r="E111" t="s">
-        <v>59</v>
-      </c>
-      <c r="F111">
-        <v>0.3125</v>
-      </c>
-      <c r="G111">
-        <v>0</v>
-      </c>
-      <c r="H111">
-        <v>0.639889005382374</v>
-      </c>
-      <c r="J111">
-        <v>0.2823842823842824</v>
-      </c>
-      <c r="K111">
-        <v>6</v>
-      </c>
-      <c r="L111">
-        <v>8</v>
-      </c>
-      <c r="M111">
-        <v>0.8471528471528473</v>
-      </c>
-      <c r="N111">
-        <v>0.8471528471528473</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14">
-      <c r="A112" t="s">
-        <v>33</v>
-      </c>
-      <c r="B112" t="s">
-        <v>34</v>
-      </c>
-      <c r="C112" t="b">
-        <v>0</v>
-      </c>
-      <c r="D112" t="s">
-        <v>53</v>
-      </c>
-      <c r="E112" t="s">
-        <v>53</v>
-      </c>
-      <c r="F112">
-        <v>0.625</v>
-      </c>
-      <c r="G112">
-        <v>0.269833642034704</v>
-      </c>
-      <c r="H112">
-        <v>0.9801663579652961</v>
-      </c>
-      <c r="J112">
-        <v>0.4908424908424909</v>
-      </c>
-      <c r="K112">
-        <v>6</v>
-      </c>
-      <c r="L112">
-        <v>8</v>
-      </c>
-      <c r="M112">
-        <v>0.9546009546009547</v>
-      </c>
-      <c r="N112">
-        <v>0.9546009546009547</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14">
-      <c r="A113" t="s">
-        <v>33</v>
-      </c>
-      <c r="B113" t="s">
-        <v>34</v>
-      </c>
-      <c r="C113" t="b">
-        <v>0</v>
-      </c>
-      <c r="D113" t="s">
-        <v>50</v>
-      </c>
-      <c r="E113" t="s">
-        <v>50</v>
-      </c>
-      <c r="F113">
-        <v>0.3958333333333333</v>
-      </c>
-      <c r="G113">
-        <v>0.0550411051089964</v>
-      </c>
-      <c r="H113">
-        <v>0.7366255615576702</v>
-      </c>
-      <c r="J113">
-        <v>0.5727605727605728</v>
-      </c>
-      <c r="K113">
-        <v>6</v>
-      </c>
-      <c r="L113">
-        <v>8</v>
-      </c>
-      <c r="M113">
-        <v>0.9546009546009547</v>
-      </c>
-      <c r="N113">
-        <v>0.9546009546009547</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14">
-      <c r="A114" t="s">
-        <v>33</v>
-      </c>
-      <c r="B114" t="s">
-        <v>34</v>
-      </c>
-      <c r="C114" t="b">
-        <v>0</v>
-      </c>
-      <c r="D114" t="s">
-        <v>52</v>
-      </c>
-      <c r="E114" t="s">
-        <v>52</v>
-      </c>
-      <c r="F114">
-        <v>0.6041666666666666</v>
-      </c>
-      <c r="G114">
-        <v>0.2698663135289662</v>
-      </c>
-      <c r="H114">
-        <v>0.9384670198043671</v>
-      </c>
-      <c r="J114">
-        <v>0.5727605727605728</v>
-      </c>
-      <c r="K114">
-        <v>6</v>
-      </c>
-      <c r="L114">
-        <v>8</v>
-      </c>
-      <c r="M114">
-        <v>0.9546009546009547</v>
-      </c>
-      <c r="N114">
-        <v>0.9546009546009547</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14">
-      <c r="A115" t="s">
-        <v>33</v>
-      </c>
-      <c r="B115" t="s">
-        <v>34</v>
-      </c>
-      <c r="C115" t="b">
-        <v>0</v>
-      </c>
-      <c r="D115" t="s">
-        <v>47</v>
-      </c>
-      <c r="E115" t="s">
-        <v>47</v>
-      </c>
-      <c r="F115">
-        <v>0.3958333333333333</v>
-      </c>
-      <c r="G115">
-        <v>0.04921991405618208</v>
-      </c>
-      <c r="H115">
-        <v>0.7424467526104845</v>
-      </c>
-      <c r="J115">
-        <v>0.5727605727605728</v>
-      </c>
-      <c r="K115">
-        <v>6</v>
-      </c>
-      <c r="L115">
-        <v>8</v>
-      </c>
-      <c r="M115">
-        <v>0.9546009546009547</v>
-      </c>
-      <c r="N115">
-        <v>0.9546009546009547</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14">
-      <c r="A116" t="s">
-        <v>33</v>
-      </c>
-      <c r="B116" t="s">
-        <v>34</v>
-      </c>
-      <c r="C116" t="b">
-        <v>0</v>
-      </c>
-      <c r="D116" t="s">
-        <v>55</v>
-      </c>
-      <c r="E116" t="s">
-        <v>55</v>
-      </c>
-      <c r="F116">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="G116">
-        <v>0.02892602137359861</v>
-      </c>
-      <c r="H116">
-        <v>0.8044073119597348</v>
-      </c>
-      <c r="J116">
-        <v>0.662004662004662</v>
-      </c>
-      <c r="K116">
-        <v>6</v>
-      </c>
-      <c r="L116">
-        <v>8</v>
-      </c>
-      <c r="M116">
-        <v>0.993006993006993</v>
-      </c>
-      <c r="N116">
-        <v>0.993006993006993</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14">
-      <c r="A117" t="s">
-        <v>33</v>
-      </c>
-      <c r="B117" t="s">
-        <v>34</v>
-      </c>
-      <c r="C117" t="b">
-        <v>0</v>
-      </c>
-      <c r="D117" t="s">
-        <v>51</v>
-      </c>
-      <c r="E117" t="s">
-        <v>51</v>
-      </c>
-      <c r="F117">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="G117">
-        <v>0.1835616877720909</v>
-      </c>
-      <c r="H117">
-        <v>0.8997716455612423</v>
-      </c>
-      <c r="J117">
-        <v>0.8518148518148518</v>
-      </c>
-      <c r="K117">
-        <v>6</v>
-      </c>
-      <c r="L117">
-        <v>8</v>
-      </c>
-      <c r="M117">
-        <v>1</v>
-      </c>
-      <c r="N117">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14">
-      <c r="A118" t="s">
-        <v>33</v>
-      </c>
-      <c r="B118" t="s">
-        <v>34</v>
-      </c>
-      <c r="C118" t="b">
-        <v>0</v>
-      </c>
-      <c r="D118" t="s">
-        <v>46</v>
-      </c>
-      <c r="E118" t="s">
-        <v>46</v>
-      </c>
-      <c r="F118">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="G118">
-        <v>0.2015740742207652</v>
-      </c>
-      <c r="H118">
-        <v>0.8817592591125681</v>
-      </c>
-      <c r="J118">
-        <v>0.8518148518148518</v>
-      </c>
-      <c r="K118">
-        <v>6</v>
-      </c>
-      <c r="L118">
-        <v>8</v>
-      </c>
-      <c r="M118">
-        <v>1</v>
-      </c>
-      <c r="N118">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14">
-      <c r="A119" t="s">
-        <v>33</v>
-      </c>
-      <c r="B119" t="s">
-        <v>34</v>
-      </c>
-      <c r="C119" t="b">
-        <v>0</v>
-      </c>
-      <c r="D119" t="s">
-        <v>49</v>
-      </c>
-      <c r="E119" t="s">
-        <v>49</v>
-      </c>
-      <c r="F119">
-        <v>0.4791666666666667</v>
-      </c>
-      <c r="G119">
-        <v>0.1383744384423298</v>
-      </c>
-      <c r="H119">
-        <v>0.8199588948910036</v>
-      </c>
-      <c r="J119">
         <v>0.9497169497169498</v>
-      </c>
-      <c r="K119">
-        <v>6</v>
-      </c>
-      <c r="L119">
-        <v>8</v>
-      </c>
-      <c r="M119">
-        <v>1</v>
-      </c>
-      <c r="N119">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14">
-      <c r="A120" t="s">
-        <v>33</v>
-      </c>
-      <c r="B120" t="s">
-        <v>34</v>
-      </c>
-      <c r="C120" t="b">
-        <v>0</v>
-      </c>
-      <c r="D120" t="s">
-        <v>57</v>
-      </c>
-      <c r="E120" t="s">
-        <v>57</v>
-      </c>
-      <c r="F120">
-        <v>0.4791666666666667</v>
-      </c>
-      <c r="G120">
-        <v>0.1367011441190805</v>
-      </c>
-      <c r="H120">
-        <v>0.821632189214253</v>
-      </c>
-      <c r="J120">
-        <v>0.9497169497169498</v>
-      </c>
-      <c r="K120">
-        <v>6</v>
-      </c>
-      <c r="L120">
-        <v>8</v>
-      </c>
-      <c r="M120">
-        <v>1</v>
-      </c>
-      <c r="N120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14">
-      <c r="A121" t="s">
-        <v>33</v>
-      </c>
-      <c r="B121" t="s">
-        <v>34</v>
-      </c>
-      <c r="C121" t="b">
-        <v>0</v>
-      </c>
-      <c r="D121" t="s">
-        <v>48</v>
-      </c>
-      <c r="E121" t="s">
-        <v>48</v>
-      </c>
-      <c r="F121">
-        <v>0.5</v>
-      </c>
-      <c r="G121">
-        <v>0.1329607286706863</v>
-      </c>
-      <c r="H121">
-        <v>0.8670392713293138</v>
-      </c>
-      <c r="J121">
-        <v>1</v>
-      </c>
-      <c r="K121">
-        <v>6</v>
-      </c>
-      <c r="L121">
-        <v>8</v>
-      </c>
-      <c r="M121">
-        <v>1</v>
-      </c>
-      <c r="N121">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6024,7 +4429,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
@@ -6035,21 +4440,21 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -6074,189 +4479,36 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5">
         <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13">
-        <v>5</v>
-      </c>
-      <c r="D13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14">
-        <v>6</v>
-      </c>
-      <c r="D14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6271,24 +4523,24 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -6303,596 +4555,596 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B30" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B31" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C33" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B34" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B35" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B37" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B38" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B39" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B40" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B41" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B42" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B45" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B46" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B47" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B48" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B49" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C49" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C50" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B52" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C52" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B53" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B54" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C54" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
